--- a/monbo-api/tests/regression/regression_farms.xlsx
+++ b/monbo-api/tests/regression/regression_farms.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC940"/>
+  <dimension ref="A1:AB940"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="21.1640625" customWidth="1" min="1" max="1"/>
@@ -459,19 +459,18 @@
     <col width="16.1640625" customWidth="1" min="3" max="3"/>
     <col width="18.6640625" customWidth="1" min="4" max="4"/>
     <col width="26.1640625" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="23.83203125" customWidth="1" min="9" max="9"/>
-    <col width="36.33203125" customWidth="1" min="10" max="10"/>
-    <col width="19.5" customWidth="1" min="11" max="11"/>
-    <col width="13.5" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="21.5" customWidth="1" min="14" max="14"/>
-    <col width="27.33203125" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="25.83203125" customWidth="1" min="17" max="17"/>
-    <col width="24.33203125" customWidth="1" min="18" max="18"/>
-    <col width="25.5" customWidth="1" min="19" max="19"/>
-    <col width="10.5" customWidth="1" min="20" max="29"/>
+    <col width="23.83203125" customWidth="1" min="8" max="8"/>
+    <col width="36.33203125" customWidth="1" min="9" max="9"/>
+    <col width="19.5" customWidth="1" min="10" max="10"/>
+    <col width="13.5" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21.5" customWidth="1" min="13" max="13"/>
+    <col width="27.33203125" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="25.83203125" customWidth="1" min="16" max="16"/>
+    <col width="24.33203125" customWidth="1" min="17" max="17"/>
+    <col width="25.5" customWidth="1" min="18" max="18"/>
+    <col width="10.5" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1">
@@ -496,12 +495,12 @@
           <t>OBLIGATORIO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>OBLIGATORIO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>OBLIGATORIO</t>
@@ -512,24 +511,19 @@
           <t>OBLIGATORIO</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>OBLIGATORIO</t>
         </is>
       </c>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>OBLIGATORIO</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="4" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="n"/>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2" ht="36.75" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -559,74 +553,70 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>País</t>
+          <t>Región</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>Formato coordenadas</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Formato coordenadas</t>
+          <t>Tipo Geometría</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Tipo Geometría</t>
+          <t>Coordenadas finca</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Coordenadas finca</t>
+          <t>Superficie [hectáreas]</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Superficie [hectáreas]</t>
+          <t>Tipo de cultivo</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Tipo de cultivo</t>
+          <t>Asociación</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Asociación</t>
+          <t>Nombre documento 1</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>Nombre documento 1</t>
+          <t>Enlace documento 1</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>Enlace documento 1</t>
+          <t>Nombre documento 2</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>Nombre documento 2</t>
+          <t>Enlace documento 2</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>Enlace documento 2</t>
+          <t>Nombre documento 3</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>Nombre documento 3</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
           <t>Enlace documento 3</t>
         </is>
       </c>
+      <c r="S2" s="6" t="n"/>
       <c r="T2" s="6" t="n"/>
       <c r="U2" s="6" t="n"/>
       <c r="V2" s="6" t="n"/>
@@ -636,7 +626,6 @@
       <c r="Z2" s="6" t="n"/>
       <c r="AA2" s="6" t="n"/>
       <c r="AB2" s="6" t="n"/>
-      <c r="AC2" s="6" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -663,73 +652,69 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Bosque</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Bosque</t>
+          <t>WKT o GeoJSON</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>WKT o GeoJSON</t>
+          <t>Point o Polygon</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Point o Polygon</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Ejemplo de GeoJSON Polygon:
 [[[-84.3752215666988, 10.14538073039277],[-84.37413039878913, 10.146085611928038],[-84.3704136080969, 10.145867434475802],[-84.37147067700938, 10.143182161350728],[-84.37155592450235, 10.140731829977492],[-84.37631273460845, 10.142913632799782],[-84.3752215666988, 10.14538073039277]]]</t>
         </is>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>5.57</v>
       </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Café Arábica</t>
+        </is>
+      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Café Arábica</t>
+          <t>Cooperativa Cafetalera Tierra de Sabores</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa Cafetalera Tierra de Sabores</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
           <t>Declaración Jurada</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>https://www.drive.google.com</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>Permiso de uso de tierras</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>https://www.drive.google.com</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Certificado Registro Único Contribuyente (RUC)</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="R3" s="9" t="inlineStr">
         <is>
           <t>https://www.drive.google.com</t>
         </is>
       </c>
+      <c r="S3" s="10" t="n"/>
       <c r="T3" s="10" t="n"/>
       <c r="U3" s="10" t="n"/>
       <c r="V3" s="10" t="n"/>
@@ -739,7 +724,6 @@
       <c r="Z3" s="10" t="n"/>
       <c r="AA3" s="10" t="n"/>
       <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -767,42 +751,37 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Orellana (Amazonía)</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Orellana (Amazonía)</t>
+          <t>GeoJSON</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>GeoJSON</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
           <t>[[[-76.351123, -0.25926], [-76.352001, -0.258128], [-76.35349, -0.257795], [-76.354024, -0.25926], [-76.353452, -0.260658], [-76.352039, -0.260325], [-76.351123, -0.25926]]]</t>
         </is>
       </c>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L4" s="11" t="n"/>
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="n"/>
       <c r="O4" s="11" t="n"/>
       <c r="P4" s="11" t="n"/>
       <c r="Q4" s="11" t="n"/>
       <c r="R4" s="11" t="n"/>
-      <c r="S4" s="11" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -830,42 +809,37 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Sucumbíos (Amazonía)</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Sucumbíos (Amazonía)</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
           <t>POLYGON ((-76.564091 -0.221076, -76.565531 -0.220146, -76.567212 -0.22096, -76.566419 -0.222699, -76.564626 -0.222849, -76.564091 -0.221076))</t>
         </is>
       </c>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Café</t>
         </is>
       </c>
+      <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
-      <c r="S5" s="11" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -893,42 +867,37 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Yasuní</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Yasuní</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
           <t>POLYGON ((-75.948473 -1.05, -75.949313 -1.048802, -75.95084 -1.048535, -75.951451 -1.05, -75.950802 -1.051398, -75.949313 -1.051198, -75.948473 -1.05))</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L6" s="11" t="n"/>
       <c r="M6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
       <c r="Q6" s="11" t="n"/>
       <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -956,44 +925,39 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>Caquetá</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Caquetá</t>
+          <t>GeoJSON</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>GeoJSON</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
           <t>[-74.40326, 1.04092]</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="J7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>Café</t>
         </is>
       </c>
+      <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -1021,42 +985,37 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>Puntarenas</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Puntarenas</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
           <t>POINT (-84.08983 9.60073)</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>Café</t>
         </is>
       </c>
+      <c r="L8" s="11" t="n"/>
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -1084,42 +1043,37 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>Puntarenas</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Puntarenas</t>
+          <t>GeoJSON</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>GeoJSON</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
           <t>[[[-84.087172, 9.600735], [-84.088247, 9.601742], [-84.089818, 9.601697], [-84.08998, 9.60017], [-84.089207, 9.598899], [-84.087716, 9.599335], [-84.087172, 9.600735]]]</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -1147,42 +1101,37 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>Puntarenas</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Puntarenas</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
           <t>POLYGON ((-84.0893096 9.6008056, -84.089255 9.6008056, -84.089255 9.6008598, -84.0893096 9.6008598, -84.0893096 9.6008056))</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L10" s="11" t="n"/>
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="n"/>
       <c r="O10" s="11" t="n"/>
       <c r="P10" s="11" t="n"/>
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="11" t="n"/>
-      <c r="S10" s="11" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -1210,42 +1159,37 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Frontera con Colombia</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Frontera con Colombia</t>
+          <t>GeoJSON</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>GeoJSON</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
           <t>[[[-76.4431975, 0.2447107], [-76.4405025, 0.2447107], [-76.4405025, 0.2609893], [-76.4431975, 0.2609893], [-76.4431975, 0.2447107]]]</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -1273,42 +1217,37 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>Ucayali</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Ucayali</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
           <t>POLYGON ((-74.998632 -10.0, -74.999619 -9.998839, -75.001218 -9.999123, -75.001052 -10.000757, -74.999577 -10.00129, -74.998632 -10.0))</t>
         </is>
       </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L12" s="11" t="n"/>
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="11" t="n"/>
       <c r="P12" s="11" t="n"/>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="11" t="n"/>
-      <c r="S12" s="11" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -1336,42 +1275,37 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>Orellana (Amazonía)</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Orellana (Amazonía)</t>
+          <t>WKT</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>WKT</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Polygon</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
           <t>POLYGON ((-76.3513475 -0.2513566, -76.3486525 -0.2486434, -76.3486525 -0.2513566, -76.3513475 -0.2486434, -76.3513475 -0.2513566))</t>
         </is>
       </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Cacao</t>
         </is>
       </c>
+      <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="11" t="n"/>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="11" t="n"/>
@@ -1392,7 +1326,6 @@
       <c r="P14" s="11" t="n"/>
       <c r="Q14" s="11" t="n"/>
       <c r="R14" s="11" t="n"/>
-      <c r="S14" s="11" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="11" t="n"/>
@@ -1413,7 +1346,6 @@
       <c r="P15" s="11" t="n"/>
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="11" t="n"/>
@@ -1434,7 +1366,6 @@
       <c r="P16" s="11" t="n"/>
       <c r="Q16" s="11" t="n"/>
       <c r="R16" s="11" t="n"/>
-      <c r="S16" s="11" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="11" t="n"/>
@@ -1455,7 +1386,6 @@
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="11" t="n"/>
@@ -1476,7 +1406,6 @@
       <c r="P18" s="11" t="n"/>
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="n"/>
-      <c r="S18" s="11" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="11" t="n"/>
@@ -1497,7 +1426,6 @@
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="11" t="n"/>
@@ -1518,7 +1446,6 @@
       <c r="P20" s="11" t="n"/>
       <c r="Q20" s="11" t="n"/>
       <c r="R20" s="11" t="n"/>
-      <c r="S20" s="11" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="11" t="n"/>
@@ -1539,7 +1466,6 @@
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="n"/>
-      <c r="S21" s="11" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="11" t="n"/>
@@ -1560,7 +1486,6 @@
       <c r="P22" s="11" t="n"/>
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="n"/>
-      <c r="S22" s="11" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="11" t="n"/>
@@ -1581,7 +1506,6 @@
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="n"/>
-      <c r="S23" s="11" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="11" t="n"/>
@@ -1602,7 +1526,6 @@
       <c r="P24" s="11" t="n"/>
       <c r="Q24" s="11" t="n"/>
       <c r="R24" s="11" t="n"/>
-      <c r="S24" s="11" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="n"/>
@@ -1623,7 +1546,6 @@
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="n"/>
-      <c r="S25" s="11" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="11" t="n"/>
@@ -1644,7 +1566,6 @@
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="11" t="n"/>
       <c r="R26" s="11" t="n"/>
-      <c r="S26" s="11" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="11" t="n"/>
@@ -1665,7 +1586,6 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="11" t="n"/>
@@ -1686,7 +1606,6 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="11" t="n"/>
       <c r="R28" s="11" t="n"/>
-      <c r="S28" s="11" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="11" t="n"/>
@@ -1707,7 +1626,6 @@
       <c r="P29" s="11" t="n"/>
       <c r="Q29" s="11" t="n"/>
       <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="11" t="n"/>
@@ -1728,7 +1646,6 @@
       <c r="P30" s="11" t="n"/>
       <c r="Q30" s="11" t="n"/>
       <c r="R30" s="11" t="n"/>
-      <c r="S30" s="11" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="11" t="n"/>
@@ -1749,7 +1666,6 @@
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="n"/>
-      <c r="S31" s="11" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="11" t="n"/>
@@ -1770,7 +1686,6 @@
       <c r="P32" s="11" t="n"/>
       <c r="Q32" s="11" t="n"/>
       <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="11" t="n"/>
@@ -1791,7 +1706,6 @@
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="n"/>
-      <c r="S33" s="11" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="11" t="n"/>
@@ -1812,7 +1726,6 @@
       <c r="P34" s="11" t="n"/>
       <c r="Q34" s="11" t="n"/>
       <c r="R34" s="11" t="n"/>
-      <c r="S34" s="11" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="11" t="n"/>
@@ -1833,7 +1746,6 @@
       <c r="P35" s="11" t="n"/>
       <c r="Q35" s="11" t="n"/>
       <c r="R35" s="11" t="n"/>
-      <c r="S35" s="11" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="11" t="n"/>
@@ -1854,7 +1766,6 @@
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="11" t="n"/>
       <c r="R36" s="11" t="n"/>
-      <c r="S36" s="11" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="n"/>
@@ -1875,7 +1786,6 @@
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="11" t="n"/>
       <c r="R37" s="11" t="n"/>
-      <c r="S37" s="11" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="n"/>
@@ -1896,7 +1806,6 @@
       <c r="P38" s="11" t="n"/>
       <c r="Q38" s="11" t="n"/>
       <c r="R38" s="11" t="n"/>
-      <c r="S38" s="11" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="11" t="n"/>
@@ -1917,7 +1826,6 @@
       <c r="P39" s="11" t="n"/>
       <c r="Q39" s="11" t="n"/>
       <c r="R39" s="11" t="n"/>
-      <c r="S39" s="11" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="n"/>
@@ -1938,7 +1846,6 @@
       <c r="P40" s="11" t="n"/>
       <c r="Q40" s="11" t="n"/>
       <c r="R40" s="11" t="n"/>
-      <c r="S40" s="11" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="11" t="n"/>
@@ -1959,7 +1866,6 @@
       <c r="P41" s="11" t="n"/>
       <c r="Q41" s="11" t="n"/>
       <c r="R41" s="11" t="n"/>
-      <c r="S41" s="11" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="11" t="n"/>
@@ -1980,7 +1886,6 @@
       <c r="P42" s="11" t="n"/>
       <c r="Q42" s="11" t="n"/>
       <c r="R42" s="11" t="n"/>
-      <c r="S42" s="11" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="11" t="n"/>
@@ -2001,7 +1906,6 @@
       <c r="P43" s="11" t="n"/>
       <c r="Q43" s="11" t="n"/>
       <c r="R43" s="11" t="n"/>
-      <c r="S43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="11" t="n"/>
@@ -2022,7 +1926,6 @@
       <c r="P44" s="11" t="n"/>
       <c r="Q44" s="11" t="n"/>
       <c r="R44" s="11" t="n"/>
-      <c r="S44" s="11" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="11" t="n"/>
@@ -2043,7 +1946,6 @@
       <c r="P45" s="11" t="n"/>
       <c r="Q45" s="11" t="n"/>
       <c r="R45" s="11" t="n"/>
-      <c r="S45" s="11" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="11" t="n"/>
@@ -2064,7 +1966,6 @@
       <c r="P46" s="11" t="n"/>
       <c r="Q46" s="11" t="n"/>
       <c r="R46" s="11" t="n"/>
-      <c r="S46" s="11" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="11" t="n"/>
@@ -2085,7 +1986,6 @@
       <c r="P47" s="11" t="n"/>
       <c r="Q47" s="11" t="n"/>
       <c r="R47" s="11" t="n"/>
-      <c r="S47" s="11" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="11" t="n"/>
@@ -2106,7 +2006,6 @@
       <c r="P48" s="11" t="n"/>
       <c r="Q48" s="11" t="n"/>
       <c r="R48" s="11" t="n"/>
-      <c r="S48" s="11" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="11" t="n"/>
@@ -2127,7 +2026,6 @@
       <c r="P49" s="11" t="n"/>
       <c r="Q49" s="11" t="n"/>
       <c r="R49" s="11" t="n"/>
-      <c r="S49" s="11" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="11" t="n"/>
@@ -2148,7 +2046,6 @@
       <c r="P50" s="11" t="n"/>
       <c r="Q50" s="11" t="n"/>
       <c r="R50" s="11" t="n"/>
-      <c r="S50" s="11" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="11" t="n"/>
@@ -2169,7 +2066,6 @@
       <c r="P51" s="11" t="n"/>
       <c r="Q51" s="11" t="n"/>
       <c r="R51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="11" t="n"/>
@@ -2190,7 +2086,6 @@
       <c r="P52" s="11" t="n"/>
       <c r="Q52" s="11" t="n"/>
       <c r="R52" s="11" t="n"/>
-      <c r="S52" s="11" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="11" t="n"/>
@@ -2211,7 +2106,6 @@
       <c r="P53" s="11" t="n"/>
       <c r="Q53" s="11" t="n"/>
       <c r="R53" s="11" t="n"/>
-      <c r="S53" s="11" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="11" t="n"/>
@@ -2232,7 +2126,6 @@
       <c r="P54" s="11" t="n"/>
       <c r="Q54" s="11" t="n"/>
       <c r="R54" s="11" t="n"/>
-      <c r="S54" s="11" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="11" t="n"/>
@@ -2253,7 +2146,6 @@
       <c r="P55" s="11" t="n"/>
       <c r="Q55" s="11" t="n"/>
       <c r="R55" s="11" t="n"/>
-      <c r="S55" s="11" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="11" t="n"/>
@@ -2274,7 +2166,6 @@
       <c r="P56" s="11" t="n"/>
       <c r="Q56" s="11" t="n"/>
       <c r="R56" s="11" t="n"/>
-      <c r="S56" s="11" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="11" t="n"/>
@@ -2295,7 +2186,6 @@
       <c r="P57" s="11" t="n"/>
       <c r="Q57" s="11" t="n"/>
       <c r="R57" s="11" t="n"/>
-      <c r="S57" s="11" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="11" t="n"/>
@@ -2316,7 +2206,6 @@
       <c r="P58" s="11" t="n"/>
       <c r="Q58" s="11" t="n"/>
       <c r="R58" s="11" t="n"/>
-      <c r="S58" s="11" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="11" t="n"/>
@@ -2337,7 +2226,6 @@
       <c r="P59" s="11" t="n"/>
       <c r="Q59" s="11" t="n"/>
       <c r="R59" s="11" t="n"/>
-      <c r="S59" s="11" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="11" t="n"/>
@@ -2358,7 +2246,6 @@
       <c r="P60" s="11" t="n"/>
       <c r="Q60" s="11" t="n"/>
       <c r="R60" s="11" t="n"/>
-      <c r="S60" s="11" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="11" t="n"/>
@@ -2379,7 +2266,6 @@
       <c r="P61" s="11" t="n"/>
       <c r="Q61" s="11" t="n"/>
       <c r="R61" s="11" t="n"/>
-      <c r="S61" s="11" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="11" t="n"/>
@@ -2400,7 +2286,6 @@
       <c r="P62" s="11" t="n"/>
       <c r="Q62" s="11" t="n"/>
       <c r="R62" s="11" t="n"/>
-      <c r="S62" s="11" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="11" t="n"/>
@@ -2421,7 +2306,6 @@
       <c r="P63" s="11" t="n"/>
       <c r="Q63" s="11" t="n"/>
       <c r="R63" s="11" t="n"/>
-      <c r="S63" s="11" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="11" t="n"/>
@@ -2442,7 +2326,6 @@
       <c r="P64" s="11" t="n"/>
       <c r="Q64" s="11" t="n"/>
       <c r="R64" s="11" t="n"/>
-      <c r="S64" s="11" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="11" t="n"/>
@@ -2463,7 +2346,6 @@
       <c r="P65" s="11" t="n"/>
       <c r="Q65" s="11" t="n"/>
       <c r="R65" s="11" t="n"/>
-      <c r="S65" s="11" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="11" t="n"/>
@@ -2484,7 +2366,6 @@
       <c r="P66" s="11" t="n"/>
       <c r="Q66" s="11" t="n"/>
       <c r="R66" s="11" t="n"/>
-      <c r="S66" s="11" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="11" t="n"/>
@@ -2505,7 +2386,6 @@
       <c r="P67" s="11" t="n"/>
       <c r="Q67" s="11" t="n"/>
       <c r="R67" s="11" t="n"/>
-      <c r="S67" s="11" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="11" t="n"/>
@@ -2526,7 +2406,6 @@
       <c r="P68" s="11" t="n"/>
       <c r="Q68" s="11" t="n"/>
       <c r="R68" s="11" t="n"/>
-      <c r="S68" s="11" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="11" t="n"/>
@@ -2547,7 +2426,6 @@
       <c r="P69" s="11" t="n"/>
       <c r="Q69" s="11" t="n"/>
       <c r="R69" s="11" t="n"/>
-      <c r="S69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="11" t="n"/>
@@ -2568,7 +2446,6 @@
       <c r="P70" s="11" t="n"/>
       <c r="Q70" s="11" t="n"/>
       <c r="R70" s="11" t="n"/>
-      <c r="S70" s="11" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="11" t="n"/>
@@ -2589,7 +2466,6 @@
       <c r="P71" s="11" t="n"/>
       <c r="Q71" s="11" t="n"/>
       <c r="R71" s="11" t="n"/>
-      <c r="S71" s="11" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="11" t="n"/>
@@ -2610,7 +2486,6 @@
       <c r="P72" s="11" t="n"/>
       <c r="Q72" s="11" t="n"/>
       <c r="R72" s="11" t="n"/>
-      <c r="S72" s="11" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="11" t="n"/>
@@ -2631,7 +2506,6 @@
       <c r="P73" s="11" t="n"/>
       <c r="Q73" s="11" t="n"/>
       <c r="R73" s="11" t="n"/>
-      <c r="S73" s="11" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="11" t="n"/>
@@ -2652,7 +2526,6 @@
       <c r="P74" s="11" t="n"/>
       <c r="Q74" s="11" t="n"/>
       <c r="R74" s="11" t="n"/>
-      <c r="S74" s="11" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="11" t="n"/>
@@ -2673,7 +2546,6 @@
       <c r="P75" s="11" t="n"/>
       <c r="Q75" s="11" t="n"/>
       <c r="R75" s="11" t="n"/>
-      <c r="S75" s="11" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="11" t="n"/>
@@ -2694,7 +2566,6 @@
       <c r="P76" s="11" t="n"/>
       <c r="Q76" s="11" t="n"/>
       <c r="R76" s="11" t="n"/>
-      <c r="S76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="11" t="n"/>
@@ -2715,7 +2586,6 @@
       <c r="P77" s="11" t="n"/>
       <c r="Q77" s="11" t="n"/>
       <c r="R77" s="11" t="n"/>
-      <c r="S77" s="11" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="11" t="n"/>
@@ -2736,7 +2606,6 @@
       <c r="P78" s="11" t="n"/>
       <c r="Q78" s="11" t="n"/>
       <c r="R78" s="11" t="n"/>
-      <c r="S78" s="11" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="11" t="n"/>
@@ -2757,7 +2626,6 @@
       <c r="P79" s="11" t="n"/>
       <c r="Q79" s="11" t="n"/>
       <c r="R79" s="11" t="n"/>
-      <c r="S79" s="11" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="11" t="n"/>
@@ -2778,7 +2646,6 @@
       <c r="P80" s="11" t="n"/>
       <c r="Q80" s="11" t="n"/>
       <c r="R80" s="11" t="n"/>
-      <c r="S80" s="11" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="11" t="n"/>
@@ -2799,7 +2666,6 @@
       <c r="P81" s="11" t="n"/>
       <c r="Q81" s="11" t="n"/>
       <c r="R81" s="11" t="n"/>
-      <c r="S81" s="11" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="11" t="n"/>
@@ -2820,7 +2686,6 @@
       <c r="P82" s="11" t="n"/>
       <c r="Q82" s="11" t="n"/>
       <c r="R82" s="11" t="n"/>
-      <c r="S82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="11" t="n"/>
@@ -2841,7 +2706,6 @@
       <c r="P83" s="11" t="n"/>
       <c r="Q83" s="11" t="n"/>
       <c r="R83" s="11" t="n"/>
-      <c r="S83" s="11" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="11" t="n"/>
@@ -2862,7 +2726,6 @@
       <c r="P84" s="11" t="n"/>
       <c r="Q84" s="11" t="n"/>
       <c r="R84" s="11" t="n"/>
-      <c r="S84" s="11" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="11" t="n"/>
@@ -2883,7 +2746,6 @@
       <c r="P85" s="11" t="n"/>
       <c r="Q85" s="11" t="n"/>
       <c r="R85" s="11" t="n"/>
-      <c r="S85" s="11" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="11" t="n"/>
@@ -2904,7 +2766,6 @@
       <c r="P86" s="11" t="n"/>
       <c r="Q86" s="11" t="n"/>
       <c r="R86" s="11" t="n"/>
-      <c r="S86" s="11" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="11" t="n"/>
@@ -2925,7 +2786,6 @@
       <c r="P87" s="11" t="n"/>
       <c r="Q87" s="11" t="n"/>
       <c r="R87" s="11" t="n"/>
-      <c r="S87" s="11" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="11" t="n"/>
@@ -2946,7 +2806,6 @@
       <c r="P88" s="11" t="n"/>
       <c r="Q88" s="11" t="n"/>
       <c r="R88" s="11" t="n"/>
-      <c r="S88" s="11" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="11" t="n"/>
@@ -2967,7 +2826,6 @@
       <c r="P89" s="11" t="n"/>
       <c r="Q89" s="11" t="n"/>
       <c r="R89" s="11" t="n"/>
-      <c r="S89" s="11" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="11" t="n"/>
@@ -2988,7 +2846,6 @@
       <c r="P90" s="11" t="n"/>
       <c r="Q90" s="11" t="n"/>
       <c r="R90" s="11" t="n"/>
-      <c r="S90" s="11" t="n"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="11" t="n"/>
@@ -3009,7 +2866,6 @@
       <c r="P91" s="11" t="n"/>
       <c r="Q91" s="11" t="n"/>
       <c r="R91" s="11" t="n"/>
-      <c r="S91" s="11" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="11" t="n"/>
@@ -3030,7 +2886,6 @@
       <c r="P92" s="11" t="n"/>
       <c r="Q92" s="11" t="n"/>
       <c r="R92" s="11" t="n"/>
-      <c r="S92" s="11" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="11" t="n"/>
@@ -3051,7 +2906,6 @@
       <c r="P93" s="11" t="n"/>
       <c r="Q93" s="11" t="n"/>
       <c r="R93" s="11" t="n"/>
-      <c r="S93" s="11" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="11" t="n"/>
@@ -3072,7 +2926,6 @@
       <c r="P94" s="11" t="n"/>
       <c r="Q94" s="11" t="n"/>
       <c r="R94" s="11" t="n"/>
-      <c r="S94" s="11" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="11" t="n"/>
@@ -3093,7 +2946,6 @@
       <c r="P95" s="11" t="n"/>
       <c r="Q95" s="11" t="n"/>
       <c r="R95" s="11" t="n"/>
-      <c r="S95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="11" t="n"/>
@@ -3114,7 +2966,6 @@
       <c r="P96" s="11" t="n"/>
       <c r="Q96" s="11" t="n"/>
       <c r="R96" s="11" t="n"/>
-      <c r="S96" s="11" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="11" t="n"/>
@@ -3135,7 +2986,6 @@
       <c r="P97" s="11" t="n"/>
       <c r="Q97" s="11" t="n"/>
       <c r="R97" s="11" t="n"/>
-      <c r="S97" s="11" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="11" t="n"/>
@@ -3156,7 +3006,6 @@
       <c r="P98" s="11" t="n"/>
       <c r="Q98" s="11" t="n"/>
       <c r="R98" s="11" t="n"/>
-      <c r="S98" s="11" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="11" t="n"/>
@@ -3177,7 +3026,6 @@
       <c r="P99" s="11" t="n"/>
       <c r="Q99" s="11" t="n"/>
       <c r="R99" s="11" t="n"/>
-      <c r="S99" s="11" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="11" t="n"/>
@@ -3198,7 +3046,6 @@
       <c r="P100" s="11" t="n"/>
       <c r="Q100" s="11" t="n"/>
       <c r="R100" s="11" t="n"/>
-      <c r="S100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="11" t="n"/>
@@ -3219,7 +3066,6 @@
       <c r="P101" s="11" t="n"/>
       <c r="Q101" s="11" t="n"/>
       <c r="R101" s="11" t="n"/>
-      <c r="S101" s="11" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="11" t="n"/>
@@ -3240,7 +3086,6 @@
       <c r="P102" s="11" t="n"/>
       <c r="Q102" s="11" t="n"/>
       <c r="R102" s="11" t="n"/>
-      <c r="S102" s="11" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="11" t="n"/>
@@ -3261,7 +3106,6 @@
       <c r="P103" s="11" t="n"/>
       <c r="Q103" s="11" t="n"/>
       <c r="R103" s="11" t="n"/>
-      <c r="S103" s="11" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="11" t="n"/>
@@ -3282,7 +3126,6 @@
       <c r="P104" s="11" t="n"/>
       <c r="Q104" s="11" t="n"/>
       <c r="R104" s="11" t="n"/>
-      <c r="S104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="11" t="n"/>
@@ -3303,7 +3146,6 @@
       <c r="P105" s="11" t="n"/>
       <c r="Q105" s="11" t="n"/>
       <c r="R105" s="11" t="n"/>
-      <c r="S105" s="11" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="11" t="n"/>
@@ -3324,7 +3166,6 @@
       <c r="P106" s="11" t="n"/>
       <c r="Q106" s="11" t="n"/>
       <c r="R106" s="11" t="n"/>
-      <c r="S106" s="11" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="11" t="n"/>
@@ -3345,7 +3186,6 @@
       <c r="P107" s="11" t="n"/>
       <c r="Q107" s="11" t="n"/>
       <c r="R107" s="11" t="n"/>
-      <c r="S107" s="11" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="11" t="n"/>
@@ -3366,7 +3206,6 @@
       <c r="P108" s="11" t="n"/>
       <c r="Q108" s="11" t="n"/>
       <c r="R108" s="11" t="n"/>
-      <c r="S108" s="11" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="11" t="n"/>
@@ -3387,7 +3226,6 @@
       <c r="P109" s="11" t="n"/>
       <c r="Q109" s="11" t="n"/>
       <c r="R109" s="11" t="n"/>
-      <c r="S109" s="11" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="11" t="n"/>
@@ -3408,7 +3246,6 @@
       <c r="P110" s="11" t="n"/>
       <c r="Q110" s="11" t="n"/>
       <c r="R110" s="11" t="n"/>
-      <c r="S110" s="11" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="11" t="n"/>
@@ -3429,7 +3266,6 @@
       <c r="P111" s="11" t="n"/>
       <c r="Q111" s="11" t="n"/>
       <c r="R111" s="11" t="n"/>
-      <c r="S111" s="11" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="11" t="n"/>
@@ -3450,7 +3286,6 @@
       <c r="P112" s="11" t="n"/>
       <c r="Q112" s="11" t="n"/>
       <c r="R112" s="11" t="n"/>
-      <c r="S112" s="11" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="11" t="n"/>
@@ -3471,7 +3306,6 @@
       <c r="P113" s="11" t="n"/>
       <c r="Q113" s="11" t="n"/>
       <c r="R113" s="11" t="n"/>
-      <c r="S113" s="11" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="11" t="n"/>
@@ -3492,7 +3326,6 @@
       <c r="P114" s="11" t="n"/>
       <c r="Q114" s="11" t="n"/>
       <c r="R114" s="11" t="n"/>
-      <c r="S114" s="11" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="11" t="n"/>
@@ -3513,7 +3346,6 @@
       <c r="P115" s="11" t="n"/>
       <c r="Q115" s="11" t="n"/>
       <c r="R115" s="11" t="n"/>
-      <c r="S115" s="11" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="11" t="n"/>
@@ -3534,7 +3366,6 @@
       <c r="P116" s="11" t="n"/>
       <c r="Q116" s="11" t="n"/>
       <c r="R116" s="11" t="n"/>
-      <c r="S116" s="11" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="11" t="n"/>
@@ -3555,7 +3386,6 @@
       <c r="P117" s="11" t="n"/>
       <c r="Q117" s="11" t="n"/>
       <c r="R117" s="11" t="n"/>
-      <c r="S117" s="11" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="11" t="n"/>
@@ -3576,7 +3406,6 @@
       <c r="P118" s="11" t="n"/>
       <c r="Q118" s="11" t="n"/>
       <c r="R118" s="11" t="n"/>
-      <c r="S118" s="11" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="11" t="n"/>
@@ -3597,7 +3426,6 @@
       <c r="P119" s="11" t="n"/>
       <c r="Q119" s="11" t="n"/>
       <c r="R119" s="11" t="n"/>
-      <c r="S119" s="11" t="n"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="11" t="n"/>
@@ -3618,7 +3446,6 @@
       <c r="P120" s="11" t="n"/>
       <c r="Q120" s="11" t="n"/>
       <c r="R120" s="11" t="n"/>
-      <c r="S120" s="11" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="11" t="n"/>
@@ -3639,7 +3466,6 @@
       <c r="P121" s="11" t="n"/>
       <c r="Q121" s="11" t="n"/>
       <c r="R121" s="11" t="n"/>
-      <c r="S121" s="11" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="11" t="n"/>
@@ -3660,7 +3486,6 @@
       <c r="P122" s="11" t="n"/>
       <c r="Q122" s="11" t="n"/>
       <c r="R122" s="11" t="n"/>
-      <c r="S122" s="11" t="n"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="11" t="n"/>
@@ -3681,7 +3506,6 @@
       <c r="P123" s="11" t="n"/>
       <c r="Q123" s="11" t="n"/>
       <c r="R123" s="11" t="n"/>
-      <c r="S123" s="11" t="n"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="11" t="n"/>
@@ -3702,7 +3526,6 @@
       <c r="P124" s="11" t="n"/>
       <c r="Q124" s="11" t="n"/>
       <c r="R124" s="11" t="n"/>
-      <c r="S124" s="11" t="n"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="11" t="n"/>
@@ -3723,7 +3546,6 @@
       <c r="P125" s="11" t="n"/>
       <c r="Q125" s="11" t="n"/>
       <c r="R125" s="11" t="n"/>
-      <c r="S125" s="11" t="n"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="11" t="n"/>
@@ -3744,7 +3566,6 @@
       <c r="P126" s="11" t="n"/>
       <c r="Q126" s="11" t="n"/>
       <c r="R126" s="11" t="n"/>
-      <c r="S126" s="11" t="n"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="11" t="n"/>
@@ -3765,7 +3586,6 @@
       <c r="P127" s="11" t="n"/>
       <c r="Q127" s="11" t="n"/>
       <c r="R127" s="11" t="n"/>
-      <c r="S127" s="11" t="n"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="11" t="n"/>
@@ -3786,7 +3606,6 @@
       <c r="P128" s="11" t="n"/>
       <c r="Q128" s="11" t="n"/>
       <c r="R128" s="11" t="n"/>
-      <c r="S128" s="11" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="11" t="n"/>
@@ -3807,7 +3626,6 @@
       <c r="P129" s="11" t="n"/>
       <c r="Q129" s="11" t="n"/>
       <c r="R129" s="11" t="n"/>
-      <c r="S129" s="11" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="11" t="n"/>
@@ -3828,7 +3646,6 @@
       <c r="P130" s="11" t="n"/>
       <c r="Q130" s="11" t="n"/>
       <c r="R130" s="11" t="n"/>
-      <c r="S130" s="11" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="11" t="n"/>
@@ -3849,7 +3666,6 @@
       <c r="P131" s="11" t="n"/>
       <c r="Q131" s="11" t="n"/>
       <c r="R131" s="11" t="n"/>
-      <c r="S131" s="11" t="n"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="11" t="n"/>
@@ -3870,7 +3686,6 @@
       <c r="P132" s="11" t="n"/>
       <c r="Q132" s="11" t="n"/>
       <c r="R132" s="11" t="n"/>
-      <c r="S132" s="11" t="n"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="11" t="n"/>
@@ -3891,7 +3706,6 @@
       <c r="P133" s="11" t="n"/>
       <c r="Q133" s="11" t="n"/>
       <c r="R133" s="11" t="n"/>
-      <c r="S133" s="11" t="n"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="11" t="n"/>
@@ -3912,7 +3726,6 @@
       <c r="P134" s="11" t="n"/>
       <c r="Q134" s="11" t="n"/>
       <c r="R134" s="11" t="n"/>
-      <c r="S134" s="11" t="n"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="11" t="n"/>
@@ -3933,7 +3746,6 @@
       <c r="P135" s="11" t="n"/>
       <c r="Q135" s="11" t="n"/>
       <c r="R135" s="11" t="n"/>
-      <c r="S135" s="11" t="n"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="11" t="n"/>
@@ -3954,7 +3766,6 @@
       <c r="P136" s="11" t="n"/>
       <c r="Q136" s="11" t="n"/>
       <c r="R136" s="11" t="n"/>
-      <c r="S136" s="11" t="n"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="11" t="n"/>
@@ -3975,7 +3786,6 @@
       <c r="P137" s="11" t="n"/>
       <c r="Q137" s="11" t="n"/>
       <c r="R137" s="11" t="n"/>
-      <c r="S137" s="11" t="n"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="11" t="n"/>
@@ -3996,7 +3806,6 @@
       <c r="P138" s="11" t="n"/>
       <c r="Q138" s="11" t="n"/>
       <c r="R138" s="11" t="n"/>
-      <c r="S138" s="11" t="n"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="11" t="n"/>
@@ -4017,7 +3826,6 @@
       <c r="P139" s="11" t="n"/>
       <c r="Q139" s="11" t="n"/>
       <c r="R139" s="11" t="n"/>
-      <c r="S139" s="11" t="n"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="11" t="n"/>
@@ -4038,7 +3846,6 @@
       <c r="P140" s="11" t="n"/>
       <c r="Q140" s="11" t="n"/>
       <c r="R140" s="11" t="n"/>
-      <c r="S140" s="11" t="n"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="11" t="n"/>
@@ -4059,7 +3866,6 @@
       <c r="P141" s="11" t="n"/>
       <c r="Q141" s="11" t="n"/>
       <c r="R141" s="11" t="n"/>
-      <c r="S141" s="11" t="n"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="11" t="n"/>
@@ -4080,7 +3886,6 @@
       <c r="P142" s="11" t="n"/>
       <c r="Q142" s="11" t="n"/>
       <c r="R142" s="11" t="n"/>
-      <c r="S142" s="11" t="n"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="11" t="n"/>
@@ -4101,7 +3906,6 @@
       <c r="P143" s="11" t="n"/>
       <c r="Q143" s="11" t="n"/>
       <c r="R143" s="11" t="n"/>
-      <c r="S143" s="11" t="n"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="11" t="n"/>
@@ -4122,7 +3926,6 @@
       <c r="P144" s="11" t="n"/>
       <c r="Q144" s="11" t="n"/>
       <c r="R144" s="11" t="n"/>
-      <c r="S144" s="11" t="n"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="11" t="n"/>
@@ -4143,7 +3946,6 @@
       <c r="P145" s="11" t="n"/>
       <c r="Q145" s="11" t="n"/>
       <c r="R145" s="11" t="n"/>
-      <c r="S145" s="11" t="n"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="11" t="n"/>
@@ -4164,7 +3966,6 @@
       <c r="P146" s="11" t="n"/>
       <c r="Q146" s="11" t="n"/>
       <c r="R146" s="11" t="n"/>
-      <c r="S146" s="11" t="n"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="11" t="n"/>
@@ -4185,7 +3986,6 @@
       <c r="P147" s="11" t="n"/>
       <c r="Q147" s="11" t="n"/>
       <c r="R147" s="11" t="n"/>
-      <c r="S147" s="11" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="11" t="n"/>
@@ -4206,7 +4006,6 @@
       <c r="P148" s="11" t="n"/>
       <c r="Q148" s="11" t="n"/>
       <c r="R148" s="11" t="n"/>
-      <c r="S148" s="11" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="11" t="n"/>
@@ -4227,7 +4026,6 @@
       <c r="P149" s="11" t="n"/>
       <c r="Q149" s="11" t="n"/>
       <c r="R149" s="11" t="n"/>
-      <c r="S149" s="11" t="n"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="11" t="n"/>
@@ -4248,7 +4046,6 @@
       <c r="P150" s="11" t="n"/>
       <c r="Q150" s="11" t="n"/>
       <c r="R150" s="11" t="n"/>
-      <c r="S150" s="11" t="n"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="11" t="n"/>
@@ -4269,7 +4066,6 @@
       <c r="P151" s="11" t="n"/>
       <c r="Q151" s="11" t="n"/>
       <c r="R151" s="11" t="n"/>
-      <c r="S151" s="11" t="n"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="11" t="n"/>
@@ -4290,7 +4086,6 @@
       <c r="P152" s="11" t="n"/>
       <c r="Q152" s="11" t="n"/>
       <c r="R152" s="11" t="n"/>
-      <c r="S152" s="11" t="n"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="11" t="n"/>
@@ -4311,7 +4106,6 @@
       <c r="P153" s="11" t="n"/>
       <c r="Q153" s="11" t="n"/>
       <c r="R153" s="11" t="n"/>
-      <c r="S153" s="11" t="n"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="11" t="n"/>
@@ -4332,7 +4126,6 @@
       <c r="P154" s="11" t="n"/>
       <c r="Q154" s="11" t="n"/>
       <c r="R154" s="11" t="n"/>
-      <c r="S154" s="11" t="n"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="11" t="n"/>
@@ -4353,7 +4146,6 @@
       <c r="P155" s="11" t="n"/>
       <c r="Q155" s="11" t="n"/>
       <c r="R155" s="11" t="n"/>
-      <c r="S155" s="11" t="n"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="11" t="n"/>
@@ -4374,7 +4166,6 @@
       <c r="P156" s="11" t="n"/>
       <c r="Q156" s="11" t="n"/>
       <c r="R156" s="11" t="n"/>
-      <c r="S156" s="11" t="n"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="11" t="n"/>
@@ -4395,7 +4186,6 @@
       <c r="P157" s="11" t="n"/>
       <c r="Q157" s="11" t="n"/>
       <c r="R157" s="11" t="n"/>
-      <c r="S157" s="11" t="n"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="11" t="n"/>
@@ -4416,7 +4206,6 @@
       <c r="P158" s="11" t="n"/>
       <c r="Q158" s="11" t="n"/>
       <c r="R158" s="11" t="n"/>
-      <c r="S158" s="11" t="n"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="11" t="n"/>
@@ -4437,7 +4226,6 @@
       <c r="P159" s="11" t="n"/>
       <c r="Q159" s="11" t="n"/>
       <c r="R159" s="11" t="n"/>
-      <c r="S159" s="11" t="n"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="11" t="n"/>
@@ -4458,7 +4246,6 @@
       <c r="P160" s="11" t="n"/>
       <c r="Q160" s="11" t="n"/>
       <c r="R160" s="11" t="n"/>
-      <c r="S160" s="11" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="11" t="n"/>
@@ -4479,7 +4266,6 @@
       <c r="P161" s="11" t="n"/>
       <c r="Q161" s="11" t="n"/>
       <c r="R161" s="11" t="n"/>
-      <c r="S161" s="11" t="n"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="11" t="n"/>
@@ -4500,7 +4286,6 @@
       <c r="P162" s="11" t="n"/>
       <c r="Q162" s="11" t="n"/>
       <c r="R162" s="11" t="n"/>
-      <c r="S162" s="11" t="n"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="11" t="n"/>
@@ -4521,7 +4306,6 @@
       <c r="P163" s="11" t="n"/>
       <c r="Q163" s="11" t="n"/>
       <c r="R163" s="11" t="n"/>
-      <c r="S163" s="11" t="n"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="11" t="n"/>
@@ -4542,7 +4326,6 @@
       <c r="P164" s="11" t="n"/>
       <c r="Q164" s="11" t="n"/>
       <c r="R164" s="11" t="n"/>
-      <c r="S164" s="11" t="n"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="11" t="n"/>
@@ -4563,7 +4346,6 @@
       <c r="P165" s="11" t="n"/>
       <c r="Q165" s="11" t="n"/>
       <c r="R165" s="11" t="n"/>
-      <c r="S165" s="11" t="n"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="11" t="n"/>
@@ -4584,7 +4366,6 @@
       <c r="P166" s="11" t="n"/>
       <c r="Q166" s="11" t="n"/>
       <c r="R166" s="11" t="n"/>
-      <c r="S166" s="11" t="n"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="11" t="n"/>
@@ -4605,7 +4386,6 @@
       <c r="P167" s="11" t="n"/>
       <c r="Q167" s="11" t="n"/>
       <c r="R167" s="11" t="n"/>
-      <c r="S167" s="11" t="n"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="11" t="n"/>
@@ -4626,7 +4406,6 @@
       <c r="P168" s="11" t="n"/>
       <c r="Q168" s="11" t="n"/>
       <c r="R168" s="11" t="n"/>
-      <c r="S168" s="11" t="n"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="11" t="n"/>
@@ -4647,7 +4426,6 @@
       <c r="P169" s="11" t="n"/>
       <c r="Q169" s="11" t="n"/>
       <c r="R169" s="11" t="n"/>
-      <c r="S169" s="11" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="11" t="n"/>
@@ -4668,7 +4446,6 @@
       <c r="P170" s="11" t="n"/>
       <c r="Q170" s="11" t="n"/>
       <c r="R170" s="11" t="n"/>
-      <c r="S170" s="11" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="11" t="n"/>
@@ -4689,7 +4466,6 @@
       <c r="P171" s="11" t="n"/>
       <c r="Q171" s="11" t="n"/>
       <c r="R171" s="11" t="n"/>
-      <c r="S171" s="11" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="11" t="n"/>
@@ -4710,7 +4486,6 @@
       <c r="P172" s="11" t="n"/>
       <c r="Q172" s="11" t="n"/>
       <c r="R172" s="11" t="n"/>
-      <c r="S172" s="11" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="11" t="n"/>
@@ -4731,7 +4506,6 @@
       <c r="P173" s="11" t="n"/>
       <c r="Q173" s="11" t="n"/>
       <c r="R173" s="11" t="n"/>
-      <c r="S173" s="11" t="n"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="11" t="n"/>
@@ -4752,7 +4526,6 @@
       <c r="P174" s="11" t="n"/>
       <c r="Q174" s="11" t="n"/>
       <c r="R174" s="11" t="n"/>
-      <c r="S174" s="11" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="11" t="n"/>
@@ -4773,7 +4546,6 @@
       <c r="P175" s="11" t="n"/>
       <c r="Q175" s="11" t="n"/>
       <c r="R175" s="11" t="n"/>
-      <c r="S175" s="11" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="11" t="n"/>
@@ -4794,7 +4566,6 @@
       <c r="P176" s="11" t="n"/>
       <c r="Q176" s="11" t="n"/>
       <c r="R176" s="11" t="n"/>
-      <c r="S176" s="11" t="n"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="11" t="n"/>
@@ -4815,7 +4586,6 @@
       <c r="P177" s="11" t="n"/>
       <c r="Q177" s="11" t="n"/>
       <c r="R177" s="11" t="n"/>
-      <c r="S177" s="11" t="n"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="11" t="n"/>
@@ -4836,7 +4606,6 @@
       <c r="P178" s="11" t="n"/>
       <c r="Q178" s="11" t="n"/>
       <c r="R178" s="11" t="n"/>
-      <c r="S178" s="11" t="n"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="11" t="n"/>
@@ -4857,7 +4626,6 @@
       <c r="P179" s="11" t="n"/>
       <c r="Q179" s="11" t="n"/>
       <c r="R179" s="11" t="n"/>
-      <c r="S179" s="11" t="n"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="11" t="n"/>
@@ -4878,7 +4646,6 @@
       <c r="P180" s="11" t="n"/>
       <c r="Q180" s="11" t="n"/>
       <c r="R180" s="11" t="n"/>
-      <c r="S180" s="11" t="n"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="11" t="n"/>
@@ -4899,7 +4666,6 @@
       <c r="P181" s="11" t="n"/>
       <c r="Q181" s="11" t="n"/>
       <c r="R181" s="11" t="n"/>
-      <c r="S181" s="11" t="n"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="11" t="n"/>
@@ -4920,7 +4686,6 @@
       <c r="P182" s="11" t="n"/>
       <c r="Q182" s="11" t="n"/>
       <c r="R182" s="11" t="n"/>
-      <c r="S182" s="11" t="n"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="11" t="n"/>
@@ -4941,7 +4706,6 @@
       <c r="P183" s="11" t="n"/>
       <c r="Q183" s="11" t="n"/>
       <c r="R183" s="11" t="n"/>
-      <c r="S183" s="11" t="n"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="11" t="n"/>
@@ -4962,7 +4726,6 @@
       <c r="P184" s="11" t="n"/>
       <c r="Q184" s="11" t="n"/>
       <c r="R184" s="11" t="n"/>
-      <c r="S184" s="11" t="n"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="11" t="n"/>
@@ -4983,7 +4746,6 @@
       <c r="P185" s="11" t="n"/>
       <c r="Q185" s="11" t="n"/>
       <c r="R185" s="11" t="n"/>
-      <c r="S185" s="11" t="n"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="11" t="n"/>
@@ -5004,7 +4766,6 @@
       <c r="P186" s="11" t="n"/>
       <c r="Q186" s="11" t="n"/>
       <c r="R186" s="11" t="n"/>
-      <c r="S186" s="11" t="n"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="11" t="n"/>
@@ -5025,7 +4786,6 @@
       <c r="P187" s="11" t="n"/>
       <c r="Q187" s="11" t="n"/>
       <c r="R187" s="11" t="n"/>
-      <c r="S187" s="11" t="n"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="11" t="n"/>
@@ -5046,7 +4806,6 @@
       <c r="P188" s="11" t="n"/>
       <c r="Q188" s="11" t="n"/>
       <c r="R188" s="11" t="n"/>
-      <c r="S188" s="11" t="n"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="11" t="n"/>
@@ -5067,7 +4826,6 @@
       <c r="P189" s="11" t="n"/>
       <c r="Q189" s="11" t="n"/>
       <c r="R189" s="11" t="n"/>
-      <c r="S189" s="11" t="n"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="11" t="n"/>
@@ -5088,7 +4846,6 @@
       <c r="P190" s="11" t="n"/>
       <c r="Q190" s="11" t="n"/>
       <c r="R190" s="11" t="n"/>
-      <c r="S190" s="11" t="n"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="11" t="n"/>
@@ -5109,7 +4866,6 @@
       <c r="P191" s="11" t="n"/>
       <c r="Q191" s="11" t="n"/>
       <c r="R191" s="11" t="n"/>
-      <c r="S191" s="11" t="n"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="11" t="n"/>
@@ -5130,7 +4886,6 @@
       <c r="P192" s="11" t="n"/>
       <c r="Q192" s="11" t="n"/>
       <c r="R192" s="11" t="n"/>
-      <c r="S192" s="11" t="n"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="11" t="n"/>
@@ -5151,7 +4906,6 @@
       <c r="P193" s="11" t="n"/>
       <c r="Q193" s="11" t="n"/>
       <c r="R193" s="11" t="n"/>
-      <c r="S193" s="11" t="n"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="11" t="n"/>
@@ -5172,7 +4926,6 @@
       <c r="P194" s="11" t="n"/>
       <c r="Q194" s="11" t="n"/>
       <c r="R194" s="11" t="n"/>
-      <c r="S194" s="11" t="n"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="11" t="n"/>
@@ -5193,7 +4946,6 @@
       <c r="P195" s="11" t="n"/>
       <c r="Q195" s="11" t="n"/>
       <c r="R195" s="11" t="n"/>
-      <c r="S195" s="11" t="n"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="11" t="n"/>
@@ -5214,7 +4966,6 @@
       <c r="P196" s="11" t="n"/>
       <c r="Q196" s="11" t="n"/>
       <c r="R196" s="11" t="n"/>
-      <c r="S196" s="11" t="n"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="11" t="n"/>
@@ -5235,7 +4986,6 @@
       <c r="P197" s="11" t="n"/>
       <c r="Q197" s="11" t="n"/>
       <c r="R197" s="11" t="n"/>
-      <c r="S197" s="11" t="n"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="11" t="n"/>
@@ -5256,7 +5006,6 @@
       <c r="P198" s="11" t="n"/>
       <c r="Q198" s="11" t="n"/>
       <c r="R198" s="11" t="n"/>
-      <c r="S198" s="11" t="n"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="11" t="n"/>
@@ -5277,7 +5026,6 @@
       <c r="P199" s="11" t="n"/>
       <c r="Q199" s="11" t="n"/>
       <c r="R199" s="11" t="n"/>
-      <c r="S199" s="11" t="n"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="11" t="n"/>
@@ -5298,7 +5046,6 @@
       <c r="P200" s="11" t="n"/>
       <c r="Q200" s="11" t="n"/>
       <c r="R200" s="11" t="n"/>
-      <c r="S200" s="11" t="n"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="11" t="n"/>
@@ -5319,7 +5066,6 @@
       <c r="P201" s="11" t="n"/>
       <c r="Q201" s="11" t="n"/>
       <c r="R201" s="11" t="n"/>
-      <c r="S201" s="11" t="n"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="11" t="n"/>
@@ -5340,7 +5086,6 @@
       <c r="P202" s="11" t="n"/>
       <c r="Q202" s="11" t="n"/>
       <c r="R202" s="11" t="n"/>
-      <c r="S202" s="11" t="n"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="11" t="n"/>
@@ -5361,7 +5106,6 @@
       <c r="P203" s="11" t="n"/>
       <c r="Q203" s="11" t="n"/>
       <c r="R203" s="11" t="n"/>
-      <c r="S203" s="11" t="n"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="11" t="n"/>
@@ -5382,7 +5126,6 @@
       <c r="P204" s="11" t="n"/>
       <c r="Q204" s="11" t="n"/>
       <c r="R204" s="11" t="n"/>
-      <c r="S204" s="11" t="n"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="11" t="n"/>
@@ -5403,7 +5146,6 @@
       <c r="P205" s="11" t="n"/>
       <c r="Q205" s="11" t="n"/>
       <c r="R205" s="11" t="n"/>
-      <c r="S205" s="11" t="n"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="11" t="n"/>
@@ -5424,7 +5166,6 @@
       <c r="P206" s="11" t="n"/>
       <c r="Q206" s="11" t="n"/>
       <c r="R206" s="11" t="n"/>
-      <c r="S206" s="11" t="n"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="11" t="n"/>
@@ -5445,7 +5186,6 @@
       <c r="P207" s="11" t="n"/>
       <c r="Q207" s="11" t="n"/>
       <c r="R207" s="11" t="n"/>
-      <c r="S207" s="11" t="n"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="11" t="n"/>
@@ -5466,7 +5206,6 @@
       <c r="P208" s="11" t="n"/>
       <c r="Q208" s="11" t="n"/>
       <c r="R208" s="11" t="n"/>
-      <c r="S208" s="11" t="n"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="11" t="n"/>
@@ -5487,7 +5226,6 @@
       <c r="P209" s="11" t="n"/>
       <c r="Q209" s="11" t="n"/>
       <c r="R209" s="11" t="n"/>
-      <c r="S209" s="11" t="n"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="11" t="n"/>
@@ -5508,7 +5246,6 @@
       <c r="P210" s="11" t="n"/>
       <c r="Q210" s="11" t="n"/>
       <c r="R210" s="11" t="n"/>
-      <c r="S210" s="11" t="n"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="11" t="n"/>
@@ -5529,7 +5266,6 @@
       <c r="P211" s="11" t="n"/>
       <c r="Q211" s="11" t="n"/>
       <c r="R211" s="11" t="n"/>
-      <c r="S211" s="11" t="n"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="11" t="n"/>
@@ -5550,7 +5286,6 @@
       <c r="P212" s="11" t="n"/>
       <c r="Q212" s="11" t="n"/>
       <c r="R212" s="11" t="n"/>
-      <c r="S212" s="11" t="n"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="11" t="n"/>
@@ -5571,7 +5306,6 @@
       <c r="P213" s="11" t="n"/>
       <c r="Q213" s="11" t="n"/>
       <c r="R213" s="11" t="n"/>
-      <c r="S213" s="11" t="n"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="11" t="n"/>
@@ -5592,7 +5326,6 @@
       <c r="P214" s="11" t="n"/>
       <c r="Q214" s="11" t="n"/>
       <c r="R214" s="11" t="n"/>
-      <c r="S214" s="11" t="n"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="11" t="n"/>
@@ -5613,7 +5346,6 @@
       <c r="P215" s="11" t="n"/>
       <c r="Q215" s="11" t="n"/>
       <c r="R215" s="11" t="n"/>
-      <c r="S215" s="11" t="n"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="11" t="n"/>
@@ -5634,7 +5366,6 @@
       <c r="P216" s="11" t="n"/>
       <c r="Q216" s="11" t="n"/>
       <c r="R216" s="11" t="n"/>
-      <c r="S216" s="11" t="n"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="11" t="n"/>
@@ -5655,7 +5386,6 @@
       <c r="P217" s="11" t="n"/>
       <c r="Q217" s="11" t="n"/>
       <c r="R217" s="11" t="n"/>
-      <c r="S217" s="11" t="n"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="11" t="n"/>
@@ -5676,7 +5406,6 @@
       <c r="P218" s="11" t="n"/>
       <c r="Q218" s="11" t="n"/>
       <c r="R218" s="11" t="n"/>
-      <c r="S218" s="11" t="n"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="11" t="n"/>
@@ -5697,7 +5426,6 @@
       <c r="P219" s="11" t="n"/>
       <c r="Q219" s="11" t="n"/>
       <c r="R219" s="11" t="n"/>
-      <c r="S219" s="11" t="n"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="11" t="n"/>
@@ -5718,7 +5446,6 @@
       <c r="P220" s="11" t="n"/>
       <c r="Q220" s="11" t="n"/>
       <c r="R220" s="11" t="n"/>
-      <c r="S220" s="11" t="n"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="11" t="n"/>
@@ -5739,7 +5466,6 @@
       <c r="P221" s="11" t="n"/>
       <c r="Q221" s="11" t="n"/>
       <c r="R221" s="11" t="n"/>
-      <c r="S221" s="11" t="n"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="11" t="n"/>
@@ -5760,7 +5486,6 @@
       <c r="P222" s="11" t="n"/>
       <c r="Q222" s="11" t="n"/>
       <c r="R222" s="11" t="n"/>
-      <c r="S222" s="11" t="n"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="11" t="n"/>
@@ -5781,7 +5506,6 @@
       <c r="P223" s="11" t="n"/>
       <c r="Q223" s="11" t="n"/>
       <c r="R223" s="11" t="n"/>
-      <c r="S223" s="11" t="n"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="11" t="n"/>
@@ -5802,7 +5526,6 @@
       <c r="P224" s="11" t="n"/>
       <c r="Q224" s="11" t="n"/>
       <c r="R224" s="11" t="n"/>
-      <c r="S224" s="11" t="n"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="11" t="n"/>
@@ -5823,7 +5546,6 @@
       <c r="P225" s="11" t="n"/>
       <c r="Q225" s="11" t="n"/>
       <c r="R225" s="11" t="n"/>
-      <c r="S225" s="11" t="n"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="11" t="n"/>
@@ -5844,7 +5566,6 @@
       <c r="P226" s="11" t="n"/>
       <c r="Q226" s="11" t="n"/>
       <c r="R226" s="11" t="n"/>
-      <c r="S226" s="11" t="n"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="11" t="n"/>
@@ -5865,7 +5586,6 @@
       <c r="P227" s="11" t="n"/>
       <c r="Q227" s="11" t="n"/>
       <c r="R227" s="11" t="n"/>
-      <c r="S227" s="11" t="n"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="11" t="n"/>
@@ -5886,7 +5606,6 @@
       <c r="P228" s="11" t="n"/>
       <c r="Q228" s="11" t="n"/>
       <c r="R228" s="11" t="n"/>
-      <c r="S228" s="11" t="n"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="11" t="n"/>
@@ -5907,7 +5626,6 @@
       <c r="P229" s="11" t="n"/>
       <c r="Q229" s="11" t="n"/>
       <c r="R229" s="11" t="n"/>
-      <c r="S229" s="11" t="n"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="11" t="n"/>
@@ -5928,7 +5646,6 @@
       <c r="P230" s="11" t="n"/>
       <c r="Q230" s="11" t="n"/>
       <c r="R230" s="11" t="n"/>
-      <c r="S230" s="11" t="n"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="11" t="n"/>
@@ -5949,7 +5666,6 @@
       <c r="P231" s="11" t="n"/>
       <c r="Q231" s="11" t="n"/>
       <c r="R231" s="11" t="n"/>
-      <c r="S231" s="11" t="n"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="11" t="n"/>
@@ -5970,7 +5686,6 @@
       <c r="P232" s="11" t="n"/>
       <c r="Q232" s="11" t="n"/>
       <c r="R232" s="11" t="n"/>
-      <c r="S232" s="11" t="n"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="11" t="n"/>
@@ -5991,7 +5706,6 @@
       <c r="P233" s="11" t="n"/>
       <c r="Q233" s="11" t="n"/>
       <c r="R233" s="11" t="n"/>
-      <c r="S233" s="11" t="n"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="11" t="n"/>
@@ -6012,7 +5726,6 @@
       <c r="P234" s="11" t="n"/>
       <c r="Q234" s="11" t="n"/>
       <c r="R234" s="11" t="n"/>
-      <c r="S234" s="11" t="n"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="11" t="n"/>
@@ -6033,7 +5746,6 @@
       <c r="P235" s="11" t="n"/>
       <c r="Q235" s="11" t="n"/>
       <c r="R235" s="11" t="n"/>
-      <c r="S235" s="11" t="n"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="11" t="n"/>
@@ -6054,7 +5766,6 @@
       <c r="P236" s="11" t="n"/>
       <c r="Q236" s="11" t="n"/>
       <c r="R236" s="11" t="n"/>
-      <c r="S236" s="11" t="n"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="11" t="n"/>
@@ -6075,7 +5786,6 @@
       <c r="P237" s="11" t="n"/>
       <c r="Q237" s="11" t="n"/>
       <c r="R237" s="11" t="n"/>
-      <c r="S237" s="11" t="n"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="11" t="n"/>
@@ -6096,7 +5806,6 @@
       <c r="P238" s="11" t="n"/>
       <c r="Q238" s="11" t="n"/>
       <c r="R238" s="11" t="n"/>
-      <c r="S238" s="11" t="n"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="11" t="n"/>
@@ -6117,7 +5826,6 @@
       <c r="P239" s="11" t="n"/>
       <c r="Q239" s="11" t="n"/>
       <c r="R239" s="11" t="n"/>
-      <c r="S239" s="11" t="n"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="11" t="n"/>
@@ -6138,7 +5846,6 @@
       <c r="P240" s="11" t="n"/>
       <c r="Q240" s="11" t="n"/>
       <c r="R240" s="11" t="n"/>
-      <c r="S240" s="11" t="n"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="11" t="n"/>
@@ -6159,7 +5866,6 @@
       <c r="P241" s="11" t="n"/>
       <c r="Q241" s="11" t="n"/>
       <c r="R241" s="11" t="n"/>
-      <c r="S241" s="11" t="n"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="11" t="n"/>
@@ -6180,7 +5886,6 @@
       <c r="P242" s="11" t="n"/>
       <c r="Q242" s="11" t="n"/>
       <c r="R242" s="11" t="n"/>
-      <c r="S242" s="11" t="n"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="11" t="n"/>
@@ -6201,7 +5906,6 @@
       <c r="P243" s="11" t="n"/>
       <c r="Q243" s="11" t="n"/>
       <c r="R243" s="11" t="n"/>
-      <c r="S243" s="11" t="n"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="11" t="n"/>
@@ -6222,7 +5926,6 @@
       <c r="P244" s="11" t="n"/>
       <c r="Q244" s="11" t="n"/>
       <c r="R244" s="11" t="n"/>
-      <c r="S244" s="11" t="n"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="11" t="n"/>
@@ -6243,7 +5946,6 @@
       <c r="P245" s="11" t="n"/>
       <c r="Q245" s="11" t="n"/>
       <c r="R245" s="11" t="n"/>
-      <c r="S245" s="11" t="n"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="11" t="n"/>
@@ -6264,7 +5966,6 @@
       <c r="P246" s="11" t="n"/>
       <c r="Q246" s="11" t="n"/>
       <c r="R246" s="11" t="n"/>
-      <c r="S246" s="11" t="n"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="11" t="n"/>
@@ -6285,7 +5986,6 @@
       <c r="P247" s="11" t="n"/>
       <c r="Q247" s="11" t="n"/>
       <c r="R247" s="11" t="n"/>
-      <c r="S247" s="11" t="n"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="11" t="n"/>
@@ -6306,7 +6006,6 @@
       <c r="P248" s="11" t="n"/>
       <c r="Q248" s="11" t="n"/>
       <c r="R248" s="11" t="n"/>
-      <c r="S248" s="11" t="n"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="11" t="n"/>
@@ -6327,7 +6026,6 @@
       <c r="P249" s="11" t="n"/>
       <c r="Q249" s="11" t="n"/>
       <c r="R249" s="11" t="n"/>
-      <c r="S249" s="11" t="n"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="11" t="n"/>
@@ -6348,7 +6046,6 @@
       <c r="P250" s="11" t="n"/>
       <c r="Q250" s="11" t="n"/>
       <c r="R250" s="11" t="n"/>
-      <c r="S250" s="11" t="n"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="11" t="n"/>
@@ -6369,7 +6066,6 @@
       <c r="P251" s="11" t="n"/>
       <c r="Q251" s="11" t="n"/>
       <c r="R251" s="11" t="n"/>
-      <c r="S251" s="11" t="n"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="11" t="n"/>
@@ -6390,7 +6086,6 @@
       <c r="P252" s="11" t="n"/>
       <c r="Q252" s="11" t="n"/>
       <c r="R252" s="11" t="n"/>
-      <c r="S252" s="11" t="n"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="11" t="n"/>
@@ -6411,7 +6106,6 @@
       <c r="P253" s="11" t="n"/>
       <c r="Q253" s="11" t="n"/>
       <c r="R253" s="11" t="n"/>
-      <c r="S253" s="11" t="n"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="11" t="n"/>
@@ -6432,7 +6126,6 @@
       <c r="P254" s="11" t="n"/>
       <c r="Q254" s="11" t="n"/>
       <c r="R254" s="11" t="n"/>
-      <c r="S254" s="11" t="n"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="11" t="n"/>
@@ -6453,7 +6146,6 @@
       <c r="P255" s="11" t="n"/>
       <c r="Q255" s="11" t="n"/>
       <c r="R255" s="11" t="n"/>
-      <c r="S255" s="11" t="n"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="11" t="n"/>
@@ -6474,7 +6166,6 @@
       <c r="P256" s="11" t="n"/>
       <c r="Q256" s="11" t="n"/>
       <c r="R256" s="11" t="n"/>
-      <c r="S256" s="11" t="n"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="11" t="n"/>
@@ -6495,7 +6186,6 @@
       <c r="P257" s="11" t="n"/>
       <c r="Q257" s="11" t="n"/>
       <c r="R257" s="11" t="n"/>
-      <c r="S257" s="11" t="n"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="11" t="n"/>
@@ -6516,7 +6206,6 @@
       <c r="P258" s="11" t="n"/>
       <c r="Q258" s="11" t="n"/>
       <c r="R258" s="11" t="n"/>
-      <c r="S258" s="11" t="n"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="11" t="n"/>
@@ -6537,7 +6226,6 @@
       <c r="P259" s="11" t="n"/>
       <c r="Q259" s="11" t="n"/>
       <c r="R259" s="11" t="n"/>
-      <c r="S259" s="11" t="n"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="11" t="n"/>
@@ -6558,7 +6246,6 @@
       <c r="P260" s="11" t="n"/>
       <c r="Q260" s="11" t="n"/>
       <c r="R260" s="11" t="n"/>
-      <c r="S260" s="11" t="n"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="11" t="n"/>
@@ -6579,7 +6266,6 @@
       <c r="P261" s="11" t="n"/>
       <c r="Q261" s="11" t="n"/>
       <c r="R261" s="11" t="n"/>
-      <c r="S261" s="11" t="n"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="11" t="n"/>
@@ -6600,7 +6286,6 @@
       <c r="P262" s="11" t="n"/>
       <c r="Q262" s="11" t="n"/>
       <c r="R262" s="11" t="n"/>
-      <c r="S262" s="11" t="n"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="11" t="n"/>
@@ -6621,7 +6306,6 @@
       <c r="P263" s="11" t="n"/>
       <c r="Q263" s="11" t="n"/>
       <c r="R263" s="11" t="n"/>
-      <c r="S263" s="11" t="n"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="11" t="n"/>
@@ -6642,7 +6326,6 @@
       <c r="P264" s="11" t="n"/>
       <c r="Q264" s="11" t="n"/>
       <c r="R264" s="11" t="n"/>
-      <c r="S264" s="11" t="n"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="11" t="n"/>
@@ -6663,7 +6346,6 @@
       <c r="P265" s="11" t="n"/>
       <c r="Q265" s="11" t="n"/>
       <c r="R265" s="11" t="n"/>
-      <c r="S265" s="11" t="n"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="11" t="n"/>
@@ -6684,7 +6366,6 @@
       <c r="P266" s="11" t="n"/>
       <c r="Q266" s="11" t="n"/>
       <c r="R266" s="11" t="n"/>
-      <c r="S266" s="11" t="n"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="11" t="n"/>
@@ -6705,7 +6386,6 @@
       <c r="P267" s="11" t="n"/>
       <c r="Q267" s="11" t="n"/>
       <c r="R267" s="11" t="n"/>
-      <c r="S267" s="11" t="n"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="11" t="n"/>
@@ -6726,7 +6406,6 @@
       <c r="P268" s="11" t="n"/>
       <c r="Q268" s="11" t="n"/>
       <c r="R268" s="11" t="n"/>
-      <c r="S268" s="11" t="n"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="11" t="n"/>
@@ -6747,7 +6426,6 @@
       <c r="P269" s="11" t="n"/>
       <c r="Q269" s="11" t="n"/>
       <c r="R269" s="11" t="n"/>
-      <c r="S269" s="11" t="n"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="11" t="n"/>
@@ -6768,7 +6446,6 @@
       <c r="P270" s="11" t="n"/>
       <c r="Q270" s="11" t="n"/>
       <c r="R270" s="11" t="n"/>
-      <c r="S270" s="11" t="n"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="11" t="n"/>
@@ -6789,7 +6466,6 @@
       <c r="P271" s="11" t="n"/>
       <c r="Q271" s="11" t="n"/>
       <c r="R271" s="11" t="n"/>
-      <c r="S271" s="11" t="n"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="11" t="n"/>
@@ -6810,7 +6486,6 @@
       <c r="P272" s="11" t="n"/>
       <c r="Q272" s="11" t="n"/>
       <c r="R272" s="11" t="n"/>
-      <c r="S272" s="11" t="n"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="11" t="n"/>
@@ -6831,7 +6506,6 @@
       <c r="P273" s="11" t="n"/>
       <c r="Q273" s="11" t="n"/>
       <c r="R273" s="11" t="n"/>
-      <c r="S273" s="11" t="n"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="11" t="n"/>
@@ -6852,7 +6526,6 @@
       <c r="P274" s="11" t="n"/>
       <c r="Q274" s="11" t="n"/>
       <c r="R274" s="11" t="n"/>
-      <c r="S274" s="11" t="n"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="11" t="n"/>
@@ -6873,7 +6546,6 @@
       <c r="P275" s="11" t="n"/>
       <c r="Q275" s="11" t="n"/>
       <c r="R275" s="11" t="n"/>
-      <c r="S275" s="11" t="n"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="11" t="n"/>
@@ -6894,7 +6566,6 @@
       <c r="P276" s="11" t="n"/>
       <c r="Q276" s="11" t="n"/>
       <c r="R276" s="11" t="n"/>
-      <c r="S276" s="11" t="n"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="11" t="n"/>
@@ -6915,7 +6586,6 @@
       <c r="P277" s="11" t="n"/>
       <c r="Q277" s="11" t="n"/>
       <c r="R277" s="11" t="n"/>
-      <c r="S277" s="11" t="n"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="11" t="n"/>
@@ -6936,7 +6606,6 @@
       <c r="P278" s="11" t="n"/>
       <c r="Q278" s="11" t="n"/>
       <c r="R278" s="11" t="n"/>
-      <c r="S278" s="11" t="n"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="11" t="n"/>
@@ -6957,7 +6626,6 @@
       <c r="P279" s="11" t="n"/>
       <c r="Q279" s="11" t="n"/>
       <c r="R279" s="11" t="n"/>
-      <c r="S279" s="11" t="n"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="11" t="n"/>
@@ -6978,7 +6646,6 @@
       <c r="P280" s="11" t="n"/>
       <c r="Q280" s="11" t="n"/>
       <c r="R280" s="11" t="n"/>
-      <c r="S280" s="11" t="n"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="11" t="n"/>
@@ -6999,7 +6666,6 @@
       <c r="P281" s="11" t="n"/>
       <c r="Q281" s="11" t="n"/>
       <c r="R281" s="11" t="n"/>
-      <c r="S281" s="11" t="n"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="11" t="n"/>
@@ -7020,7 +6686,6 @@
       <c r="P282" s="11" t="n"/>
       <c r="Q282" s="11" t="n"/>
       <c r="R282" s="11" t="n"/>
-      <c r="S282" s="11" t="n"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="11" t="n"/>
@@ -7041,7 +6706,6 @@
       <c r="P283" s="11" t="n"/>
       <c r="Q283" s="11" t="n"/>
       <c r="R283" s="11" t="n"/>
-      <c r="S283" s="11" t="n"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="11" t="n"/>
@@ -7062,7 +6726,6 @@
       <c r="P284" s="11" t="n"/>
       <c r="Q284" s="11" t="n"/>
       <c r="R284" s="11" t="n"/>
-      <c r="S284" s="11" t="n"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="11" t="n"/>
@@ -7083,7 +6746,6 @@
       <c r="P285" s="11" t="n"/>
       <c r="Q285" s="11" t="n"/>
       <c r="R285" s="11" t="n"/>
-      <c r="S285" s="11" t="n"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="11" t="n"/>
@@ -7104,7 +6766,6 @@
       <c r="P286" s="11" t="n"/>
       <c r="Q286" s="11" t="n"/>
       <c r="R286" s="11" t="n"/>
-      <c r="S286" s="11" t="n"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="11" t="n"/>
@@ -7125,7 +6786,6 @@
       <c r="P287" s="11" t="n"/>
       <c r="Q287" s="11" t="n"/>
       <c r="R287" s="11" t="n"/>
-      <c r="S287" s="11" t="n"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="11" t="n"/>
@@ -7146,7 +6806,6 @@
       <c r="P288" s="11" t="n"/>
       <c r="Q288" s="11" t="n"/>
       <c r="R288" s="11" t="n"/>
-      <c r="S288" s="11" t="n"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="11" t="n"/>
@@ -7167,7 +6826,6 @@
       <c r="P289" s="11" t="n"/>
       <c r="Q289" s="11" t="n"/>
       <c r="R289" s="11" t="n"/>
-      <c r="S289" s="11" t="n"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="11" t="n"/>
@@ -7188,7 +6846,6 @@
       <c r="P290" s="11" t="n"/>
       <c r="Q290" s="11" t="n"/>
       <c r="R290" s="11" t="n"/>
-      <c r="S290" s="11" t="n"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="11" t="n"/>
@@ -7209,7 +6866,6 @@
       <c r="P291" s="11" t="n"/>
       <c r="Q291" s="11" t="n"/>
       <c r="R291" s="11" t="n"/>
-      <c r="S291" s="11" t="n"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="11" t="n"/>
@@ -7230,7 +6886,6 @@
       <c r="P292" s="11" t="n"/>
       <c r="Q292" s="11" t="n"/>
       <c r="R292" s="11" t="n"/>
-      <c r="S292" s="11" t="n"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="11" t="n"/>
@@ -7251,7 +6906,6 @@
       <c r="P293" s="11" t="n"/>
       <c r="Q293" s="11" t="n"/>
       <c r="R293" s="11" t="n"/>
-      <c r="S293" s="11" t="n"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="11" t="n"/>
@@ -7272,7 +6926,6 @@
       <c r="P294" s="11" t="n"/>
       <c r="Q294" s="11" t="n"/>
       <c r="R294" s="11" t="n"/>
-      <c r="S294" s="11" t="n"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="11" t="n"/>
@@ -7293,7 +6946,6 @@
       <c r="P295" s="11" t="n"/>
       <c r="Q295" s="11" t="n"/>
       <c r="R295" s="11" t="n"/>
-      <c r="S295" s="11" t="n"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="11" t="n"/>
@@ -7314,7 +6966,6 @@
       <c r="P296" s="11" t="n"/>
       <c r="Q296" s="11" t="n"/>
       <c r="R296" s="11" t="n"/>
-      <c r="S296" s="11" t="n"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="11" t="n"/>
@@ -7335,7 +6986,6 @@
       <c r="P297" s="11" t="n"/>
       <c r="Q297" s="11" t="n"/>
       <c r="R297" s="11" t="n"/>
-      <c r="S297" s="11" t="n"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="11" t="n"/>
@@ -7356,7 +7006,6 @@
       <c r="P298" s="11" t="n"/>
       <c r="Q298" s="11" t="n"/>
       <c r="R298" s="11" t="n"/>
-      <c r="S298" s="11" t="n"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="11" t="n"/>
@@ -7377,7 +7026,6 @@
       <c r="P299" s="11" t="n"/>
       <c r="Q299" s="11" t="n"/>
       <c r="R299" s="11" t="n"/>
-      <c r="S299" s="11" t="n"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="11" t="n"/>
@@ -7398,7 +7046,6 @@
       <c r="P300" s="11" t="n"/>
       <c r="Q300" s="11" t="n"/>
       <c r="R300" s="11" t="n"/>
-      <c r="S300" s="11" t="n"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="11" t="n"/>
@@ -7419,7 +7066,6 @@
       <c r="P301" s="11" t="n"/>
       <c r="Q301" s="11" t="n"/>
       <c r="R301" s="11" t="n"/>
-      <c r="S301" s="11" t="n"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="11" t="n"/>
@@ -7440,7 +7086,6 @@
       <c r="P302" s="11" t="n"/>
       <c r="Q302" s="11" t="n"/>
       <c r="R302" s="11" t="n"/>
-      <c r="S302" s="11" t="n"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="11" t="n"/>
@@ -7461,7 +7106,6 @@
       <c r="P303" s="11" t="n"/>
       <c r="Q303" s="11" t="n"/>
       <c r="R303" s="11" t="n"/>
-      <c r="S303" s="11" t="n"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="11" t="n"/>
@@ -7482,7 +7126,6 @@
       <c r="P304" s="11" t="n"/>
       <c r="Q304" s="11" t="n"/>
       <c r="R304" s="11" t="n"/>
-      <c r="S304" s="11" t="n"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="11" t="n"/>
@@ -7503,7 +7146,6 @@
       <c r="P305" s="11" t="n"/>
       <c r="Q305" s="11" t="n"/>
       <c r="R305" s="11" t="n"/>
-      <c r="S305" s="11" t="n"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="11" t="n"/>
@@ -7524,7 +7166,6 @@
       <c r="P306" s="11" t="n"/>
       <c r="Q306" s="11" t="n"/>
       <c r="R306" s="11" t="n"/>
-      <c r="S306" s="11" t="n"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="11" t="n"/>
@@ -7545,7 +7186,6 @@
       <c r="P307" s="11" t="n"/>
       <c r="Q307" s="11" t="n"/>
       <c r="R307" s="11" t="n"/>
-      <c r="S307" s="11" t="n"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="11" t="n"/>
@@ -7566,7 +7206,6 @@
       <c r="P308" s="11" t="n"/>
       <c r="Q308" s="11" t="n"/>
       <c r="R308" s="11" t="n"/>
-      <c r="S308" s="11" t="n"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="11" t="n"/>
@@ -7587,7 +7226,6 @@
       <c r="P309" s="11" t="n"/>
       <c r="Q309" s="11" t="n"/>
       <c r="R309" s="11" t="n"/>
-      <c r="S309" s="11" t="n"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="11" t="n"/>
@@ -7608,7 +7246,6 @@
       <c r="P310" s="11" t="n"/>
       <c r="Q310" s="11" t="n"/>
       <c r="R310" s="11" t="n"/>
-      <c r="S310" s="11" t="n"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="11" t="n"/>
@@ -7629,7 +7266,6 @@
       <c r="P311" s="11" t="n"/>
       <c r="Q311" s="11" t="n"/>
       <c r="R311" s="11" t="n"/>
-      <c r="S311" s="11" t="n"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="11" t="n"/>
@@ -7650,7 +7286,6 @@
       <c r="P312" s="11" t="n"/>
       <c r="Q312" s="11" t="n"/>
       <c r="R312" s="11" t="n"/>
-      <c r="S312" s="11" t="n"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="11" t="n"/>
@@ -7671,7 +7306,6 @@
       <c r="P313" s="11" t="n"/>
       <c r="Q313" s="11" t="n"/>
       <c r="R313" s="11" t="n"/>
-      <c r="S313" s="11" t="n"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="11" t="n"/>
@@ -7692,7 +7326,6 @@
       <c r="P314" s="11" t="n"/>
       <c r="Q314" s="11" t="n"/>
       <c r="R314" s="11" t="n"/>
-      <c r="S314" s="11" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="11" t="n"/>
@@ -7713,7 +7346,6 @@
       <c r="P315" s="11" t="n"/>
       <c r="Q315" s="11" t="n"/>
       <c r="R315" s="11" t="n"/>
-      <c r="S315" s="11" t="n"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="11" t="n"/>
@@ -7734,7 +7366,6 @@
       <c r="P316" s="11" t="n"/>
       <c r="Q316" s="11" t="n"/>
       <c r="R316" s="11" t="n"/>
-      <c r="S316" s="11" t="n"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="11" t="n"/>
@@ -7755,7 +7386,6 @@
       <c r="P317" s="11" t="n"/>
       <c r="Q317" s="11" t="n"/>
       <c r="R317" s="11" t="n"/>
-      <c r="S317" s="11" t="n"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="11" t="n"/>
@@ -7776,7 +7406,6 @@
       <c r="P318" s="11" t="n"/>
       <c r="Q318" s="11" t="n"/>
       <c r="R318" s="11" t="n"/>
-      <c r="S318" s="11" t="n"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="11" t="n"/>
@@ -7797,7 +7426,6 @@
       <c r="P319" s="11" t="n"/>
       <c r="Q319" s="11" t="n"/>
       <c r="R319" s="11" t="n"/>
-      <c r="S319" s="11" t="n"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="11" t="n"/>
@@ -7818,7 +7446,6 @@
       <c r="P320" s="11" t="n"/>
       <c r="Q320" s="11" t="n"/>
       <c r="R320" s="11" t="n"/>
-      <c r="S320" s="11" t="n"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="11" t="n"/>
@@ -7839,7 +7466,6 @@
       <c r="P321" s="11" t="n"/>
       <c r="Q321" s="11" t="n"/>
       <c r="R321" s="11" t="n"/>
-      <c r="S321" s="11" t="n"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="11" t="n"/>
@@ -7860,7 +7486,6 @@
       <c r="P322" s="11" t="n"/>
       <c r="Q322" s="11" t="n"/>
       <c r="R322" s="11" t="n"/>
-      <c r="S322" s="11" t="n"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="11" t="n"/>
@@ -7881,7 +7506,6 @@
       <c r="P323" s="11" t="n"/>
       <c r="Q323" s="11" t="n"/>
       <c r="R323" s="11" t="n"/>
-      <c r="S323" s="11" t="n"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="11" t="n"/>
@@ -7902,7 +7526,6 @@
       <c r="P324" s="11" t="n"/>
       <c r="Q324" s="11" t="n"/>
       <c r="R324" s="11" t="n"/>
-      <c r="S324" s="11" t="n"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="11" t="n"/>
@@ -7923,7 +7546,6 @@
       <c r="P325" s="11" t="n"/>
       <c r="Q325" s="11" t="n"/>
       <c r="R325" s="11" t="n"/>
-      <c r="S325" s="11" t="n"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="11" t="n"/>
@@ -7944,7 +7566,6 @@
       <c r="P326" s="11" t="n"/>
       <c r="Q326" s="11" t="n"/>
       <c r="R326" s="11" t="n"/>
-      <c r="S326" s="11" t="n"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="11" t="n"/>
@@ -7965,7 +7586,6 @@
       <c r="P327" s="11" t="n"/>
       <c r="Q327" s="11" t="n"/>
       <c r="R327" s="11" t="n"/>
-      <c r="S327" s="11" t="n"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="11" t="n"/>
@@ -7986,7 +7606,6 @@
       <c r="P328" s="11" t="n"/>
       <c r="Q328" s="11" t="n"/>
       <c r="R328" s="11" t="n"/>
-      <c r="S328" s="11" t="n"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="11" t="n"/>
@@ -8007,7 +7626,6 @@
       <c r="P329" s="11" t="n"/>
       <c r="Q329" s="11" t="n"/>
       <c r="R329" s="11" t="n"/>
-      <c r="S329" s="11" t="n"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="11" t="n"/>
@@ -8028,7 +7646,6 @@
       <c r="P330" s="11" t="n"/>
       <c r="Q330" s="11" t="n"/>
       <c r="R330" s="11" t="n"/>
-      <c r="S330" s="11" t="n"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="11" t="n"/>
@@ -8049,7 +7666,6 @@
       <c r="P331" s="11" t="n"/>
       <c r="Q331" s="11" t="n"/>
       <c r="R331" s="11" t="n"/>
-      <c r="S331" s="11" t="n"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="11" t="n"/>
@@ -8070,7 +7686,6 @@
       <c r="P332" s="11" t="n"/>
       <c r="Q332" s="11" t="n"/>
       <c r="R332" s="11" t="n"/>
-      <c r="S332" s="11" t="n"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="11" t="n"/>
@@ -8091,7 +7706,6 @@
       <c r="P333" s="11" t="n"/>
       <c r="Q333" s="11" t="n"/>
       <c r="R333" s="11" t="n"/>
-      <c r="S333" s="11" t="n"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="11" t="n"/>
@@ -8112,7 +7726,6 @@
       <c r="P334" s="11" t="n"/>
       <c r="Q334" s="11" t="n"/>
       <c r="R334" s="11" t="n"/>
-      <c r="S334" s="11" t="n"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="11" t="n"/>
@@ -8133,7 +7746,6 @@
       <c r="P335" s="11" t="n"/>
       <c r="Q335" s="11" t="n"/>
       <c r="R335" s="11" t="n"/>
-      <c r="S335" s="11" t="n"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="11" t="n"/>
@@ -8154,7 +7766,6 @@
       <c r="P336" s="11" t="n"/>
       <c r="Q336" s="11" t="n"/>
       <c r="R336" s="11" t="n"/>
-      <c r="S336" s="11" t="n"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="11" t="n"/>
@@ -8175,7 +7786,6 @@
       <c r="P337" s="11" t="n"/>
       <c r="Q337" s="11" t="n"/>
       <c r="R337" s="11" t="n"/>
-      <c r="S337" s="11" t="n"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="11" t="n"/>
@@ -8196,7 +7806,6 @@
       <c r="P338" s="11" t="n"/>
       <c r="Q338" s="11" t="n"/>
       <c r="R338" s="11" t="n"/>
-      <c r="S338" s="11" t="n"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="11" t="n"/>
@@ -8217,7 +7826,6 @@
       <c r="P339" s="11" t="n"/>
       <c r="Q339" s="11" t="n"/>
       <c r="R339" s="11" t="n"/>
-      <c r="S339" s="11" t="n"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="11" t="n"/>
@@ -8238,7 +7846,6 @@
       <c r="P340" s="11" t="n"/>
       <c r="Q340" s="11" t="n"/>
       <c r="R340" s="11" t="n"/>
-      <c r="S340" s="11" t="n"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="11" t="n"/>
@@ -8259,7 +7866,6 @@
       <c r="P341" s="11" t="n"/>
       <c r="Q341" s="11" t="n"/>
       <c r="R341" s="11" t="n"/>
-      <c r="S341" s="11" t="n"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="11" t="n"/>
@@ -8280,7 +7886,6 @@
       <c r="P342" s="11" t="n"/>
       <c r="Q342" s="11" t="n"/>
       <c r="R342" s="11" t="n"/>
-      <c r="S342" s="11" t="n"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="11" t="n"/>
@@ -8301,7 +7906,6 @@
       <c r="P343" s="11" t="n"/>
       <c r="Q343" s="11" t="n"/>
       <c r="R343" s="11" t="n"/>
-      <c r="S343" s="11" t="n"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="11" t="n"/>
@@ -8322,7 +7926,6 @@
       <c r="P344" s="11" t="n"/>
       <c r="Q344" s="11" t="n"/>
       <c r="R344" s="11" t="n"/>
-      <c r="S344" s="11" t="n"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="11" t="n"/>
@@ -8343,7 +7946,6 @@
       <c r="P345" s="11" t="n"/>
       <c r="Q345" s="11" t="n"/>
       <c r="R345" s="11" t="n"/>
-      <c r="S345" s="11" t="n"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="11" t="n"/>
@@ -8364,7 +7966,6 @@
       <c r="P346" s="11" t="n"/>
       <c r="Q346" s="11" t="n"/>
       <c r="R346" s="11" t="n"/>
-      <c r="S346" s="11" t="n"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="11" t="n"/>
@@ -8385,7 +7986,6 @@
       <c r="P347" s="11" t="n"/>
       <c r="Q347" s="11" t="n"/>
       <c r="R347" s="11" t="n"/>
-      <c r="S347" s="11" t="n"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="11" t="n"/>
@@ -8406,7 +8006,6 @@
       <c r="P348" s="11" t="n"/>
       <c r="Q348" s="11" t="n"/>
       <c r="R348" s="11" t="n"/>
-      <c r="S348" s="11" t="n"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="11" t="n"/>
@@ -8427,7 +8026,6 @@
       <c r="P349" s="11" t="n"/>
       <c r="Q349" s="11" t="n"/>
       <c r="R349" s="11" t="n"/>
-      <c r="S349" s="11" t="n"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="11" t="n"/>
@@ -8448,7 +8046,6 @@
       <c r="P350" s="11" t="n"/>
       <c r="Q350" s="11" t="n"/>
       <c r="R350" s="11" t="n"/>
-      <c r="S350" s="11" t="n"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="11" t="n"/>
@@ -8469,7 +8066,6 @@
       <c r="P351" s="11" t="n"/>
       <c r="Q351" s="11" t="n"/>
       <c r="R351" s="11" t="n"/>
-      <c r="S351" s="11" t="n"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="11" t="n"/>
@@ -8490,7 +8086,6 @@
       <c r="P352" s="11" t="n"/>
       <c r="Q352" s="11" t="n"/>
       <c r="R352" s="11" t="n"/>
-      <c r="S352" s="11" t="n"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="11" t="n"/>
@@ -8511,7 +8106,6 @@
       <c r="P353" s="11" t="n"/>
       <c r="Q353" s="11" t="n"/>
       <c r="R353" s="11" t="n"/>
-      <c r="S353" s="11" t="n"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="11" t="n"/>
@@ -8532,7 +8126,6 @@
       <c r="P354" s="11" t="n"/>
       <c r="Q354" s="11" t="n"/>
       <c r="R354" s="11" t="n"/>
-      <c r="S354" s="11" t="n"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="11" t="n"/>
@@ -8553,7 +8146,6 @@
       <c r="P355" s="11" t="n"/>
       <c r="Q355" s="11" t="n"/>
       <c r="R355" s="11" t="n"/>
-      <c r="S355" s="11" t="n"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="11" t="n"/>
@@ -8574,7 +8166,6 @@
       <c r="P356" s="11" t="n"/>
       <c r="Q356" s="11" t="n"/>
       <c r="R356" s="11" t="n"/>
-      <c r="S356" s="11" t="n"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="11" t="n"/>
@@ -8595,7 +8186,6 @@
       <c r="P357" s="11" t="n"/>
       <c r="Q357" s="11" t="n"/>
       <c r="R357" s="11" t="n"/>
-      <c r="S357" s="11" t="n"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="11" t="n"/>
@@ -8616,7 +8206,6 @@
       <c r="P358" s="11" t="n"/>
       <c r="Q358" s="11" t="n"/>
       <c r="R358" s="11" t="n"/>
-      <c r="S358" s="11" t="n"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="11" t="n"/>
@@ -8637,7 +8226,6 @@
       <c r="P359" s="11" t="n"/>
       <c r="Q359" s="11" t="n"/>
       <c r="R359" s="11" t="n"/>
-      <c r="S359" s="11" t="n"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="11" t="n"/>
@@ -8658,7 +8246,6 @@
       <c r="P360" s="11" t="n"/>
       <c r="Q360" s="11" t="n"/>
       <c r="R360" s="11" t="n"/>
-      <c r="S360" s="11" t="n"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="11" t="n"/>
@@ -8679,7 +8266,6 @@
       <c r="P361" s="11" t="n"/>
       <c r="Q361" s="11" t="n"/>
       <c r="R361" s="11" t="n"/>
-      <c r="S361" s="11" t="n"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="11" t="n"/>
@@ -8700,7 +8286,6 @@
       <c r="P362" s="11" t="n"/>
       <c r="Q362" s="11" t="n"/>
       <c r="R362" s="11" t="n"/>
-      <c r="S362" s="11" t="n"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="11" t="n"/>
@@ -8721,7 +8306,6 @@
       <c r="P363" s="11" t="n"/>
       <c r="Q363" s="11" t="n"/>
       <c r="R363" s="11" t="n"/>
-      <c r="S363" s="11" t="n"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="11" t="n"/>
@@ -8742,7 +8326,6 @@
       <c r="P364" s="11" t="n"/>
       <c r="Q364" s="11" t="n"/>
       <c r="R364" s="11" t="n"/>
-      <c r="S364" s="11" t="n"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="11" t="n"/>
@@ -8763,7 +8346,6 @@
       <c r="P365" s="11" t="n"/>
       <c r="Q365" s="11" t="n"/>
       <c r="R365" s="11" t="n"/>
-      <c r="S365" s="11" t="n"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="11" t="n"/>
@@ -8784,7 +8366,6 @@
       <c r="P366" s="11" t="n"/>
       <c r="Q366" s="11" t="n"/>
       <c r="R366" s="11" t="n"/>
-      <c r="S366" s="11" t="n"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="11" t="n"/>
@@ -8805,7 +8386,6 @@
       <c r="P367" s="11" t="n"/>
       <c r="Q367" s="11" t="n"/>
       <c r="R367" s="11" t="n"/>
-      <c r="S367" s="11" t="n"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="11" t="n"/>
@@ -8826,7 +8406,6 @@
       <c r="P368" s="11" t="n"/>
       <c r="Q368" s="11" t="n"/>
       <c r="R368" s="11" t="n"/>
-      <c r="S368" s="11" t="n"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="11" t="n"/>
@@ -8847,7 +8426,6 @@
       <c r="P369" s="11" t="n"/>
       <c r="Q369" s="11" t="n"/>
       <c r="R369" s="11" t="n"/>
-      <c r="S369" s="11" t="n"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="11" t="n"/>
@@ -8868,7 +8446,6 @@
       <c r="P370" s="11" t="n"/>
       <c r="Q370" s="11" t="n"/>
       <c r="R370" s="11" t="n"/>
-      <c r="S370" s="11" t="n"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="11" t="n"/>
@@ -8889,7 +8466,6 @@
       <c r="P371" s="11" t="n"/>
       <c r="Q371" s="11" t="n"/>
       <c r="R371" s="11" t="n"/>
-      <c r="S371" s="11" t="n"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="11" t="n"/>
@@ -8910,7 +8486,6 @@
       <c r="P372" s="11" t="n"/>
       <c r="Q372" s="11" t="n"/>
       <c r="R372" s="11" t="n"/>
-      <c r="S372" s="11" t="n"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="11" t="n"/>
@@ -8931,7 +8506,6 @@
       <c r="P373" s="11" t="n"/>
       <c r="Q373" s="11" t="n"/>
       <c r="R373" s="11" t="n"/>
-      <c r="S373" s="11" t="n"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="11" t="n"/>
@@ -8952,7 +8526,6 @@
       <c r="P374" s="11" t="n"/>
       <c r="Q374" s="11" t="n"/>
       <c r="R374" s="11" t="n"/>
-      <c r="S374" s="11" t="n"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="11" t="n"/>
@@ -8973,7 +8546,6 @@
       <c r="P375" s="11" t="n"/>
       <c r="Q375" s="11" t="n"/>
       <c r="R375" s="11" t="n"/>
-      <c r="S375" s="11" t="n"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="11" t="n"/>
@@ -8994,7 +8566,6 @@
       <c r="P376" s="11" t="n"/>
       <c r="Q376" s="11" t="n"/>
       <c r="R376" s="11" t="n"/>
-      <c r="S376" s="11" t="n"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="11" t="n"/>
@@ -9015,7 +8586,6 @@
       <c r="P377" s="11" t="n"/>
       <c r="Q377" s="11" t="n"/>
       <c r="R377" s="11" t="n"/>
-      <c r="S377" s="11" t="n"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="11" t="n"/>
@@ -9036,7 +8606,6 @@
       <c r="P378" s="11" t="n"/>
       <c r="Q378" s="11" t="n"/>
       <c r="R378" s="11" t="n"/>
-      <c r="S378" s="11" t="n"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="11" t="n"/>
@@ -9057,7 +8626,6 @@
       <c r="P379" s="11" t="n"/>
       <c r="Q379" s="11" t="n"/>
       <c r="R379" s="11" t="n"/>
-      <c r="S379" s="11" t="n"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="11" t="n"/>
@@ -9078,7 +8646,6 @@
       <c r="P380" s="11" t="n"/>
       <c r="Q380" s="11" t="n"/>
       <c r="R380" s="11" t="n"/>
-      <c r="S380" s="11" t="n"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="11" t="n"/>
@@ -9099,7 +8666,6 @@
       <c r="P381" s="11" t="n"/>
       <c r="Q381" s="11" t="n"/>
       <c r="R381" s="11" t="n"/>
-      <c r="S381" s="11" t="n"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="11" t="n"/>
@@ -9120,7 +8686,6 @@
       <c r="P382" s="11" t="n"/>
       <c r="Q382" s="11" t="n"/>
       <c r="R382" s="11" t="n"/>
-      <c r="S382" s="11" t="n"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="11" t="n"/>
@@ -9141,7 +8706,6 @@
       <c r="P383" s="11" t="n"/>
       <c r="Q383" s="11" t="n"/>
       <c r="R383" s="11" t="n"/>
-      <c r="S383" s="11" t="n"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="11" t="n"/>
@@ -9162,7 +8726,6 @@
       <c r="P384" s="11" t="n"/>
       <c r="Q384" s="11" t="n"/>
       <c r="R384" s="11" t="n"/>
-      <c r="S384" s="11" t="n"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="11" t="n"/>
@@ -9183,7 +8746,6 @@
       <c r="P385" s="11" t="n"/>
       <c r="Q385" s="11" t="n"/>
       <c r="R385" s="11" t="n"/>
-      <c r="S385" s="11" t="n"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="11" t="n"/>
@@ -9204,7 +8766,6 @@
       <c r="P386" s="11" t="n"/>
       <c r="Q386" s="11" t="n"/>
       <c r="R386" s="11" t="n"/>
-      <c r="S386" s="11" t="n"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="11" t="n"/>
@@ -9225,7 +8786,6 @@
       <c r="P387" s="11" t="n"/>
       <c r="Q387" s="11" t="n"/>
       <c r="R387" s="11" t="n"/>
-      <c r="S387" s="11" t="n"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="11" t="n"/>
@@ -9246,7 +8806,6 @@
       <c r="P388" s="11" t="n"/>
       <c r="Q388" s="11" t="n"/>
       <c r="R388" s="11" t="n"/>
-      <c r="S388" s="11" t="n"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="11" t="n"/>
@@ -9267,7 +8826,6 @@
       <c r="P389" s="11" t="n"/>
       <c r="Q389" s="11" t="n"/>
       <c r="R389" s="11" t="n"/>
-      <c r="S389" s="11" t="n"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="11" t="n"/>
@@ -9288,7 +8846,6 @@
       <c r="P390" s="11" t="n"/>
       <c r="Q390" s="11" t="n"/>
       <c r="R390" s="11" t="n"/>
-      <c r="S390" s="11" t="n"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="11" t="n"/>
@@ -9309,7 +8866,6 @@
       <c r="P391" s="11" t="n"/>
       <c r="Q391" s="11" t="n"/>
       <c r="R391" s="11" t="n"/>
-      <c r="S391" s="11" t="n"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="11" t="n"/>
@@ -9330,7 +8886,6 @@
       <c r="P392" s="11" t="n"/>
       <c r="Q392" s="11" t="n"/>
       <c r="R392" s="11" t="n"/>
-      <c r="S392" s="11" t="n"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="11" t="n"/>
@@ -9351,7 +8906,6 @@
       <c r="P393" s="11" t="n"/>
       <c r="Q393" s="11" t="n"/>
       <c r="R393" s="11" t="n"/>
-      <c r="S393" s="11" t="n"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="11" t="n"/>
@@ -9372,7 +8926,6 @@
       <c r="P394" s="11" t="n"/>
       <c r="Q394" s="11" t="n"/>
       <c r="R394" s="11" t="n"/>
-      <c r="S394" s="11" t="n"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="11" t="n"/>
@@ -9393,7 +8946,6 @@
       <c r="P395" s="11" t="n"/>
       <c r="Q395" s="11" t="n"/>
       <c r="R395" s="11" t="n"/>
-      <c r="S395" s="11" t="n"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="11" t="n"/>
@@ -9414,7 +8966,6 @@
       <c r="P396" s="11" t="n"/>
       <c r="Q396" s="11" t="n"/>
       <c r="R396" s="11" t="n"/>
-      <c r="S396" s="11" t="n"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="11" t="n"/>
@@ -9435,7 +8986,6 @@
       <c r="P397" s="11" t="n"/>
       <c r="Q397" s="11" t="n"/>
       <c r="R397" s="11" t="n"/>
-      <c r="S397" s="11" t="n"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="11" t="n"/>
@@ -9456,7 +9006,6 @@
       <c r="P398" s="11" t="n"/>
       <c r="Q398" s="11" t="n"/>
       <c r="R398" s="11" t="n"/>
-      <c r="S398" s="11" t="n"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="11" t="n"/>
@@ -9477,7 +9026,6 @@
       <c r="P399" s="11" t="n"/>
       <c r="Q399" s="11" t="n"/>
       <c r="R399" s="11" t="n"/>
-      <c r="S399" s="11" t="n"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="11" t="n"/>
@@ -9498,7 +9046,6 @@
       <c r="P400" s="11" t="n"/>
       <c r="Q400" s="11" t="n"/>
       <c r="R400" s="11" t="n"/>
-      <c r="S400" s="11" t="n"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="11" t="n"/>
@@ -9519,7 +9066,6 @@
       <c r="P401" s="11" t="n"/>
       <c r="Q401" s="11" t="n"/>
       <c r="R401" s="11" t="n"/>
-      <c r="S401" s="11" t="n"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="11" t="n"/>
@@ -9540,7 +9086,6 @@
       <c r="P402" s="11" t="n"/>
       <c r="Q402" s="11" t="n"/>
       <c r="R402" s="11" t="n"/>
-      <c r="S402" s="11" t="n"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="11" t="n"/>
@@ -9561,7 +9106,6 @@
       <c r="P403" s="11" t="n"/>
       <c r="Q403" s="11" t="n"/>
       <c r="R403" s="11" t="n"/>
-      <c r="S403" s="11" t="n"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="11" t="n"/>
@@ -9582,7 +9126,6 @@
       <c r="P404" s="11" t="n"/>
       <c r="Q404" s="11" t="n"/>
       <c r="R404" s="11" t="n"/>
-      <c r="S404" s="11" t="n"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="11" t="n"/>
@@ -9603,7 +9146,6 @@
       <c r="P405" s="11" t="n"/>
       <c r="Q405" s="11" t="n"/>
       <c r="R405" s="11" t="n"/>
-      <c r="S405" s="11" t="n"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="11" t="n"/>
@@ -9624,7 +9166,6 @@
       <c r="P406" s="11" t="n"/>
       <c r="Q406" s="11" t="n"/>
       <c r="R406" s="11" t="n"/>
-      <c r="S406" s="11" t="n"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="11" t="n"/>
@@ -9645,7 +9186,6 @@
       <c r="P407" s="11" t="n"/>
       <c r="Q407" s="11" t="n"/>
       <c r="R407" s="11" t="n"/>
-      <c r="S407" s="11" t="n"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="11" t="n"/>
@@ -9666,7 +9206,6 @@
       <c r="P408" s="11" t="n"/>
       <c r="Q408" s="11" t="n"/>
       <c r="R408" s="11" t="n"/>
-      <c r="S408" s="11" t="n"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="11" t="n"/>
@@ -9687,7 +9226,6 @@
       <c r="P409" s="11" t="n"/>
       <c r="Q409" s="11" t="n"/>
       <c r="R409" s="11" t="n"/>
-      <c r="S409" s="11" t="n"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="11" t="n"/>
@@ -9708,7 +9246,6 @@
       <c r="P410" s="11" t="n"/>
       <c r="Q410" s="11" t="n"/>
       <c r="R410" s="11" t="n"/>
-      <c r="S410" s="11" t="n"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="11" t="n"/>
@@ -9729,7 +9266,6 @@
       <c r="P411" s="11" t="n"/>
       <c r="Q411" s="11" t="n"/>
       <c r="R411" s="11" t="n"/>
-      <c r="S411" s="11" t="n"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="11" t="n"/>
@@ -9750,7 +9286,6 @@
       <c r="P412" s="11" t="n"/>
       <c r="Q412" s="11" t="n"/>
       <c r="R412" s="11" t="n"/>
-      <c r="S412" s="11" t="n"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="11" t="n"/>
@@ -9771,7 +9306,6 @@
       <c r="P413" s="11" t="n"/>
       <c r="Q413" s="11" t="n"/>
       <c r="R413" s="11" t="n"/>
-      <c r="S413" s="11" t="n"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="11" t="n"/>
@@ -9792,7 +9326,6 @@
       <c r="P414" s="11" t="n"/>
       <c r="Q414" s="11" t="n"/>
       <c r="R414" s="11" t="n"/>
-      <c r="S414" s="11" t="n"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="11" t="n"/>
@@ -9813,7 +9346,6 @@
       <c r="P415" s="11" t="n"/>
       <c r="Q415" s="11" t="n"/>
       <c r="R415" s="11" t="n"/>
-      <c r="S415" s="11" t="n"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="11" t="n"/>
@@ -9834,7 +9366,6 @@
       <c r="P416" s="11" t="n"/>
       <c r="Q416" s="11" t="n"/>
       <c r="R416" s="11" t="n"/>
-      <c r="S416" s="11" t="n"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="11" t="n"/>
@@ -9855,7 +9386,6 @@
       <c r="P417" s="11" t="n"/>
       <c r="Q417" s="11" t="n"/>
       <c r="R417" s="11" t="n"/>
-      <c r="S417" s="11" t="n"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="11" t="n"/>
@@ -9876,7 +9406,6 @@
       <c r="P418" s="11" t="n"/>
       <c r="Q418" s="11" t="n"/>
       <c r="R418" s="11" t="n"/>
-      <c r="S418" s="11" t="n"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="11" t="n"/>
@@ -9897,7 +9426,6 @@
       <c r="P419" s="11" t="n"/>
       <c r="Q419" s="11" t="n"/>
       <c r="R419" s="11" t="n"/>
-      <c r="S419" s="11" t="n"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="11" t="n"/>
@@ -9918,7 +9446,6 @@
       <c r="P420" s="11" t="n"/>
       <c r="Q420" s="11" t="n"/>
       <c r="R420" s="11" t="n"/>
-      <c r="S420" s="11" t="n"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="11" t="n"/>
@@ -9939,7 +9466,6 @@
       <c r="P421" s="11" t="n"/>
       <c r="Q421" s="11" t="n"/>
       <c r="R421" s="11" t="n"/>
-      <c r="S421" s="11" t="n"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="11" t="n"/>
@@ -9960,7 +9486,6 @@
       <c r="P422" s="11" t="n"/>
       <c r="Q422" s="11" t="n"/>
       <c r="R422" s="11" t="n"/>
-      <c r="S422" s="11" t="n"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="11" t="n"/>
@@ -9981,7 +9506,6 @@
       <c r="P423" s="11" t="n"/>
       <c r="Q423" s="11" t="n"/>
       <c r="R423" s="11" t="n"/>
-      <c r="S423" s="11" t="n"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="11" t="n"/>
@@ -10002,7 +9526,6 @@
       <c r="P424" s="11" t="n"/>
       <c r="Q424" s="11" t="n"/>
       <c r="R424" s="11" t="n"/>
-      <c r="S424" s="11" t="n"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="11" t="n"/>
@@ -10023,7 +9546,6 @@
       <c r="P425" s="11" t="n"/>
       <c r="Q425" s="11" t="n"/>
       <c r="R425" s="11" t="n"/>
-      <c r="S425" s="11" t="n"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="11" t="n"/>
@@ -10044,7 +9566,6 @@
       <c r="P426" s="11" t="n"/>
       <c r="Q426" s="11" t="n"/>
       <c r="R426" s="11" t="n"/>
-      <c r="S426" s="11" t="n"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="11" t="n"/>
@@ -10065,7 +9586,6 @@
       <c r="P427" s="11" t="n"/>
       <c r="Q427" s="11" t="n"/>
       <c r="R427" s="11" t="n"/>
-      <c r="S427" s="11" t="n"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="11" t="n"/>
@@ -10086,7 +9606,6 @@
       <c r="P428" s="11" t="n"/>
       <c r="Q428" s="11" t="n"/>
       <c r="R428" s="11" t="n"/>
-      <c r="S428" s="11" t="n"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="11" t="n"/>
@@ -10107,7 +9626,6 @@
       <c r="P429" s="11" t="n"/>
       <c r="Q429" s="11" t="n"/>
       <c r="R429" s="11" t="n"/>
-      <c r="S429" s="11" t="n"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="11" t="n"/>
@@ -10128,7 +9646,6 @@
       <c r="P430" s="11" t="n"/>
       <c r="Q430" s="11" t="n"/>
       <c r="R430" s="11" t="n"/>
-      <c r="S430" s="11" t="n"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="11" t="n"/>
@@ -10149,7 +9666,6 @@
       <c r="P431" s="11" t="n"/>
       <c r="Q431" s="11" t="n"/>
       <c r="R431" s="11" t="n"/>
-      <c r="S431" s="11" t="n"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="11" t="n"/>
@@ -10170,7 +9686,6 @@
       <c r="P432" s="11" t="n"/>
       <c r="Q432" s="11" t="n"/>
       <c r="R432" s="11" t="n"/>
-      <c r="S432" s="11" t="n"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="11" t="n"/>
@@ -10191,7 +9706,6 @@
       <c r="P433" s="11" t="n"/>
       <c r="Q433" s="11" t="n"/>
       <c r="R433" s="11" t="n"/>
-      <c r="S433" s="11" t="n"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="11" t="n"/>
@@ -10212,7 +9726,6 @@
       <c r="P434" s="11" t="n"/>
       <c r="Q434" s="11" t="n"/>
       <c r="R434" s="11" t="n"/>
-      <c r="S434" s="11" t="n"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="11" t="n"/>
@@ -10233,7 +9746,6 @@
       <c r="P435" s="11" t="n"/>
       <c r="Q435" s="11" t="n"/>
       <c r="R435" s="11" t="n"/>
-      <c r="S435" s="11" t="n"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="11" t="n"/>
@@ -10254,7 +9766,6 @@
       <c r="P436" s="11" t="n"/>
       <c r="Q436" s="11" t="n"/>
       <c r="R436" s="11" t="n"/>
-      <c r="S436" s="11" t="n"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="11" t="n"/>
@@ -10275,7 +9786,6 @@
       <c r="P437" s="11" t="n"/>
       <c r="Q437" s="11" t="n"/>
       <c r="R437" s="11" t="n"/>
-      <c r="S437" s="11" t="n"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="11" t="n"/>
@@ -10296,7 +9806,6 @@
       <c r="P438" s="11" t="n"/>
       <c r="Q438" s="11" t="n"/>
       <c r="R438" s="11" t="n"/>
-      <c r="S438" s="11" t="n"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="11" t="n"/>
@@ -10317,7 +9826,6 @@
       <c r="P439" s="11" t="n"/>
       <c r="Q439" s="11" t="n"/>
       <c r="R439" s="11" t="n"/>
-      <c r="S439" s="11" t="n"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="11" t="n"/>
@@ -10338,7 +9846,6 @@
       <c r="P440" s="11" t="n"/>
       <c r="Q440" s="11" t="n"/>
       <c r="R440" s="11" t="n"/>
-      <c r="S440" s="11" t="n"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="11" t="n"/>
@@ -10359,7 +9866,6 @@
       <c r="P441" s="11" t="n"/>
       <c r="Q441" s="11" t="n"/>
       <c r="R441" s="11" t="n"/>
-      <c r="S441" s="11" t="n"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="11" t="n"/>
@@ -10380,7 +9886,6 @@
       <c r="P442" s="11" t="n"/>
       <c r="Q442" s="11" t="n"/>
       <c r="R442" s="11" t="n"/>
-      <c r="S442" s="11" t="n"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="11" t="n"/>
@@ -10401,7 +9906,6 @@
       <c r="P443" s="11" t="n"/>
       <c r="Q443" s="11" t="n"/>
       <c r="R443" s="11" t="n"/>
-      <c r="S443" s="11" t="n"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="11" t="n"/>
@@ -10422,7 +9926,6 @@
       <c r="P444" s="11" t="n"/>
       <c r="Q444" s="11" t="n"/>
       <c r="R444" s="11" t="n"/>
-      <c r="S444" s="11" t="n"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="11" t="n"/>
@@ -10443,7 +9946,6 @@
       <c r="P445" s="11" t="n"/>
       <c r="Q445" s="11" t="n"/>
       <c r="R445" s="11" t="n"/>
-      <c r="S445" s="11" t="n"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="11" t="n"/>
@@ -10464,7 +9966,6 @@
       <c r="P446" s="11" t="n"/>
       <c r="Q446" s="11" t="n"/>
       <c r="R446" s="11" t="n"/>
-      <c r="S446" s="11" t="n"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="11" t="n"/>
@@ -10485,7 +9986,6 @@
       <c r="P447" s="11" t="n"/>
       <c r="Q447" s="11" t="n"/>
       <c r="R447" s="11" t="n"/>
-      <c r="S447" s="11" t="n"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="11" t="n"/>
@@ -10506,7 +10006,6 @@
       <c r="P448" s="11" t="n"/>
       <c r="Q448" s="11" t="n"/>
       <c r="R448" s="11" t="n"/>
-      <c r="S448" s="11" t="n"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="11" t="n"/>
@@ -10527,7 +10026,6 @@
       <c r="P449" s="11" t="n"/>
       <c r="Q449" s="11" t="n"/>
       <c r="R449" s="11" t="n"/>
-      <c r="S449" s="11" t="n"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="11" t="n"/>
@@ -10548,7 +10046,6 @@
       <c r="P450" s="11" t="n"/>
       <c r="Q450" s="11" t="n"/>
       <c r="R450" s="11" t="n"/>
-      <c r="S450" s="11" t="n"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="11" t="n"/>
@@ -10569,7 +10066,6 @@
       <c r="P451" s="11" t="n"/>
       <c r="Q451" s="11" t="n"/>
       <c r="R451" s="11" t="n"/>
-      <c r="S451" s="11" t="n"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="11" t="n"/>
@@ -10590,7 +10086,6 @@
       <c r="P452" s="11" t="n"/>
       <c r="Q452" s="11" t="n"/>
       <c r="R452" s="11" t="n"/>
-      <c r="S452" s="11" t="n"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="11" t="n"/>
@@ -10611,7 +10106,6 @@
       <c r="P453" s="11" t="n"/>
       <c r="Q453" s="11" t="n"/>
       <c r="R453" s="11" t="n"/>
-      <c r="S453" s="11" t="n"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="11" t="n"/>
@@ -10632,7 +10126,6 @@
       <c r="P454" s="11" t="n"/>
       <c r="Q454" s="11" t="n"/>
       <c r="R454" s="11" t="n"/>
-      <c r="S454" s="11" t="n"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="11" t="n"/>
@@ -10653,7 +10146,6 @@
       <c r="P455" s="11" t="n"/>
       <c r="Q455" s="11" t="n"/>
       <c r="R455" s="11" t="n"/>
-      <c r="S455" s="11" t="n"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="11" t="n"/>
@@ -10674,7 +10166,6 @@
       <c r="P456" s="11" t="n"/>
       <c r="Q456" s="11" t="n"/>
       <c r="R456" s="11" t="n"/>
-      <c r="S456" s="11" t="n"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="11" t="n"/>
@@ -10695,7 +10186,6 @@
       <c r="P457" s="11" t="n"/>
       <c r="Q457" s="11" t="n"/>
       <c r="R457" s="11" t="n"/>
-      <c r="S457" s="11" t="n"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="11" t="n"/>
@@ -10716,7 +10206,6 @@
       <c r="P458" s="11" t="n"/>
       <c r="Q458" s="11" t="n"/>
       <c r="R458" s="11" t="n"/>
-      <c r="S458" s="11" t="n"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="11" t="n"/>
@@ -10737,7 +10226,6 @@
       <c r="P459" s="11" t="n"/>
       <c r="Q459" s="11" t="n"/>
       <c r="R459" s="11" t="n"/>
-      <c r="S459" s="11" t="n"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="11" t="n"/>
@@ -10758,7 +10246,6 @@
       <c r="P460" s="11" t="n"/>
       <c r="Q460" s="11" t="n"/>
       <c r="R460" s="11" t="n"/>
-      <c r="S460" s="11" t="n"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="11" t="n"/>
@@ -10779,7 +10266,6 @@
       <c r="P461" s="11" t="n"/>
       <c r="Q461" s="11" t="n"/>
       <c r="R461" s="11" t="n"/>
-      <c r="S461" s="11" t="n"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="11" t="n"/>
@@ -10800,7 +10286,6 @@
       <c r="P462" s="11" t="n"/>
       <c r="Q462" s="11" t="n"/>
       <c r="R462" s="11" t="n"/>
-      <c r="S462" s="11" t="n"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="11" t="n"/>
@@ -10821,7 +10306,6 @@
       <c r="P463" s="11" t="n"/>
       <c r="Q463" s="11" t="n"/>
       <c r="R463" s="11" t="n"/>
-      <c r="S463" s="11" t="n"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="11" t="n"/>
@@ -10842,7 +10326,6 @@
       <c r="P464" s="11" t="n"/>
       <c r="Q464" s="11" t="n"/>
       <c r="R464" s="11" t="n"/>
-      <c r="S464" s="11" t="n"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="11" t="n"/>
@@ -10863,7 +10346,6 @@
       <c r="P465" s="11" t="n"/>
       <c r="Q465" s="11" t="n"/>
       <c r="R465" s="11" t="n"/>
-      <c r="S465" s="11" t="n"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="11" t="n"/>
@@ -10884,7 +10366,6 @@
       <c r="P466" s="11" t="n"/>
       <c r="Q466" s="11" t="n"/>
       <c r="R466" s="11" t="n"/>
-      <c r="S466" s="11" t="n"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="11" t="n"/>
@@ -10905,7 +10386,6 @@
       <c r="P467" s="11" t="n"/>
       <c r="Q467" s="11" t="n"/>
       <c r="R467" s="11" t="n"/>
-      <c r="S467" s="11" t="n"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="11" t="n"/>
@@ -10926,7 +10406,6 @@
       <c r="P468" s="11" t="n"/>
       <c r="Q468" s="11" t="n"/>
       <c r="R468" s="11" t="n"/>
-      <c r="S468" s="11" t="n"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="11" t="n"/>
@@ -10947,7 +10426,6 @@
       <c r="P469" s="11" t="n"/>
       <c r="Q469" s="11" t="n"/>
       <c r="R469" s="11" t="n"/>
-      <c r="S469" s="11" t="n"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="11" t="n"/>
@@ -10968,7 +10446,6 @@
       <c r="P470" s="11" t="n"/>
       <c r="Q470" s="11" t="n"/>
       <c r="R470" s="11" t="n"/>
-      <c r="S470" s="11" t="n"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="11" t="n"/>
@@ -10989,7 +10466,6 @@
       <c r="P471" s="11" t="n"/>
       <c r="Q471" s="11" t="n"/>
       <c r="R471" s="11" t="n"/>
-      <c r="S471" s="11" t="n"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="11" t="n"/>
@@ -11010,7 +10486,6 @@
       <c r="P472" s="11" t="n"/>
       <c r="Q472" s="11" t="n"/>
       <c r="R472" s="11" t="n"/>
-      <c r="S472" s="11" t="n"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="11" t="n"/>
@@ -11031,7 +10506,6 @@
       <c r="P473" s="11" t="n"/>
       <c r="Q473" s="11" t="n"/>
       <c r="R473" s="11" t="n"/>
-      <c r="S473" s="11" t="n"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="11" t="n"/>
@@ -11052,7 +10526,6 @@
       <c r="P474" s="11" t="n"/>
       <c r="Q474" s="11" t="n"/>
       <c r="R474" s="11" t="n"/>
-      <c r="S474" s="11" t="n"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="11" t="n"/>
@@ -11073,7 +10546,6 @@
       <c r="P475" s="11" t="n"/>
       <c r="Q475" s="11" t="n"/>
       <c r="R475" s="11" t="n"/>
-      <c r="S475" s="11" t="n"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="11" t="n"/>
@@ -11094,7 +10566,6 @@
       <c r="P476" s="11" t="n"/>
       <c r="Q476" s="11" t="n"/>
       <c r="R476" s="11" t="n"/>
-      <c r="S476" s="11" t="n"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="11" t="n"/>
@@ -11115,7 +10586,6 @@
       <c r="P477" s="11" t="n"/>
       <c r="Q477" s="11" t="n"/>
       <c r="R477" s="11" t="n"/>
-      <c r="S477" s="11" t="n"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="11" t="n"/>
@@ -11136,7 +10606,6 @@
       <c r="P478" s="11" t="n"/>
       <c r="Q478" s="11" t="n"/>
       <c r="R478" s="11" t="n"/>
-      <c r="S478" s="11" t="n"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="11" t="n"/>
@@ -11157,7 +10626,6 @@
       <c r="P479" s="11" t="n"/>
       <c r="Q479" s="11" t="n"/>
       <c r="R479" s="11" t="n"/>
-      <c r="S479" s="11" t="n"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="11" t="n"/>
@@ -11178,7 +10646,6 @@
       <c r="P480" s="11" t="n"/>
       <c r="Q480" s="11" t="n"/>
       <c r="R480" s="11" t="n"/>
-      <c r="S480" s="11" t="n"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="11" t="n"/>
@@ -11199,7 +10666,6 @@
       <c r="P481" s="11" t="n"/>
       <c r="Q481" s="11" t="n"/>
       <c r="R481" s="11" t="n"/>
-      <c r="S481" s="11" t="n"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="11" t="n"/>
@@ -11220,7 +10686,6 @@
       <c r="P482" s="11" t="n"/>
       <c r="Q482" s="11" t="n"/>
       <c r="R482" s="11" t="n"/>
-      <c r="S482" s="11" t="n"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="11" t="n"/>
@@ -11241,7 +10706,6 @@
       <c r="P483" s="11" t="n"/>
       <c r="Q483" s="11" t="n"/>
       <c r="R483" s="11" t="n"/>
-      <c r="S483" s="11" t="n"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="11" t="n"/>
@@ -11262,7 +10726,6 @@
       <c r="P484" s="11" t="n"/>
       <c r="Q484" s="11" t="n"/>
       <c r="R484" s="11" t="n"/>
-      <c r="S484" s="11" t="n"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="11" t="n"/>
@@ -11283,7 +10746,6 @@
       <c r="P485" s="11" t="n"/>
       <c r="Q485" s="11" t="n"/>
       <c r="R485" s="11" t="n"/>
-      <c r="S485" s="11" t="n"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="11" t="n"/>
@@ -11304,7 +10766,6 @@
       <c r="P486" s="11" t="n"/>
       <c r="Q486" s="11" t="n"/>
       <c r="R486" s="11" t="n"/>
-      <c r="S486" s="11" t="n"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="11" t="n"/>
@@ -11325,7 +10786,6 @@
       <c r="P487" s="11" t="n"/>
       <c r="Q487" s="11" t="n"/>
       <c r="R487" s="11" t="n"/>
-      <c r="S487" s="11" t="n"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="11" t="n"/>
@@ -11346,7 +10806,6 @@
       <c r="P488" s="11" t="n"/>
       <c r="Q488" s="11" t="n"/>
       <c r="R488" s="11" t="n"/>
-      <c r="S488" s="11" t="n"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="11" t="n"/>
@@ -11367,7 +10826,6 @@
       <c r="P489" s="11" t="n"/>
       <c r="Q489" s="11" t="n"/>
       <c r="R489" s="11" t="n"/>
-      <c r="S489" s="11" t="n"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="11" t="n"/>
@@ -11388,7 +10846,6 @@
       <c r="P490" s="11" t="n"/>
       <c r="Q490" s="11" t="n"/>
       <c r="R490" s="11" t="n"/>
-      <c r="S490" s="11" t="n"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="11" t="n"/>
@@ -11409,7 +10866,6 @@
       <c r="P491" s="11" t="n"/>
       <c r="Q491" s="11" t="n"/>
       <c r="R491" s="11" t="n"/>
-      <c r="S491" s="11" t="n"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="11" t="n"/>
@@ -11430,7 +10886,6 @@
       <c r="P492" s="11" t="n"/>
       <c r="Q492" s="11" t="n"/>
       <c r="R492" s="11" t="n"/>
-      <c r="S492" s="11" t="n"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="11" t="n"/>
@@ -11451,7 +10906,6 @@
       <c r="P493" s="11" t="n"/>
       <c r="Q493" s="11" t="n"/>
       <c r="R493" s="11" t="n"/>
-      <c r="S493" s="11" t="n"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="11" t="n"/>
@@ -11472,7 +10926,6 @@
       <c r="P494" s="11" t="n"/>
       <c r="Q494" s="11" t="n"/>
       <c r="R494" s="11" t="n"/>
-      <c r="S494" s="11" t="n"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="11" t="n"/>
@@ -11493,7 +10946,6 @@
       <c r="P495" s="11" t="n"/>
       <c r="Q495" s="11" t="n"/>
       <c r="R495" s="11" t="n"/>
-      <c r="S495" s="11" t="n"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="11" t="n"/>
@@ -11514,7 +10966,6 @@
       <c r="P496" s="11" t="n"/>
       <c r="Q496" s="11" t="n"/>
       <c r="R496" s="11" t="n"/>
-      <c r="S496" s="11" t="n"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="11" t="n"/>
@@ -11535,7 +10986,6 @@
       <c r="P497" s="11" t="n"/>
       <c r="Q497" s="11" t="n"/>
       <c r="R497" s="11" t="n"/>
-      <c r="S497" s="11" t="n"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="11" t="n"/>
@@ -11556,7 +11006,6 @@
       <c r="P498" s="11" t="n"/>
       <c r="Q498" s="11" t="n"/>
       <c r="R498" s="11" t="n"/>
-      <c r="S498" s="11" t="n"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="11" t="n"/>
@@ -11577,7 +11026,6 @@
       <c r="P499" s="11" t="n"/>
       <c r="Q499" s="11" t="n"/>
       <c r="R499" s="11" t="n"/>
-      <c r="S499" s="11" t="n"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="11" t="n"/>
@@ -11598,7 +11046,6 @@
       <c r="P500" s="11" t="n"/>
       <c r="Q500" s="11" t="n"/>
       <c r="R500" s="11" t="n"/>
-      <c r="S500" s="11" t="n"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="11" t="n"/>
@@ -11619,7 +11066,6 @@
       <c r="P501" s="11" t="n"/>
       <c r="Q501" s="11" t="n"/>
       <c r="R501" s="11" t="n"/>
-      <c r="S501" s="11" t="n"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="11" t="n"/>
@@ -11640,7 +11086,6 @@
       <c r="P502" s="11" t="n"/>
       <c r="Q502" s="11" t="n"/>
       <c r="R502" s="11" t="n"/>
-      <c r="S502" s="11" t="n"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="11" t="n"/>
@@ -11661,7 +11106,6 @@
       <c r="P503" s="11" t="n"/>
       <c r="Q503" s="11" t="n"/>
       <c r="R503" s="11" t="n"/>
-      <c r="S503" s="11" t="n"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="11" t="n"/>
@@ -11682,7 +11126,6 @@
       <c r="P504" s="11" t="n"/>
       <c r="Q504" s="11" t="n"/>
       <c r="R504" s="11" t="n"/>
-      <c r="S504" s="11" t="n"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="11" t="n"/>
@@ -11703,7 +11146,6 @@
       <c r="P505" s="11" t="n"/>
       <c r="Q505" s="11" t="n"/>
       <c r="R505" s="11" t="n"/>
-      <c r="S505" s="11" t="n"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="11" t="n"/>
@@ -11724,7 +11166,6 @@
       <c r="P506" s="11" t="n"/>
       <c r="Q506" s="11" t="n"/>
       <c r="R506" s="11" t="n"/>
-      <c r="S506" s="11" t="n"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="11" t="n"/>
@@ -11745,7 +11186,6 @@
       <c r="P507" s="11" t="n"/>
       <c r="Q507" s="11" t="n"/>
       <c r="R507" s="11" t="n"/>
-      <c r="S507" s="11" t="n"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="11" t="n"/>
@@ -11766,7 +11206,6 @@
       <c r="P508" s="11" t="n"/>
       <c r="Q508" s="11" t="n"/>
       <c r="R508" s="11" t="n"/>
-      <c r="S508" s="11" t="n"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="11" t="n"/>
@@ -11787,7 +11226,6 @@
       <c r="P509" s="11" t="n"/>
       <c r="Q509" s="11" t="n"/>
       <c r="R509" s="11" t="n"/>
-      <c r="S509" s="11" t="n"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="11" t="n"/>
@@ -11808,7 +11246,6 @@
       <c r="P510" s="11" t="n"/>
       <c r="Q510" s="11" t="n"/>
       <c r="R510" s="11" t="n"/>
-      <c r="S510" s="11" t="n"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="11" t="n"/>
@@ -11829,7 +11266,6 @@
       <c r="P511" s="11" t="n"/>
       <c r="Q511" s="11" t="n"/>
       <c r="R511" s="11" t="n"/>
-      <c r="S511" s="11" t="n"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="11" t="n"/>
@@ -11850,7 +11286,6 @@
       <c r="P512" s="11" t="n"/>
       <c r="Q512" s="11" t="n"/>
       <c r="R512" s="11" t="n"/>
-      <c r="S512" s="11" t="n"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="11" t="n"/>
@@ -11871,7 +11306,6 @@
       <c r="P513" s="11" t="n"/>
       <c r="Q513" s="11" t="n"/>
       <c r="R513" s="11" t="n"/>
-      <c r="S513" s="11" t="n"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="11" t="n"/>
@@ -11892,7 +11326,6 @@
       <c r="P514" s="11" t="n"/>
       <c r="Q514" s="11" t="n"/>
       <c r="R514" s="11" t="n"/>
-      <c r="S514" s="11" t="n"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="11" t="n"/>
@@ -11913,7 +11346,6 @@
       <c r="P515" s="11" t="n"/>
       <c r="Q515" s="11" t="n"/>
       <c r="R515" s="11" t="n"/>
-      <c r="S515" s="11" t="n"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="11" t="n"/>
@@ -11934,7 +11366,6 @@
       <c r="P516" s="11" t="n"/>
       <c r="Q516" s="11" t="n"/>
       <c r="R516" s="11" t="n"/>
-      <c r="S516" s="11" t="n"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="11" t="n"/>
@@ -11955,7 +11386,6 @@
       <c r="P517" s="11" t="n"/>
       <c r="Q517" s="11" t="n"/>
       <c r="R517" s="11" t="n"/>
-      <c r="S517" s="11" t="n"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="11" t="n"/>
@@ -11976,7 +11406,6 @@
       <c r="P518" s="11" t="n"/>
       <c r="Q518" s="11" t="n"/>
       <c r="R518" s="11" t="n"/>
-      <c r="S518" s="11" t="n"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="11" t="n"/>
@@ -11997,7 +11426,6 @@
       <c r="P519" s="11" t="n"/>
       <c r="Q519" s="11" t="n"/>
       <c r="R519" s="11" t="n"/>
-      <c r="S519" s="11" t="n"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="11" t="n"/>
@@ -12018,7 +11446,6 @@
       <c r="P520" s="11" t="n"/>
       <c r="Q520" s="11" t="n"/>
       <c r="R520" s="11" t="n"/>
-      <c r="S520" s="11" t="n"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="11" t="n"/>
@@ -12039,7 +11466,6 @@
       <c r="P521" s="11" t="n"/>
       <c r="Q521" s="11" t="n"/>
       <c r="R521" s="11" t="n"/>
-      <c r="S521" s="11" t="n"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="11" t="n"/>
@@ -12060,7 +11486,6 @@
       <c r="P522" s="11" t="n"/>
       <c r="Q522" s="11" t="n"/>
       <c r="R522" s="11" t="n"/>
-      <c r="S522" s="11" t="n"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="11" t="n"/>
@@ -12081,7 +11506,6 @@
       <c r="P523" s="11" t="n"/>
       <c r="Q523" s="11" t="n"/>
       <c r="R523" s="11" t="n"/>
-      <c r="S523" s="11" t="n"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="11" t="n"/>
@@ -12102,7 +11526,6 @@
       <c r="P524" s="11" t="n"/>
       <c r="Q524" s="11" t="n"/>
       <c r="R524" s="11" t="n"/>
-      <c r="S524" s="11" t="n"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="11" t="n"/>
@@ -12123,7 +11546,6 @@
       <c r="P525" s="11" t="n"/>
       <c r="Q525" s="11" t="n"/>
       <c r="R525" s="11" t="n"/>
-      <c r="S525" s="11" t="n"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="11" t="n"/>
@@ -12144,7 +11566,6 @@
       <c r="P526" s="11" t="n"/>
       <c r="Q526" s="11" t="n"/>
       <c r="R526" s="11" t="n"/>
-      <c r="S526" s="11" t="n"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="11" t="n"/>
@@ -12165,7 +11586,6 @@
       <c r="P527" s="11" t="n"/>
       <c r="Q527" s="11" t="n"/>
       <c r="R527" s="11" t="n"/>
-      <c r="S527" s="11" t="n"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="11" t="n"/>
@@ -12186,7 +11606,6 @@
       <c r="P528" s="11" t="n"/>
       <c r="Q528" s="11" t="n"/>
       <c r="R528" s="11" t="n"/>
-      <c r="S528" s="11" t="n"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="11" t="n"/>
@@ -12207,7 +11626,6 @@
       <c r="P529" s="11" t="n"/>
       <c r="Q529" s="11" t="n"/>
       <c r="R529" s="11" t="n"/>
-      <c r="S529" s="11" t="n"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="11" t="n"/>
@@ -12228,7 +11646,6 @@
       <c r="P530" s="11" t="n"/>
       <c r="Q530" s="11" t="n"/>
       <c r="R530" s="11" t="n"/>
-      <c r="S530" s="11" t="n"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="11" t="n"/>
@@ -12249,7 +11666,6 @@
       <c r="P531" s="11" t="n"/>
       <c r="Q531" s="11" t="n"/>
       <c r="R531" s="11" t="n"/>
-      <c r="S531" s="11" t="n"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="11" t="n"/>
@@ -12270,7 +11686,6 @@
       <c r="P532" s="11" t="n"/>
       <c r="Q532" s="11" t="n"/>
       <c r="R532" s="11" t="n"/>
-      <c r="S532" s="11" t="n"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="11" t="n"/>
@@ -12291,7 +11706,6 @@
       <c r="P533" s="11" t="n"/>
       <c r="Q533" s="11" t="n"/>
       <c r="R533" s="11" t="n"/>
-      <c r="S533" s="11" t="n"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="11" t="n"/>
@@ -12312,7 +11726,6 @@
       <c r="P534" s="11" t="n"/>
       <c r="Q534" s="11" t="n"/>
       <c r="R534" s="11" t="n"/>
-      <c r="S534" s="11" t="n"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="11" t="n"/>
@@ -12333,7 +11746,6 @@
       <c r="P535" s="11" t="n"/>
       <c r="Q535" s="11" t="n"/>
       <c r="R535" s="11" t="n"/>
-      <c r="S535" s="11" t="n"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="11" t="n"/>
@@ -12354,7 +11766,6 @@
       <c r="P536" s="11" t="n"/>
       <c r="Q536" s="11" t="n"/>
       <c r="R536" s="11" t="n"/>
-      <c r="S536" s="11" t="n"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="11" t="n"/>
@@ -12375,7 +11786,6 @@
       <c r="P537" s="11" t="n"/>
       <c r="Q537" s="11" t="n"/>
       <c r="R537" s="11" t="n"/>
-      <c r="S537" s="11" t="n"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="11" t="n"/>
@@ -12396,7 +11806,6 @@
       <c r="P538" s="11" t="n"/>
       <c r="Q538" s="11" t="n"/>
       <c r="R538" s="11" t="n"/>
-      <c r="S538" s="11" t="n"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="11" t="n"/>
@@ -12417,7 +11826,6 @@
       <c r="P539" s="11" t="n"/>
       <c r="Q539" s="11" t="n"/>
       <c r="R539" s="11" t="n"/>
-      <c r="S539" s="11" t="n"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="11" t="n"/>
@@ -12438,7 +11846,6 @@
       <c r="P540" s="11" t="n"/>
       <c r="Q540" s="11" t="n"/>
       <c r="R540" s="11" t="n"/>
-      <c r="S540" s="11" t="n"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="11" t="n"/>
@@ -12459,7 +11866,6 @@
       <c r="P541" s="11" t="n"/>
       <c r="Q541" s="11" t="n"/>
       <c r="R541" s="11" t="n"/>
-      <c r="S541" s="11" t="n"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="11" t="n"/>
@@ -12480,7 +11886,6 @@
       <c r="P542" s="11" t="n"/>
       <c r="Q542" s="11" t="n"/>
       <c r="R542" s="11" t="n"/>
-      <c r="S542" s="11" t="n"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="11" t="n"/>
@@ -12501,7 +11906,6 @@
       <c r="P543" s="11" t="n"/>
       <c r="Q543" s="11" t="n"/>
       <c r="R543" s="11" t="n"/>
-      <c r="S543" s="11" t="n"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="11" t="n"/>
@@ -12522,7 +11926,6 @@
       <c r="P544" s="11" t="n"/>
       <c r="Q544" s="11" t="n"/>
       <c r="R544" s="11" t="n"/>
-      <c r="S544" s="11" t="n"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="11" t="n"/>
@@ -12543,7 +11946,6 @@
       <c r="P545" s="11" t="n"/>
       <c r="Q545" s="11" t="n"/>
       <c r="R545" s="11" t="n"/>
-      <c r="S545" s="11" t="n"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="11" t="n"/>
@@ -12564,7 +11966,6 @@
       <c r="P546" s="11" t="n"/>
       <c r="Q546" s="11" t="n"/>
       <c r="R546" s="11" t="n"/>
-      <c r="S546" s="11" t="n"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="11" t="n"/>
@@ -12585,7 +11986,6 @@
       <c r="P547" s="11" t="n"/>
       <c r="Q547" s="11" t="n"/>
       <c r="R547" s="11" t="n"/>
-      <c r="S547" s="11" t="n"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="11" t="n"/>
@@ -12606,7 +12006,6 @@
       <c r="P548" s="11" t="n"/>
       <c r="Q548" s="11" t="n"/>
       <c r="R548" s="11" t="n"/>
-      <c r="S548" s="11" t="n"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="11" t="n"/>
@@ -12627,7 +12026,6 @@
       <c r="P549" s="11" t="n"/>
       <c r="Q549" s="11" t="n"/>
       <c r="R549" s="11" t="n"/>
-      <c r="S549" s="11" t="n"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="11" t="n"/>
@@ -12648,7 +12046,6 @@
       <c r="P550" s="11" t="n"/>
       <c r="Q550" s="11" t="n"/>
       <c r="R550" s="11" t="n"/>
-      <c r="S550" s="11" t="n"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="11" t="n"/>
@@ -12669,7 +12066,6 @@
       <c r="P551" s="11" t="n"/>
       <c r="Q551" s="11" t="n"/>
       <c r="R551" s="11" t="n"/>
-      <c r="S551" s="11" t="n"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="11" t="n"/>
@@ -12690,7 +12086,6 @@
       <c r="P552" s="11" t="n"/>
       <c r="Q552" s="11" t="n"/>
       <c r="R552" s="11" t="n"/>
-      <c r="S552" s="11" t="n"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="11" t="n"/>
@@ -12711,7 +12106,6 @@
       <c r="P553" s="11" t="n"/>
       <c r="Q553" s="11" t="n"/>
       <c r="R553" s="11" t="n"/>
-      <c r="S553" s="11" t="n"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="11" t="n"/>
@@ -12732,7 +12126,6 @@
       <c r="P554" s="11" t="n"/>
       <c r="Q554" s="11" t="n"/>
       <c r="R554" s="11" t="n"/>
-      <c r="S554" s="11" t="n"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="11" t="n"/>
@@ -12753,7 +12146,6 @@
       <c r="P555" s="11" t="n"/>
       <c r="Q555" s="11" t="n"/>
       <c r="R555" s="11" t="n"/>
-      <c r="S555" s="11" t="n"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="11" t="n"/>
@@ -12774,7 +12166,6 @@
       <c r="P556" s="11" t="n"/>
       <c r="Q556" s="11" t="n"/>
       <c r="R556" s="11" t="n"/>
-      <c r="S556" s="11" t="n"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="11" t="n"/>
@@ -12795,7 +12186,6 @@
       <c r="P557" s="11" t="n"/>
       <c r="Q557" s="11" t="n"/>
       <c r="R557" s="11" t="n"/>
-      <c r="S557" s="11" t="n"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="11" t="n"/>
@@ -12816,7 +12206,6 @@
       <c r="P558" s="11" t="n"/>
       <c r="Q558" s="11" t="n"/>
       <c r="R558" s="11" t="n"/>
-      <c r="S558" s="11" t="n"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="11" t="n"/>
@@ -12837,7 +12226,6 @@
       <c r="P559" s="11" t="n"/>
       <c r="Q559" s="11" t="n"/>
       <c r="R559" s="11" t="n"/>
-      <c r="S559" s="11" t="n"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="11" t="n"/>
@@ -12858,7 +12246,6 @@
       <c r="P560" s="11" t="n"/>
       <c r="Q560" s="11" t="n"/>
       <c r="R560" s="11" t="n"/>
-      <c r="S560" s="11" t="n"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="11" t="n"/>
@@ -12879,7 +12266,6 @@
       <c r="P561" s="11" t="n"/>
       <c r="Q561" s="11" t="n"/>
       <c r="R561" s="11" t="n"/>
-      <c r="S561" s="11" t="n"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="11" t="n"/>
@@ -12900,7 +12286,6 @@
       <c r="P562" s="11" t="n"/>
       <c r="Q562" s="11" t="n"/>
       <c r="R562" s="11" t="n"/>
-      <c r="S562" s="11" t="n"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="11" t="n"/>
@@ -12921,7 +12306,6 @@
       <c r="P563" s="11" t="n"/>
       <c r="Q563" s="11" t="n"/>
       <c r="R563" s="11" t="n"/>
-      <c r="S563" s="11" t="n"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="11" t="n"/>
@@ -12942,7 +12326,6 @@
       <c r="P564" s="11" t="n"/>
       <c r="Q564" s="11" t="n"/>
       <c r="R564" s="11" t="n"/>
-      <c r="S564" s="11" t="n"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="11" t="n"/>
@@ -12963,7 +12346,6 @@
       <c r="P565" s="11" t="n"/>
       <c r="Q565" s="11" t="n"/>
       <c r="R565" s="11" t="n"/>
-      <c r="S565" s="11" t="n"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="11" t="n"/>
@@ -12984,7 +12366,6 @@
       <c r="P566" s="11" t="n"/>
       <c r="Q566" s="11" t="n"/>
       <c r="R566" s="11" t="n"/>
-      <c r="S566" s="11" t="n"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="11" t="n"/>
@@ -13005,7 +12386,6 @@
       <c r="P567" s="11" t="n"/>
       <c r="Q567" s="11" t="n"/>
       <c r="R567" s="11" t="n"/>
-      <c r="S567" s="11" t="n"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="11" t="n"/>
@@ -13026,7 +12406,6 @@
       <c r="P568" s="11" t="n"/>
       <c r="Q568" s="11" t="n"/>
       <c r="R568" s="11" t="n"/>
-      <c r="S568" s="11" t="n"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="11" t="n"/>
@@ -13047,7 +12426,6 @@
       <c r="P569" s="11" t="n"/>
       <c r="Q569" s="11" t="n"/>
       <c r="R569" s="11" t="n"/>
-      <c r="S569" s="11" t="n"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="11" t="n"/>
@@ -13068,7 +12446,6 @@
       <c r="P570" s="11" t="n"/>
       <c r="Q570" s="11" t="n"/>
       <c r="R570" s="11" t="n"/>
-      <c r="S570" s="11" t="n"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="11" t="n"/>
@@ -13089,7 +12466,6 @@
       <c r="P571" s="11" t="n"/>
       <c r="Q571" s="11" t="n"/>
       <c r="R571" s="11" t="n"/>
-      <c r="S571" s="11" t="n"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="11" t="n"/>
@@ -13110,7 +12486,6 @@
       <c r="P572" s="11" t="n"/>
       <c r="Q572" s="11" t="n"/>
       <c r="R572" s="11" t="n"/>
-      <c r="S572" s="11" t="n"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="11" t="n"/>
@@ -13131,7 +12506,6 @@
       <c r="P573" s="11" t="n"/>
       <c r="Q573" s="11" t="n"/>
       <c r="R573" s="11" t="n"/>
-      <c r="S573" s="11" t="n"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="11" t="n"/>
@@ -13152,7 +12526,6 @@
       <c r="P574" s="11" t="n"/>
       <c r="Q574" s="11" t="n"/>
       <c r="R574" s="11" t="n"/>
-      <c r="S574" s="11" t="n"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="11" t="n"/>
@@ -13173,7 +12546,6 @@
       <c r="P575" s="11" t="n"/>
       <c r="Q575" s="11" t="n"/>
       <c r="R575" s="11" t="n"/>
-      <c r="S575" s="11" t="n"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="11" t="n"/>
@@ -13194,7 +12566,6 @@
       <c r="P576" s="11" t="n"/>
       <c r="Q576" s="11" t="n"/>
       <c r="R576" s="11" t="n"/>
-      <c r="S576" s="11" t="n"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="11" t="n"/>
@@ -13215,7 +12586,6 @@
       <c r="P577" s="11" t="n"/>
       <c r="Q577" s="11" t="n"/>
       <c r="R577" s="11" t="n"/>
-      <c r="S577" s="11" t="n"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="11" t="n"/>
@@ -13236,7 +12606,6 @@
       <c r="P578" s="11" t="n"/>
       <c r="Q578" s="11" t="n"/>
       <c r="R578" s="11" t="n"/>
-      <c r="S578" s="11" t="n"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="11" t="n"/>
@@ -13257,7 +12626,6 @@
       <c r="P579" s="11" t="n"/>
       <c r="Q579" s="11" t="n"/>
       <c r="R579" s="11" t="n"/>
-      <c r="S579" s="11" t="n"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="11" t="n"/>
@@ -13278,7 +12646,6 @@
       <c r="P580" s="11" t="n"/>
       <c r="Q580" s="11" t="n"/>
       <c r="R580" s="11" t="n"/>
-      <c r="S580" s="11" t="n"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="11" t="n"/>
@@ -13299,7 +12666,6 @@
       <c r="P581" s="11" t="n"/>
       <c r="Q581" s="11" t="n"/>
       <c r="R581" s="11" t="n"/>
-      <c r="S581" s="11" t="n"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="11" t="n"/>
@@ -13320,7 +12686,6 @@
       <c r="P582" s="11" t="n"/>
       <c r="Q582" s="11" t="n"/>
       <c r="R582" s="11" t="n"/>
-      <c r="S582" s="11" t="n"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="11" t="n"/>
@@ -13341,7 +12706,6 @@
       <c r="P583" s="11" t="n"/>
       <c r="Q583" s="11" t="n"/>
       <c r="R583" s="11" t="n"/>
-      <c r="S583" s="11" t="n"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="11" t="n"/>
@@ -13362,7 +12726,6 @@
       <c r="P584" s="11" t="n"/>
       <c r="Q584" s="11" t="n"/>
       <c r="R584" s="11" t="n"/>
-      <c r="S584" s="11" t="n"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="11" t="n"/>
@@ -13383,7 +12746,6 @@
       <c r="P585" s="11" t="n"/>
       <c r="Q585" s="11" t="n"/>
       <c r="R585" s="11" t="n"/>
-      <c r="S585" s="11" t="n"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="11" t="n"/>
@@ -13404,7 +12766,6 @@
       <c r="P586" s="11" t="n"/>
       <c r="Q586" s="11" t="n"/>
       <c r="R586" s="11" t="n"/>
-      <c r="S586" s="11" t="n"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="11" t="n"/>
@@ -13425,7 +12786,6 @@
       <c r="P587" s="11" t="n"/>
       <c r="Q587" s="11" t="n"/>
       <c r="R587" s="11" t="n"/>
-      <c r="S587" s="11" t="n"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="11" t="n"/>
@@ -13446,7 +12806,6 @@
       <c r="P588" s="11" t="n"/>
       <c r="Q588" s="11" t="n"/>
       <c r="R588" s="11" t="n"/>
-      <c r="S588" s="11" t="n"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="11" t="n"/>
@@ -13467,7 +12826,6 @@
       <c r="P589" s="11" t="n"/>
       <c r="Q589" s="11" t="n"/>
       <c r="R589" s="11" t="n"/>
-      <c r="S589" s="11" t="n"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="11" t="n"/>
@@ -13488,7 +12846,6 @@
       <c r="P590" s="11" t="n"/>
       <c r="Q590" s="11" t="n"/>
       <c r="R590" s="11" t="n"/>
-      <c r="S590" s="11" t="n"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="11" t="n"/>
@@ -13509,7 +12866,6 @@
       <c r="P591" s="11" t="n"/>
       <c r="Q591" s="11" t="n"/>
       <c r="R591" s="11" t="n"/>
-      <c r="S591" s="11" t="n"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="11" t="n"/>
@@ -13530,7 +12886,6 @@
       <c r="P592" s="11" t="n"/>
       <c r="Q592" s="11" t="n"/>
       <c r="R592" s="11" t="n"/>
-      <c r="S592" s="11" t="n"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="11" t="n"/>
@@ -13551,7 +12906,6 @@
       <c r="P593" s="11" t="n"/>
       <c r="Q593" s="11" t="n"/>
       <c r="R593" s="11" t="n"/>
-      <c r="S593" s="11" t="n"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="11" t="n"/>
@@ -13572,7 +12926,6 @@
       <c r="P594" s="11" t="n"/>
       <c r="Q594" s="11" t="n"/>
       <c r="R594" s="11" t="n"/>
-      <c r="S594" s="11" t="n"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="11" t="n"/>
@@ -13593,7 +12946,6 @@
       <c r="P595" s="11" t="n"/>
       <c r="Q595" s="11" t="n"/>
       <c r="R595" s="11" t="n"/>
-      <c r="S595" s="11" t="n"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="11" t="n"/>
@@ -13614,7 +12966,6 @@
       <c r="P596" s="11" t="n"/>
       <c r="Q596" s="11" t="n"/>
       <c r="R596" s="11" t="n"/>
-      <c r="S596" s="11" t="n"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="11" t="n"/>
@@ -13635,7 +12986,6 @@
       <c r="P597" s="11" t="n"/>
       <c r="Q597" s="11" t="n"/>
       <c r="R597" s="11" t="n"/>
-      <c r="S597" s="11" t="n"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="11" t="n"/>
@@ -13656,7 +13006,6 @@
       <c r="P598" s="11" t="n"/>
       <c r="Q598" s="11" t="n"/>
       <c r="R598" s="11" t="n"/>
-      <c r="S598" s="11" t="n"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="11" t="n"/>
@@ -13677,7 +13026,6 @@
       <c r="P599" s="11" t="n"/>
       <c r="Q599" s="11" t="n"/>
       <c r="R599" s="11" t="n"/>
-      <c r="S599" s="11" t="n"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="11" t="n"/>
@@ -13698,7 +13046,6 @@
       <c r="P600" s="11" t="n"/>
       <c r="Q600" s="11" t="n"/>
       <c r="R600" s="11" t="n"/>
-      <c r="S600" s="11" t="n"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="11" t="n"/>
@@ -13719,7 +13066,6 @@
       <c r="P601" s="11" t="n"/>
       <c r="Q601" s="11" t="n"/>
       <c r="R601" s="11" t="n"/>
-      <c r="S601" s="11" t="n"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="11" t="n"/>
@@ -13740,7 +13086,6 @@
       <c r="P602" s="11" t="n"/>
       <c r="Q602" s="11" t="n"/>
       <c r="R602" s="11" t="n"/>
-      <c r="S602" s="11" t="n"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="11" t="n"/>
@@ -13761,7 +13106,6 @@
       <c r="P603" s="11" t="n"/>
       <c r="Q603" s="11" t="n"/>
       <c r="R603" s="11" t="n"/>
-      <c r="S603" s="11" t="n"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="11" t="n"/>
@@ -13782,7 +13126,6 @@
       <c r="P604" s="11" t="n"/>
       <c r="Q604" s="11" t="n"/>
       <c r="R604" s="11" t="n"/>
-      <c r="S604" s="11" t="n"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="11" t="n"/>
@@ -13803,7 +13146,6 @@
       <c r="P605" s="11" t="n"/>
       <c r="Q605" s="11" t="n"/>
       <c r="R605" s="11" t="n"/>
-      <c r="S605" s="11" t="n"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="11" t="n"/>
@@ -13824,7 +13166,6 @@
       <c r="P606" s="11" t="n"/>
       <c r="Q606" s="11" t="n"/>
       <c r="R606" s="11" t="n"/>
-      <c r="S606" s="11" t="n"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="11" t="n"/>
@@ -13845,7 +13186,6 @@
       <c r="P607" s="11" t="n"/>
       <c r="Q607" s="11" t="n"/>
       <c r="R607" s="11" t="n"/>
-      <c r="S607" s="11" t="n"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="11" t="n"/>
@@ -13866,7 +13206,6 @@
       <c r="P608" s="11" t="n"/>
       <c r="Q608" s="11" t="n"/>
       <c r="R608" s="11" t="n"/>
-      <c r="S608" s="11" t="n"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="11" t="n"/>
@@ -13887,7 +13226,6 @@
       <c r="P609" s="11" t="n"/>
       <c r="Q609" s="11" t="n"/>
       <c r="R609" s="11" t="n"/>
-      <c r="S609" s="11" t="n"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="11" t="n"/>
@@ -13908,7 +13246,6 @@
       <c r="P610" s="11" t="n"/>
       <c r="Q610" s="11" t="n"/>
       <c r="R610" s="11" t="n"/>
-      <c r="S610" s="11" t="n"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="11" t="n"/>
@@ -13929,7 +13266,6 @@
       <c r="P611" s="11" t="n"/>
       <c r="Q611" s="11" t="n"/>
       <c r="R611" s="11" t="n"/>
-      <c r="S611" s="11" t="n"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="11" t="n"/>
@@ -13950,7 +13286,6 @@
       <c r="P612" s="11" t="n"/>
       <c r="Q612" s="11" t="n"/>
       <c r="R612" s="11" t="n"/>
-      <c r="S612" s="11" t="n"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="11" t="n"/>
@@ -13971,7 +13306,6 @@
       <c r="P613" s="11" t="n"/>
       <c r="Q613" s="11" t="n"/>
       <c r="R613" s="11" t="n"/>
-      <c r="S613" s="11" t="n"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="11" t="n"/>
@@ -13992,7 +13326,6 @@
       <c r="P614" s="11" t="n"/>
       <c r="Q614" s="11" t="n"/>
       <c r="R614" s="11" t="n"/>
-      <c r="S614" s="11" t="n"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="11" t="n"/>
@@ -14013,7 +13346,6 @@
       <c r="P615" s="11" t="n"/>
       <c r="Q615" s="11" t="n"/>
       <c r="R615" s="11" t="n"/>
-      <c r="S615" s="11" t="n"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="11" t="n"/>
@@ -14034,7 +13366,6 @@
       <c r="P616" s="11" t="n"/>
       <c r="Q616" s="11" t="n"/>
       <c r="R616" s="11" t="n"/>
-      <c r="S616" s="11" t="n"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="11" t="n"/>
@@ -14055,7 +13386,6 @@
       <c r="P617" s="11" t="n"/>
       <c r="Q617" s="11" t="n"/>
       <c r="R617" s="11" t="n"/>
-      <c r="S617" s="11" t="n"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="11" t="n"/>
@@ -14076,7 +13406,6 @@
       <c r="P618" s="11" t="n"/>
       <c r="Q618" s="11" t="n"/>
       <c r="R618" s="11" t="n"/>
-      <c r="S618" s="11" t="n"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="11" t="n"/>
@@ -14097,7 +13426,6 @@
       <c r="P619" s="11" t="n"/>
       <c r="Q619" s="11" t="n"/>
       <c r="R619" s="11" t="n"/>
-      <c r="S619" s="11" t="n"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="11" t="n"/>
@@ -14118,7 +13446,6 @@
       <c r="P620" s="11" t="n"/>
       <c r="Q620" s="11" t="n"/>
       <c r="R620" s="11" t="n"/>
-      <c r="S620" s="11" t="n"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="11" t="n"/>
@@ -14139,7 +13466,6 @@
       <c r="P621" s="11" t="n"/>
       <c r="Q621" s="11" t="n"/>
       <c r="R621" s="11" t="n"/>
-      <c r="S621" s="11" t="n"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="11" t="n"/>
@@ -14160,7 +13486,6 @@
       <c r="P622" s="11" t="n"/>
       <c r="Q622" s="11" t="n"/>
       <c r="R622" s="11" t="n"/>
-      <c r="S622" s="11" t="n"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="11" t="n"/>
@@ -14181,7 +13506,6 @@
       <c r="P623" s="11" t="n"/>
       <c r="Q623" s="11" t="n"/>
       <c r="R623" s="11" t="n"/>
-      <c r="S623" s="11" t="n"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="11" t="n"/>
@@ -14202,7 +13526,6 @@
       <c r="P624" s="11" t="n"/>
       <c r="Q624" s="11" t="n"/>
       <c r="R624" s="11" t="n"/>
-      <c r="S624" s="11" t="n"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="11" t="n"/>
@@ -14223,7 +13546,6 @@
       <c r="P625" s="11" t="n"/>
       <c r="Q625" s="11" t="n"/>
       <c r="R625" s="11" t="n"/>
-      <c r="S625" s="11" t="n"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="11" t="n"/>
@@ -14244,7 +13566,6 @@
       <c r="P626" s="11" t="n"/>
       <c r="Q626" s="11" t="n"/>
       <c r="R626" s="11" t="n"/>
-      <c r="S626" s="11" t="n"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="11" t="n"/>
@@ -14265,7 +13586,6 @@
       <c r="P627" s="11" t="n"/>
       <c r="Q627" s="11" t="n"/>
       <c r="R627" s="11" t="n"/>
-      <c r="S627" s="11" t="n"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="11" t="n"/>
@@ -14286,7 +13606,6 @@
       <c r="P628" s="11" t="n"/>
       <c r="Q628" s="11" t="n"/>
       <c r="R628" s="11" t="n"/>
-      <c r="S628" s="11" t="n"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="11" t="n"/>
@@ -14307,7 +13626,6 @@
       <c r="P629" s="11" t="n"/>
       <c r="Q629" s="11" t="n"/>
       <c r="R629" s="11" t="n"/>
-      <c r="S629" s="11" t="n"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="11" t="n"/>
@@ -14328,7 +13646,6 @@
       <c r="P630" s="11" t="n"/>
       <c r="Q630" s="11" t="n"/>
       <c r="R630" s="11" t="n"/>
-      <c r="S630" s="11" t="n"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="11" t="n"/>
@@ -14349,7 +13666,6 @@
       <c r="P631" s="11" t="n"/>
       <c r="Q631" s="11" t="n"/>
       <c r="R631" s="11" t="n"/>
-      <c r="S631" s="11" t="n"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="11" t="n"/>
@@ -14370,7 +13686,6 @@
       <c r="P632" s="11" t="n"/>
       <c r="Q632" s="11" t="n"/>
       <c r="R632" s="11" t="n"/>
-      <c r="S632" s="11" t="n"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="11" t="n"/>
@@ -14391,7 +13706,6 @@
       <c r="P633" s="11" t="n"/>
       <c r="Q633" s="11" t="n"/>
       <c r="R633" s="11" t="n"/>
-      <c r="S633" s="11" t="n"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="11" t="n"/>
@@ -14412,7 +13726,6 @@
       <c r="P634" s="11" t="n"/>
       <c r="Q634" s="11" t="n"/>
       <c r="R634" s="11" t="n"/>
-      <c r="S634" s="11" t="n"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="11" t="n"/>
@@ -14433,7 +13746,6 @@
       <c r="P635" s="11" t="n"/>
       <c r="Q635" s="11" t="n"/>
       <c r="R635" s="11" t="n"/>
-      <c r="S635" s="11" t="n"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="11" t="n"/>
@@ -14454,7 +13766,6 @@
       <c r="P636" s="11" t="n"/>
       <c r="Q636" s="11" t="n"/>
       <c r="R636" s="11" t="n"/>
-      <c r="S636" s="11" t="n"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="11" t="n"/>
@@ -14475,7 +13786,6 @@
       <c r="P637" s="11" t="n"/>
       <c r="Q637" s="11" t="n"/>
       <c r="R637" s="11" t="n"/>
-      <c r="S637" s="11" t="n"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="11" t="n"/>
@@ -14496,7 +13806,6 @@
       <c r="P638" s="11" t="n"/>
       <c r="Q638" s="11" t="n"/>
       <c r="R638" s="11" t="n"/>
-      <c r="S638" s="11" t="n"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="11" t="n"/>
@@ -14517,7 +13826,6 @@
       <c r="P639" s="11" t="n"/>
       <c r="Q639" s="11" t="n"/>
       <c r="R639" s="11" t="n"/>
-      <c r="S639" s="11" t="n"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="11" t="n"/>
@@ -14538,7 +13846,6 @@
       <c r="P640" s="11" t="n"/>
       <c r="Q640" s="11" t="n"/>
       <c r="R640" s="11" t="n"/>
-      <c r="S640" s="11" t="n"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="11" t="n"/>
@@ -14559,7 +13866,6 @@
       <c r="P641" s="11" t="n"/>
       <c r="Q641" s="11" t="n"/>
       <c r="R641" s="11" t="n"/>
-      <c r="S641" s="11" t="n"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="11" t="n"/>
@@ -14580,7 +13886,6 @@
       <c r="P642" s="11" t="n"/>
       <c r="Q642" s="11" t="n"/>
       <c r="R642" s="11" t="n"/>
-      <c r="S642" s="11" t="n"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="11" t="n"/>
@@ -14601,7 +13906,6 @@
       <c r="P643" s="11" t="n"/>
       <c r="Q643" s="11" t="n"/>
       <c r="R643" s="11" t="n"/>
-      <c r="S643" s="11" t="n"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="11" t="n"/>
@@ -14622,7 +13926,6 @@
       <c r="P644" s="11" t="n"/>
       <c r="Q644" s="11" t="n"/>
       <c r="R644" s="11" t="n"/>
-      <c r="S644" s="11" t="n"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="11" t="n"/>
@@ -14643,7 +13946,6 @@
       <c r="P645" s="11" t="n"/>
       <c r="Q645" s="11" t="n"/>
       <c r="R645" s="11" t="n"/>
-      <c r="S645" s="11" t="n"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="11" t="n"/>
@@ -14664,7 +13966,6 @@
       <c r="P646" s="11" t="n"/>
       <c r="Q646" s="11" t="n"/>
       <c r="R646" s="11" t="n"/>
-      <c r="S646" s="11" t="n"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="11" t="n"/>
@@ -14685,7 +13986,6 @@
       <c r="P647" s="11" t="n"/>
       <c r="Q647" s="11" t="n"/>
       <c r="R647" s="11" t="n"/>
-      <c r="S647" s="11" t="n"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="11" t="n"/>
@@ -14706,7 +14006,6 @@
       <c r="P648" s="11" t="n"/>
       <c r="Q648" s="11" t="n"/>
       <c r="R648" s="11" t="n"/>
-      <c r="S648" s="11" t="n"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="11" t="n"/>
@@ -14727,7 +14026,6 @@
       <c r="P649" s="11" t="n"/>
       <c r="Q649" s="11" t="n"/>
       <c r="R649" s="11" t="n"/>
-      <c r="S649" s="11" t="n"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="11" t="n"/>
@@ -14748,7 +14046,6 @@
       <c r="P650" s="11" t="n"/>
       <c r="Q650" s="11" t="n"/>
       <c r="R650" s="11" t="n"/>
-      <c r="S650" s="11" t="n"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="11" t="n"/>
@@ -14769,7 +14066,6 @@
       <c r="P651" s="11" t="n"/>
       <c r="Q651" s="11" t="n"/>
       <c r="R651" s="11" t="n"/>
-      <c r="S651" s="11" t="n"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="11" t="n"/>
@@ -14790,7 +14086,6 @@
       <c r="P652" s="11" t="n"/>
       <c r="Q652" s="11" t="n"/>
       <c r="R652" s="11" t="n"/>
-      <c r="S652" s="11" t="n"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="11" t="n"/>
@@ -14811,7 +14106,6 @@
       <c r="P653" s="11" t="n"/>
       <c r="Q653" s="11" t="n"/>
       <c r="R653" s="11" t="n"/>
-      <c r="S653" s="11" t="n"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="11" t="n"/>
@@ -14832,7 +14126,6 @@
       <c r="P654" s="11" t="n"/>
       <c r="Q654" s="11" t="n"/>
       <c r="R654" s="11" t="n"/>
-      <c r="S654" s="11" t="n"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="11" t="n"/>
@@ -14853,7 +14146,6 @@
       <c r="P655" s="11" t="n"/>
       <c r="Q655" s="11" t="n"/>
       <c r="R655" s="11" t="n"/>
-      <c r="S655" s="11" t="n"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="11" t="n"/>
@@ -14874,7 +14166,6 @@
       <c r="P656" s="11" t="n"/>
       <c r="Q656" s="11" t="n"/>
       <c r="R656" s="11" t="n"/>
-      <c r="S656" s="11" t="n"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="11" t="n"/>
@@ -14895,7 +14186,6 @@
       <c r="P657" s="11" t="n"/>
       <c r="Q657" s="11" t="n"/>
       <c r="R657" s="11" t="n"/>
-      <c r="S657" s="11" t="n"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="11" t="n"/>
@@ -14916,7 +14206,6 @@
       <c r="P658" s="11" t="n"/>
       <c r="Q658" s="11" t="n"/>
       <c r="R658" s="11" t="n"/>
-      <c r="S658" s="11" t="n"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="11" t="n"/>
@@ -14937,7 +14226,6 @@
       <c r="P659" s="11" t="n"/>
       <c r="Q659" s="11" t="n"/>
       <c r="R659" s="11" t="n"/>
-      <c r="S659" s="11" t="n"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="11" t="n"/>
@@ -14958,7 +14246,6 @@
       <c r="P660" s="11" t="n"/>
       <c r="Q660" s="11" t="n"/>
       <c r="R660" s="11" t="n"/>
-      <c r="S660" s="11" t="n"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="11" t="n"/>
@@ -14979,7 +14266,6 @@
       <c r="P661" s="11" t="n"/>
       <c r="Q661" s="11" t="n"/>
       <c r="R661" s="11" t="n"/>
-      <c r="S661" s="11" t="n"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="11" t="n"/>
@@ -15000,7 +14286,6 @@
       <c r="P662" s="11" t="n"/>
       <c r="Q662" s="11" t="n"/>
       <c r="R662" s="11" t="n"/>
-      <c r="S662" s="11" t="n"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="11" t="n"/>
@@ -15021,7 +14306,6 @@
       <c r="P663" s="11" t="n"/>
       <c r="Q663" s="11" t="n"/>
       <c r="R663" s="11" t="n"/>
-      <c r="S663" s="11" t="n"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="11" t="n"/>
@@ -15042,7 +14326,6 @@
       <c r="P664" s="11" t="n"/>
       <c r="Q664" s="11" t="n"/>
       <c r="R664" s="11" t="n"/>
-      <c r="S664" s="11" t="n"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="11" t="n"/>
@@ -15063,7 +14346,6 @@
       <c r="P665" s="11" t="n"/>
       <c r="Q665" s="11" t="n"/>
       <c r="R665" s="11" t="n"/>
-      <c r="S665" s="11" t="n"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="11" t="n"/>
@@ -15084,7 +14366,6 @@
       <c r="P666" s="11" t="n"/>
       <c r="Q666" s="11" t="n"/>
       <c r="R666" s="11" t="n"/>
-      <c r="S666" s="11" t="n"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="11" t="n"/>
@@ -15105,7 +14386,6 @@
       <c r="P667" s="11" t="n"/>
       <c r="Q667" s="11" t="n"/>
       <c r="R667" s="11" t="n"/>
-      <c r="S667" s="11" t="n"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="11" t="n"/>
@@ -15126,7 +14406,6 @@
       <c r="P668" s="11" t="n"/>
       <c r="Q668" s="11" t="n"/>
       <c r="R668" s="11" t="n"/>
-      <c r="S668" s="11" t="n"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="11" t="n"/>
@@ -15147,7 +14426,6 @@
       <c r="P669" s="11" t="n"/>
       <c r="Q669" s="11" t="n"/>
       <c r="R669" s="11" t="n"/>
-      <c r="S669" s="11" t="n"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="11" t="n"/>
@@ -15168,7 +14446,6 @@
       <c r="P670" s="11" t="n"/>
       <c r="Q670" s="11" t="n"/>
       <c r="R670" s="11" t="n"/>
-      <c r="S670" s="11" t="n"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="11" t="n"/>
@@ -15189,7 +14466,6 @@
       <c r="P671" s="11" t="n"/>
       <c r="Q671" s="11" t="n"/>
       <c r="R671" s="11" t="n"/>
-      <c r="S671" s="11" t="n"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="11" t="n"/>
@@ -15210,7 +14486,6 @@
       <c r="P672" s="11" t="n"/>
       <c r="Q672" s="11" t="n"/>
       <c r="R672" s="11" t="n"/>
-      <c r="S672" s="11" t="n"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="11" t="n"/>
@@ -15231,7 +14506,6 @@
       <c r="P673" s="11" t="n"/>
       <c r="Q673" s="11" t="n"/>
       <c r="R673" s="11" t="n"/>
-      <c r="S673" s="11" t="n"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="11" t="n"/>
@@ -15252,7 +14526,6 @@
       <c r="P674" s="11" t="n"/>
       <c r="Q674" s="11" t="n"/>
       <c r="R674" s="11" t="n"/>
-      <c r="S674" s="11" t="n"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="11" t="n"/>
@@ -15273,7 +14546,6 @@
       <c r="P675" s="11" t="n"/>
       <c r="Q675" s="11" t="n"/>
       <c r="R675" s="11" t="n"/>
-      <c r="S675" s="11" t="n"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="11" t="n"/>
@@ -15294,7 +14566,6 @@
       <c r="P676" s="11" t="n"/>
       <c r="Q676" s="11" t="n"/>
       <c r="R676" s="11" t="n"/>
-      <c r="S676" s="11" t="n"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="11" t="n"/>
@@ -15315,7 +14586,6 @@
       <c r="P677" s="11" t="n"/>
       <c r="Q677" s="11" t="n"/>
       <c r="R677" s="11" t="n"/>
-      <c r="S677" s="11" t="n"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="11" t="n"/>
@@ -15336,7 +14606,6 @@
       <c r="P678" s="11" t="n"/>
       <c r="Q678" s="11" t="n"/>
       <c r="R678" s="11" t="n"/>
-      <c r="S678" s="11" t="n"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="11" t="n"/>
@@ -15357,7 +14626,6 @@
       <c r="P679" s="11" t="n"/>
       <c r="Q679" s="11" t="n"/>
       <c r="R679" s="11" t="n"/>
-      <c r="S679" s="11" t="n"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="11" t="n"/>
@@ -15378,7 +14646,6 @@
       <c r="P680" s="11" t="n"/>
       <c r="Q680" s="11" t="n"/>
       <c r="R680" s="11" t="n"/>
-      <c r="S680" s="11" t="n"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="11" t="n"/>
@@ -15399,7 +14666,6 @@
       <c r="P681" s="11" t="n"/>
       <c r="Q681" s="11" t="n"/>
       <c r="R681" s="11" t="n"/>
-      <c r="S681" s="11" t="n"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="11" t="n"/>
@@ -15420,7 +14686,6 @@
       <c r="P682" s="11" t="n"/>
       <c r="Q682" s="11" t="n"/>
       <c r="R682" s="11" t="n"/>
-      <c r="S682" s="11" t="n"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="11" t="n"/>
@@ -15441,7 +14706,6 @@
       <c r="P683" s="11" t="n"/>
       <c r="Q683" s="11" t="n"/>
       <c r="R683" s="11" t="n"/>
-      <c r="S683" s="11" t="n"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="11" t="n"/>
@@ -15462,7 +14726,6 @@
       <c r="P684" s="11" t="n"/>
       <c r="Q684" s="11" t="n"/>
       <c r="R684" s="11" t="n"/>
-      <c r="S684" s="11" t="n"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="11" t="n"/>
@@ -15483,7 +14746,6 @@
       <c r="P685" s="11" t="n"/>
       <c r="Q685" s="11" t="n"/>
       <c r="R685" s="11" t="n"/>
-      <c r="S685" s="11" t="n"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="11" t="n"/>
@@ -15504,7 +14766,6 @@
       <c r="P686" s="11" t="n"/>
       <c r="Q686" s="11" t="n"/>
       <c r="R686" s="11" t="n"/>
-      <c r="S686" s="11" t="n"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="11" t="n"/>
@@ -15525,7 +14786,6 @@
       <c r="P687" s="11" t="n"/>
       <c r="Q687" s="11" t="n"/>
       <c r="R687" s="11" t="n"/>
-      <c r="S687" s="11" t="n"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="11" t="n"/>
@@ -15546,7 +14806,6 @@
       <c r="P688" s="11" t="n"/>
       <c r="Q688" s="11" t="n"/>
       <c r="R688" s="11" t="n"/>
-      <c r="S688" s="11" t="n"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="11" t="n"/>
@@ -15567,7 +14826,6 @@
       <c r="P689" s="11" t="n"/>
       <c r="Q689" s="11" t="n"/>
       <c r="R689" s="11" t="n"/>
-      <c r="S689" s="11" t="n"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="11" t="n"/>
@@ -15588,7 +14846,6 @@
       <c r="P690" s="11" t="n"/>
       <c r="Q690" s="11" t="n"/>
       <c r="R690" s="11" t="n"/>
-      <c r="S690" s="11" t="n"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="11" t="n"/>
@@ -15609,7 +14866,6 @@
       <c r="P691" s="11" t="n"/>
       <c r="Q691" s="11" t="n"/>
       <c r="R691" s="11" t="n"/>
-      <c r="S691" s="11" t="n"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="11" t="n"/>
@@ -15630,7 +14886,6 @@
       <c r="P692" s="11" t="n"/>
       <c r="Q692" s="11" t="n"/>
       <c r="R692" s="11" t="n"/>
-      <c r="S692" s="11" t="n"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="11" t="n"/>
@@ -15651,7 +14906,6 @@
       <c r="P693" s="11" t="n"/>
       <c r="Q693" s="11" t="n"/>
       <c r="R693" s="11" t="n"/>
-      <c r="S693" s="11" t="n"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="11" t="n"/>
@@ -15672,7 +14926,6 @@
       <c r="P694" s="11" t="n"/>
       <c r="Q694" s="11" t="n"/>
       <c r="R694" s="11" t="n"/>
-      <c r="S694" s="11" t="n"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="11" t="n"/>
@@ -15693,7 +14946,6 @@
       <c r="P695" s="11" t="n"/>
       <c r="Q695" s="11" t="n"/>
       <c r="R695" s="11" t="n"/>
-      <c r="S695" s="11" t="n"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="11" t="n"/>
@@ -15714,7 +14966,6 @@
       <c r="P696" s="11" t="n"/>
       <c r="Q696" s="11" t="n"/>
       <c r="R696" s="11" t="n"/>
-      <c r="S696" s="11" t="n"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="11" t="n"/>
@@ -15735,7 +14986,6 @@
       <c r="P697" s="11" t="n"/>
       <c r="Q697" s="11" t="n"/>
       <c r="R697" s="11" t="n"/>
-      <c r="S697" s="11" t="n"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="11" t="n"/>
@@ -15756,7 +15006,6 @@
       <c r="P698" s="11" t="n"/>
       <c r="Q698" s="11" t="n"/>
       <c r="R698" s="11" t="n"/>
-      <c r="S698" s="11" t="n"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="11" t="n"/>
@@ -15777,7 +15026,6 @@
       <c r="P699" s="11" t="n"/>
       <c r="Q699" s="11" t="n"/>
       <c r="R699" s="11" t="n"/>
-      <c r="S699" s="11" t="n"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="11" t="n"/>
@@ -15798,7 +15046,6 @@
       <c r="P700" s="11" t="n"/>
       <c r="Q700" s="11" t="n"/>
       <c r="R700" s="11" t="n"/>
-      <c r="S700" s="11" t="n"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="11" t="n"/>
@@ -15819,7 +15066,6 @@
       <c r="P701" s="11" t="n"/>
       <c r="Q701" s="11" t="n"/>
       <c r="R701" s="11" t="n"/>
-      <c r="S701" s="11" t="n"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="11" t="n"/>
@@ -15840,7 +15086,6 @@
       <c r="P702" s="11" t="n"/>
       <c r="Q702" s="11" t="n"/>
       <c r="R702" s="11" t="n"/>
-      <c r="S702" s="11" t="n"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="11" t="n"/>
@@ -15861,7 +15106,6 @@
       <c r="P703" s="11" t="n"/>
       <c r="Q703" s="11" t="n"/>
       <c r="R703" s="11" t="n"/>
-      <c r="S703" s="11" t="n"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="11" t="n"/>
@@ -15882,7 +15126,6 @@
       <c r="P704" s="11" t="n"/>
       <c r="Q704" s="11" t="n"/>
       <c r="R704" s="11" t="n"/>
-      <c r="S704" s="11" t="n"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="11" t="n"/>
@@ -15903,7 +15146,6 @@
       <c r="P705" s="11" t="n"/>
       <c r="Q705" s="11" t="n"/>
       <c r="R705" s="11" t="n"/>
-      <c r="S705" s="11" t="n"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="11" t="n"/>
@@ -15924,7 +15166,6 @@
       <c r="P706" s="11" t="n"/>
       <c r="Q706" s="11" t="n"/>
       <c r="R706" s="11" t="n"/>
-      <c r="S706" s="11" t="n"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="11" t="n"/>
@@ -15945,7 +15186,6 @@
       <c r="P707" s="11" t="n"/>
       <c r="Q707" s="11" t="n"/>
       <c r="R707" s="11" t="n"/>
-      <c r="S707" s="11" t="n"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="11" t="n"/>
@@ -15966,7 +15206,6 @@
       <c r="P708" s="11" t="n"/>
       <c r="Q708" s="11" t="n"/>
       <c r="R708" s="11" t="n"/>
-      <c r="S708" s="11" t="n"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="11" t="n"/>
@@ -15987,7 +15226,6 @@
       <c r="P709" s="11" t="n"/>
       <c r="Q709" s="11" t="n"/>
       <c r="R709" s="11" t="n"/>
-      <c r="S709" s="11" t="n"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="11" t="n"/>
@@ -16008,7 +15246,6 @@
       <c r="P710" s="11" t="n"/>
       <c r="Q710" s="11" t="n"/>
       <c r="R710" s="11" t="n"/>
-      <c r="S710" s="11" t="n"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="11" t="n"/>
@@ -16029,7 +15266,6 @@
       <c r="P711" s="11" t="n"/>
       <c r="Q711" s="11" t="n"/>
       <c r="R711" s="11" t="n"/>
-      <c r="S711" s="11" t="n"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="11" t="n"/>
@@ -16050,7 +15286,6 @@
       <c r="P712" s="11" t="n"/>
       <c r="Q712" s="11" t="n"/>
       <c r="R712" s="11" t="n"/>
-      <c r="S712" s="11" t="n"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="11" t="n"/>
@@ -16071,7 +15306,6 @@
       <c r="P713" s="11" t="n"/>
       <c r="Q713" s="11" t="n"/>
       <c r="R713" s="11" t="n"/>
-      <c r="S713" s="11" t="n"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="11" t="n"/>
@@ -16092,7 +15326,6 @@
       <c r="P714" s="11" t="n"/>
       <c r="Q714" s="11" t="n"/>
       <c r="R714" s="11" t="n"/>
-      <c r="S714" s="11" t="n"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="11" t="n"/>
@@ -16113,7 +15346,6 @@
       <c r="P715" s="11" t="n"/>
       <c r="Q715" s="11" t="n"/>
       <c r="R715" s="11" t="n"/>
-      <c r="S715" s="11" t="n"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="11" t="n"/>
@@ -16134,7 +15366,6 @@
       <c r="P716" s="11" t="n"/>
       <c r="Q716" s="11" t="n"/>
       <c r="R716" s="11" t="n"/>
-      <c r="S716" s="11" t="n"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="11" t="n"/>
@@ -16155,7 +15386,6 @@
       <c r="P717" s="11" t="n"/>
       <c r="Q717" s="11" t="n"/>
       <c r="R717" s="11" t="n"/>
-      <c r="S717" s="11" t="n"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="11" t="n"/>
@@ -16176,7 +15406,6 @@
       <c r="P718" s="11" t="n"/>
       <c r="Q718" s="11" t="n"/>
       <c r="R718" s="11" t="n"/>
-      <c r="S718" s="11" t="n"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="11" t="n"/>
@@ -16197,7 +15426,6 @@
       <c r="P719" s="11" t="n"/>
       <c r="Q719" s="11" t="n"/>
       <c r="R719" s="11" t="n"/>
-      <c r="S719" s="11" t="n"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="11" t="n"/>
@@ -16218,7 +15446,6 @@
       <c r="P720" s="11" t="n"/>
       <c r="Q720" s="11" t="n"/>
       <c r="R720" s="11" t="n"/>
-      <c r="S720" s="11" t="n"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="11" t="n"/>
@@ -16239,7 +15466,6 @@
       <c r="P721" s="11" t="n"/>
       <c r="Q721" s="11" t="n"/>
       <c r="R721" s="11" t="n"/>
-      <c r="S721" s="11" t="n"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="11" t="n"/>
@@ -16260,7 +15486,6 @@
       <c r="P722" s="11" t="n"/>
       <c r="Q722" s="11" t="n"/>
       <c r="R722" s="11" t="n"/>
-      <c r="S722" s="11" t="n"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="11" t="n"/>
@@ -16281,7 +15506,6 @@
       <c r="P723" s="11" t="n"/>
       <c r="Q723" s="11" t="n"/>
       <c r="R723" s="11" t="n"/>
-      <c r="S723" s="11" t="n"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="11" t="n"/>
@@ -16302,7 +15526,6 @@
       <c r="P724" s="11" t="n"/>
       <c r="Q724" s="11" t="n"/>
       <c r="R724" s="11" t="n"/>
-      <c r="S724" s="11" t="n"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="11" t="n"/>
@@ -16323,7 +15546,6 @@
       <c r="P725" s="11" t="n"/>
       <c r="Q725" s="11" t="n"/>
       <c r="R725" s="11" t="n"/>
-      <c r="S725" s="11" t="n"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="11" t="n"/>
@@ -16344,7 +15566,6 @@
       <c r="P726" s="11" t="n"/>
       <c r="Q726" s="11" t="n"/>
       <c r="R726" s="11" t="n"/>
-      <c r="S726" s="11" t="n"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="11" t="n"/>
@@ -16365,7 +15586,6 @@
       <c r="P727" s="11" t="n"/>
       <c r="Q727" s="11" t="n"/>
       <c r="R727" s="11" t="n"/>
-      <c r="S727" s="11" t="n"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="11" t="n"/>
@@ -16386,7 +15606,6 @@
       <c r="P728" s="11" t="n"/>
       <c r="Q728" s="11" t="n"/>
       <c r="R728" s="11" t="n"/>
-      <c r="S728" s="11" t="n"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="11" t="n"/>
@@ -16407,7 +15626,6 @@
       <c r="P729" s="11" t="n"/>
       <c r="Q729" s="11" t="n"/>
       <c r="R729" s="11" t="n"/>
-      <c r="S729" s="11" t="n"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="11" t="n"/>
@@ -16428,7 +15646,6 @@
       <c r="P730" s="11" t="n"/>
       <c r="Q730" s="11" t="n"/>
       <c r="R730" s="11" t="n"/>
-      <c r="S730" s="11" t="n"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="11" t="n"/>
@@ -16449,7 +15666,6 @@
       <c r="P731" s="11" t="n"/>
       <c r="Q731" s="11" t="n"/>
       <c r="R731" s="11" t="n"/>
-      <c r="S731" s="11" t="n"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="11" t="n"/>
@@ -16470,7 +15686,6 @@
       <c r="P732" s="11" t="n"/>
       <c r="Q732" s="11" t="n"/>
       <c r="R732" s="11" t="n"/>
-      <c r="S732" s="11" t="n"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="11" t="n"/>
@@ -16491,7 +15706,6 @@
       <c r="P733" s="11" t="n"/>
       <c r="Q733" s="11" t="n"/>
       <c r="R733" s="11" t="n"/>
-      <c r="S733" s="11" t="n"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="11" t="n"/>
@@ -16512,7 +15726,6 @@
       <c r="P734" s="11" t="n"/>
       <c r="Q734" s="11" t="n"/>
       <c r="R734" s="11" t="n"/>
-      <c r="S734" s="11" t="n"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="11" t="n"/>
@@ -16533,7 +15746,6 @@
       <c r="P735" s="11" t="n"/>
       <c r="Q735" s="11" t="n"/>
       <c r="R735" s="11" t="n"/>
-      <c r="S735" s="11" t="n"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="11" t="n"/>
@@ -16554,7 +15766,6 @@
       <c r="P736" s="11" t="n"/>
       <c r="Q736" s="11" t="n"/>
       <c r="R736" s="11" t="n"/>
-      <c r="S736" s="11" t="n"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="11" t="n"/>
@@ -16575,7 +15786,6 @@
       <c r="P737" s="11" t="n"/>
       <c r="Q737" s="11" t="n"/>
       <c r="R737" s="11" t="n"/>
-      <c r="S737" s="11" t="n"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="11" t="n"/>
@@ -16596,7 +15806,6 @@
       <c r="P738" s="11" t="n"/>
       <c r="Q738" s="11" t="n"/>
       <c r="R738" s="11" t="n"/>
-      <c r="S738" s="11" t="n"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="11" t="n"/>
@@ -16617,7 +15826,6 @@
       <c r="P739" s="11" t="n"/>
       <c r="Q739" s="11" t="n"/>
       <c r="R739" s="11" t="n"/>
-      <c r="S739" s="11" t="n"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="11" t="n"/>
@@ -16638,7 +15846,6 @@
       <c r="P740" s="11" t="n"/>
       <c r="Q740" s="11" t="n"/>
       <c r="R740" s="11" t="n"/>
-      <c r="S740" s="11" t="n"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="11" t="n"/>
@@ -16659,7 +15866,6 @@
       <c r="P741" s="11" t="n"/>
       <c r="Q741" s="11" t="n"/>
       <c r="R741" s="11" t="n"/>
-      <c r="S741" s="11" t="n"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="11" t="n"/>
@@ -16680,7 +15886,6 @@
       <c r="P742" s="11" t="n"/>
       <c r="Q742" s="11" t="n"/>
       <c r="R742" s="11" t="n"/>
-      <c r="S742" s="11" t="n"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="11" t="n"/>
@@ -16701,7 +15906,6 @@
       <c r="P743" s="11" t="n"/>
       <c r="Q743" s="11" t="n"/>
       <c r="R743" s="11" t="n"/>
-      <c r="S743" s="11" t="n"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="11" t="n"/>
@@ -16722,7 +15926,6 @@
       <c r="P744" s="11" t="n"/>
       <c r="Q744" s="11" t="n"/>
       <c r="R744" s="11" t="n"/>
-      <c r="S744" s="11" t="n"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="11" t="n"/>
@@ -16743,7 +15946,6 @@
       <c r="P745" s="11" t="n"/>
       <c r="Q745" s="11" t="n"/>
       <c r="R745" s="11" t="n"/>
-      <c r="S745" s="11" t="n"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="11" t="n"/>
@@ -16764,7 +15966,6 @@
       <c r="P746" s="11" t="n"/>
       <c r="Q746" s="11" t="n"/>
       <c r="R746" s="11" t="n"/>
-      <c r="S746" s="11" t="n"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="11" t="n"/>
@@ -16785,7 +15986,6 @@
       <c r="P747" s="11" t="n"/>
       <c r="Q747" s="11" t="n"/>
       <c r="R747" s="11" t="n"/>
-      <c r="S747" s="11" t="n"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="11" t="n"/>
@@ -16806,7 +16006,6 @@
       <c r="P748" s="11" t="n"/>
       <c r="Q748" s="11" t="n"/>
       <c r="R748" s="11" t="n"/>
-      <c r="S748" s="11" t="n"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="11" t="n"/>
@@ -16827,7 +16026,6 @@
       <c r="P749" s="11" t="n"/>
       <c r="Q749" s="11" t="n"/>
       <c r="R749" s="11" t="n"/>
-      <c r="S749" s="11" t="n"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="11" t="n"/>
@@ -16848,7 +16046,6 @@
       <c r="P750" s="11" t="n"/>
       <c r="Q750" s="11" t="n"/>
       <c r="R750" s="11" t="n"/>
-      <c r="S750" s="11" t="n"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="11" t="n"/>
@@ -16869,7 +16066,6 @@
       <c r="P751" s="11" t="n"/>
       <c r="Q751" s="11" t="n"/>
       <c r="R751" s="11" t="n"/>
-      <c r="S751" s="11" t="n"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="11" t="n"/>
@@ -16890,7 +16086,6 @@
       <c r="P752" s="11" t="n"/>
       <c r="Q752" s="11" t="n"/>
       <c r="R752" s="11" t="n"/>
-      <c r="S752" s="11" t="n"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="11" t="n"/>
@@ -16911,7 +16106,6 @@
       <c r="P753" s="11" t="n"/>
       <c r="Q753" s="11" t="n"/>
       <c r="R753" s="11" t="n"/>
-      <c r="S753" s="11" t="n"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="11" t="n"/>
@@ -16932,7 +16126,6 @@
       <c r="P754" s="11" t="n"/>
       <c r="Q754" s="11" t="n"/>
       <c r="R754" s="11" t="n"/>
-      <c r="S754" s="11" t="n"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="11" t="n"/>
@@ -16953,7 +16146,6 @@
       <c r="P755" s="11" t="n"/>
       <c r="Q755" s="11" t="n"/>
       <c r="R755" s="11" t="n"/>
-      <c r="S755" s="11" t="n"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="11" t="n"/>
@@ -16974,7 +16166,6 @@
       <c r="P756" s="11" t="n"/>
       <c r="Q756" s="11" t="n"/>
       <c r="R756" s="11" t="n"/>
-      <c r="S756" s="11" t="n"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="11" t="n"/>
@@ -16995,7 +16186,6 @@
       <c r="P757" s="11" t="n"/>
       <c r="Q757" s="11" t="n"/>
       <c r="R757" s="11" t="n"/>
-      <c r="S757" s="11" t="n"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="11" t="n"/>
@@ -17016,7 +16206,6 @@
       <c r="P758" s="11" t="n"/>
       <c r="Q758" s="11" t="n"/>
       <c r="R758" s="11" t="n"/>
-      <c r="S758" s="11" t="n"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="11" t="n"/>
@@ -17037,7 +16226,6 @@
       <c r="P759" s="11" t="n"/>
       <c r="Q759" s="11" t="n"/>
       <c r="R759" s="11" t="n"/>
-      <c r="S759" s="11" t="n"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="11" t="n"/>
@@ -17058,7 +16246,6 @@
       <c r="P760" s="11" t="n"/>
       <c r="Q760" s="11" t="n"/>
       <c r="R760" s="11" t="n"/>
-      <c r="S760" s="11" t="n"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="11" t="n"/>
@@ -17079,7 +16266,6 @@
       <c r="P761" s="11" t="n"/>
       <c r="Q761" s="11" t="n"/>
       <c r="R761" s="11" t="n"/>
-      <c r="S761" s="11" t="n"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="11" t="n"/>
@@ -17100,7 +16286,6 @@
       <c r="P762" s="11" t="n"/>
       <c r="Q762" s="11" t="n"/>
       <c r="R762" s="11" t="n"/>
-      <c r="S762" s="11" t="n"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="11" t="n"/>
@@ -17121,7 +16306,6 @@
       <c r="P763" s="11" t="n"/>
       <c r="Q763" s="11" t="n"/>
       <c r="R763" s="11" t="n"/>
-      <c r="S763" s="11" t="n"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="11" t="n"/>
@@ -17142,7 +16326,6 @@
       <c r="P764" s="11" t="n"/>
       <c r="Q764" s="11" t="n"/>
       <c r="R764" s="11" t="n"/>
-      <c r="S764" s="11" t="n"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="11" t="n"/>
@@ -17163,7 +16346,6 @@
       <c r="P765" s="11" t="n"/>
       <c r="Q765" s="11" t="n"/>
       <c r="R765" s="11" t="n"/>
-      <c r="S765" s="11" t="n"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="11" t="n"/>
@@ -17184,7 +16366,6 @@
       <c r="P766" s="11" t="n"/>
       <c r="Q766" s="11" t="n"/>
       <c r="R766" s="11" t="n"/>
-      <c r="S766" s="11" t="n"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="11" t="n"/>
@@ -17205,7 +16386,6 @@
       <c r="P767" s="11" t="n"/>
       <c r="Q767" s="11" t="n"/>
       <c r="R767" s="11" t="n"/>
-      <c r="S767" s="11" t="n"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="11" t="n"/>
@@ -17226,7 +16406,6 @@
       <c r="P768" s="11" t="n"/>
       <c r="Q768" s="11" t="n"/>
       <c r="R768" s="11" t="n"/>
-      <c r="S768" s="11" t="n"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="11" t="n"/>
@@ -17247,7 +16426,6 @@
       <c r="P769" s="11" t="n"/>
       <c r="Q769" s="11" t="n"/>
       <c r="R769" s="11" t="n"/>
-      <c r="S769" s="11" t="n"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="11" t="n"/>
@@ -17268,7 +16446,6 @@
       <c r="P770" s="11" t="n"/>
       <c r="Q770" s="11" t="n"/>
       <c r="R770" s="11" t="n"/>
-      <c r="S770" s="11" t="n"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="11" t="n"/>
@@ -17289,7 +16466,6 @@
       <c r="P771" s="11" t="n"/>
       <c r="Q771" s="11" t="n"/>
       <c r="R771" s="11" t="n"/>
-      <c r="S771" s="11" t="n"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="11" t="n"/>
@@ -17310,7 +16486,6 @@
       <c r="P772" s="11" t="n"/>
       <c r="Q772" s="11" t="n"/>
       <c r="R772" s="11" t="n"/>
-      <c r="S772" s="11" t="n"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="11" t="n"/>
@@ -17331,7 +16506,6 @@
       <c r="P773" s="11" t="n"/>
       <c r="Q773" s="11" t="n"/>
       <c r="R773" s="11" t="n"/>
-      <c r="S773" s="11" t="n"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="11" t="n"/>
@@ -17352,7 +16526,6 @@
       <c r="P774" s="11" t="n"/>
       <c r="Q774" s="11" t="n"/>
       <c r="R774" s="11" t="n"/>
-      <c r="S774" s="11" t="n"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="11" t="n"/>
@@ -17373,7 +16546,6 @@
       <c r="P775" s="11" t="n"/>
       <c r="Q775" s="11" t="n"/>
       <c r="R775" s="11" t="n"/>
-      <c r="S775" s="11" t="n"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="11" t="n"/>
@@ -17394,7 +16566,6 @@
       <c r="P776" s="11" t="n"/>
       <c r="Q776" s="11" t="n"/>
       <c r="R776" s="11" t="n"/>
-      <c r="S776" s="11" t="n"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="11" t="n"/>
@@ -17415,7 +16586,6 @@
       <c r="P777" s="11" t="n"/>
       <c r="Q777" s="11" t="n"/>
       <c r="R777" s="11" t="n"/>
-      <c r="S777" s="11" t="n"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="11" t="n"/>
@@ -17436,7 +16606,6 @@
       <c r="P778" s="11" t="n"/>
       <c r="Q778" s="11" t="n"/>
       <c r="R778" s="11" t="n"/>
-      <c r="S778" s="11" t="n"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="11" t="n"/>
@@ -17457,7 +16626,6 @@
       <c r="P779" s="11" t="n"/>
       <c r="Q779" s="11" t="n"/>
       <c r="R779" s="11" t="n"/>
-      <c r="S779" s="11" t="n"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="11" t="n"/>
@@ -17478,7 +16646,6 @@
       <c r="P780" s="11" t="n"/>
       <c r="Q780" s="11" t="n"/>
       <c r="R780" s="11" t="n"/>
-      <c r="S780" s="11" t="n"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="11" t="n"/>
@@ -17499,7 +16666,6 @@
       <c r="P781" s="11" t="n"/>
       <c r="Q781" s="11" t="n"/>
       <c r="R781" s="11" t="n"/>
-      <c r="S781" s="11" t="n"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="11" t="n"/>
@@ -17520,7 +16686,6 @@
       <c r="P782" s="11" t="n"/>
       <c r="Q782" s="11" t="n"/>
       <c r="R782" s="11" t="n"/>
-      <c r="S782" s="11" t="n"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="11" t="n"/>
@@ -17541,7 +16706,6 @@
       <c r="P783" s="11" t="n"/>
       <c r="Q783" s="11" t="n"/>
       <c r="R783" s="11" t="n"/>
-      <c r="S783" s="11" t="n"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="11" t="n"/>
@@ -17562,7 +16726,6 @@
       <c r="P784" s="11" t="n"/>
       <c r="Q784" s="11" t="n"/>
       <c r="R784" s="11" t="n"/>
-      <c r="S784" s="11" t="n"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="11" t="n"/>
@@ -17583,7 +16746,6 @@
       <c r="P785" s="11" t="n"/>
       <c r="Q785" s="11" t="n"/>
       <c r="R785" s="11" t="n"/>
-      <c r="S785" s="11" t="n"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="11" t="n"/>
@@ -17604,7 +16766,6 @@
       <c r="P786" s="11" t="n"/>
       <c r="Q786" s="11" t="n"/>
       <c r="R786" s="11" t="n"/>
-      <c r="S786" s="11" t="n"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="11" t="n"/>
@@ -17625,7 +16786,6 @@
       <c r="P787" s="11" t="n"/>
       <c r="Q787" s="11" t="n"/>
       <c r="R787" s="11" t="n"/>
-      <c r="S787" s="11" t="n"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="11" t="n"/>
@@ -17646,7 +16806,6 @@
       <c r="P788" s="11" t="n"/>
       <c r="Q788" s="11" t="n"/>
       <c r="R788" s="11" t="n"/>
-      <c r="S788" s="11" t="n"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="11" t="n"/>
@@ -17667,7 +16826,6 @@
       <c r="P789" s="11" t="n"/>
       <c r="Q789" s="11" t="n"/>
       <c r="R789" s="11" t="n"/>
-      <c r="S789" s="11" t="n"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="11" t="n"/>
@@ -17688,7 +16846,6 @@
       <c r="P790" s="11" t="n"/>
       <c r="Q790" s="11" t="n"/>
       <c r="R790" s="11" t="n"/>
-      <c r="S790" s="11" t="n"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="11" t="n"/>
@@ -17709,7 +16866,6 @@
       <c r="P791" s="11" t="n"/>
       <c r="Q791" s="11" t="n"/>
       <c r="R791" s="11" t="n"/>
-      <c r="S791" s="11" t="n"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="11" t="n"/>
@@ -17730,7 +16886,6 @@
       <c r="P792" s="11" t="n"/>
       <c r="Q792" s="11" t="n"/>
       <c r="R792" s="11" t="n"/>
-      <c r="S792" s="11" t="n"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="11" t="n"/>
@@ -17751,7 +16906,6 @@
       <c r="P793" s="11" t="n"/>
       <c r="Q793" s="11" t="n"/>
       <c r="R793" s="11" t="n"/>
-      <c r="S793" s="11" t="n"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="11" t="n"/>
@@ -17772,7 +16926,6 @@
       <c r="P794" s="11" t="n"/>
       <c r="Q794" s="11" t="n"/>
       <c r="R794" s="11" t="n"/>
-      <c r="S794" s="11" t="n"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="11" t="n"/>
@@ -17793,7 +16946,6 @@
       <c r="P795" s="11" t="n"/>
       <c r="Q795" s="11" t="n"/>
       <c r="R795" s="11" t="n"/>
-      <c r="S795" s="11" t="n"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="11" t="n"/>
@@ -17814,7 +16966,6 @@
       <c r="P796" s="11" t="n"/>
       <c r="Q796" s="11" t="n"/>
       <c r="R796" s="11" t="n"/>
-      <c r="S796" s="11" t="n"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="11" t="n"/>
@@ -17835,7 +16986,6 @@
       <c r="P797" s="11" t="n"/>
       <c r="Q797" s="11" t="n"/>
       <c r="R797" s="11" t="n"/>
-      <c r="S797" s="11" t="n"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="11" t="n"/>
@@ -17856,7 +17006,6 @@
       <c r="P798" s="11" t="n"/>
       <c r="Q798" s="11" t="n"/>
       <c r="R798" s="11" t="n"/>
-      <c r="S798" s="11" t="n"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="11" t="n"/>
@@ -17877,7 +17026,6 @@
       <c r="P799" s="11" t="n"/>
       <c r="Q799" s="11" t="n"/>
       <c r="R799" s="11" t="n"/>
-      <c r="S799" s="11" t="n"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="11" t="n"/>
@@ -17898,7 +17046,6 @@
       <c r="P800" s="11" t="n"/>
       <c r="Q800" s="11" t="n"/>
       <c r="R800" s="11" t="n"/>
-      <c r="S800" s="11" t="n"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="11" t="n"/>
@@ -17919,7 +17066,6 @@
       <c r="P801" s="11" t="n"/>
       <c r="Q801" s="11" t="n"/>
       <c r="R801" s="11" t="n"/>
-      <c r="S801" s="11" t="n"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="11" t="n"/>
@@ -17940,7 +17086,6 @@
       <c r="P802" s="11" t="n"/>
       <c r="Q802" s="11" t="n"/>
       <c r="R802" s="11" t="n"/>
-      <c r="S802" s="11" t="n"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="11" t="n"/>
@@ -17961,7 +17106,6 @@
       <c r="P803" s="11" t="n"/>
       <c r="Q803" s="11" t="n"/>
       <c r="R803" s="11" t="n"/>
-      <c r="S803" s="11" t="n"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="11" t="n"/>
@@ -17982,7 +17126,6 @@
       <c r="P804" s="11" t="n"/>
       <c r="Q804" s="11" t="n"/>
       <c r="R804" s="11" t="n"/>
-      <c r="S804" s="11" t="n"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="11" t="n"/>
@@ -18003,7 +17146,6 @@
       <c r="P805" s="11" t="n"/>
       <c r="Q805" s="11" t="n"/>
       <c r="R805" s="11" t="n"/>
-      <c r="S805" s="11" t="n"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="11" t="n"/>
@@ -18024,7 +17166,6 @@
       <c r="P806" s="11" t="n"/>
       <c r="Q806" s="11" t="n"/>
       <c r="R806" s="11" t="n"/>
-      <c r="S806" s="11" t="n"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="11" t="n"/>
@@ -18045,7 +17186,6 @@
       <c r="P807" s="11" t="n"/>
       <c r="Q807" s="11" t="n"/>
       <c r="R807" s="11" t="n"/>
-      <c r="S807" s="11" t="n"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="11" t="n"/>
@@ -18066,7 +17206,6 @@
       <c r="P808" s="11" t="n"/>
       <c r="Q808" s="11" t="n"/>
       <c r="R808" s="11" t="n"/>
-      <c r="S808" s="11" t="n"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="11" t="n"/>
@@ -18087,7 +17226,6 @@
       <c r="P809" s="11" t="n"/>
       <c r="Q809" s="11" t="n"/>
       <c r="R809" s="11" t="n"/>
-      <c r="S809" s="11" t="n"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="11" t="n"/>
@@ -18108,7 +17246,6 @@
       <c r="P810" s="11" t="n"/>
       <c r="Q810" s="11" t="n"/>
       <c r="R810" s="11" t="n"/>
-      <c r="S810" s="11" t="n"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="11" t="n"/>
@@ -18129,7 +17266,6 @@
       <c r="P811" s="11" t="n"/>
       <c r="Q811" s="11" t="n"/>
       <c r="R811" s="11" t="n"/>
-      <c r="S811" s="11" t="n"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="11" t="n"/>
@@ -18150,7 +17286,6 @@
       <c r="P812" s="11" t="n"/>
       <c r="Q812" s="11" t="n"/>
       <c r="R812" s="11" t="n"/>
-      <c r="S812" s="11" t="n"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="11" t="n"/>
@@ -18171,7 +17306,6 @@
       <c r="P813" s="11" t="n"/>
       <c r="Q813" s="11" t="n"/>
       <c r="R813" s="11" t="n"/>
-      <c r="S813" s="11" t="n"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="11" t="n"/>
@@ -18192,7 +17326,6 @@
       <c r="P814" s="11" t="n"/>
       <c r="Q814" s="11" t="n"/>
       <c r="R814" s="11" t="n"/>
-      <c r="S814" s="11" t="n"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="11" t="n"/>
@@ -18213,7 +17346,6 @@
       <c r="P815" s="11" t="n"/>
       <c r="Q815" s="11" t="n"/>
       <c r="R815" s="11" t="n"/>
-      <c r="S815" s="11" t="n"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="11" t="n"/>
@@ -18234,7 +17366,6 @@
       <c r="P816" s="11" t="n"/>
       <c r="Q816" s="11" t="n"/>
       <c r="R816" s="11" t="n"/>
-      <c r="S816" s="11" t="n"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="11" t="n"/>
@@ -18255,7 +17386,6 @@
       <c r="P817" s="11" t="n"/>
       <c r="Q817" s="11" t="n"/>
       <c r="R817" s="11" t="n"/>
-      <c r="S817" s="11" t="n"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="11" t="n"/>
@@ -18276,7 +17406,6 @@
       <c r="P818" s="11" t="n"/>
       <c r="Q818" s="11" t="n"/>
       <c r="R818" s="11" t="n"/>
-      <c r="S818" s="11" t="n"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="11" t="n"/>
@@ -18297,7 +17426,6 @@
       <c r="P819" s="11" t="n"/>
       <c r="Q819" s="11" t="n"/>
       <c r="R819" s="11" t="n"/>
-      <c r="S819" s="11" t="n"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="11" t="n"/>
@@ -18318,7 +17446,6 @@
       <c r="P820" s="11" t="n"/>
       <c r="Q820" s="11" t="n"/>
       <c r="R820" s="11" t="n"/>
-      <c r="S820" s="11" t="n"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="11" t="n"/>
@@ -18339,7 +17466,6 @@
       <c r="P821" s="11" t="n"/>
       <c r="Q821" s="11" t="n"/>
       <c r="R821" s="11" t="n"/>
-      <c r="S821" s="11" t="n"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="11" t="n"/>
@@ -18360,7 +17486,6 @@
       <c r="P822" s="11" t="n"/>
       <c r="Q822" s="11" t="n"/>
       <c r="R822" s="11" t="n"/>
-      <c r="S822" s="11" t="n"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="11" t="n"/>
@@ -18381,7 +17506,6 @@
       <c r="P823" s="11" t="n"/>
       <c r="Q823" s="11" t="n"/>
       <c r="R823" s="11" t="n"/>
-      <c r="S823" s="11" t="n"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="11" t="n"/>
@@ -18402,7 +17526,6 @@
       <c r="P824" s="11" t="n"/>
       <c r="Q824" s="11" t="n"/>
       <c r="R824" s="11" t="n"/>
-      <c r="S824" s="11" t="n"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="11" t="n"/>
@@ -18423,7 +17546,6 @@
       <c r="P825" s="11" t="n"/>
       <c r="Q825" s="11" t="n"/>
       <c r="R825" s="11" t="n"/>
-      <c r="S825" s="11" t="n"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="11" t="n"/>
@@ -18444,7 +17566,6 @@
       <c r="P826" s="11" t="n"/>
       <c r="Q826" s="11" t="n"/>
       <c r="R826" s="11" t="n"/>
-      <c r="S826" s="11" t="n"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="11" t="n"/>
@@ -18465,7 +17586,6 @@
       <c r="P827" s="11" t="n"/>
       <c r="Q827" s="11" t="n"/>
       <c r="R827" s="11" t="n"/>
-      <c r="S827" s="11" t="n"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="11" t="n"/>
@@ -18486,7 +17606,6 @@
       <c r="P828" s="11" t="n"/>
       <c r="Q828" s="11" t="n"/>
       <c r="R828" s="11" t="n"/>
-      <c r="S828" s="11" t="n"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="11" t="n"/>
@@ -18507,7 +17626,6 @@
       <c r="P829" s="11" t="n"/>
       <c r="Q829" s="11" t="n"/>
       <c r="R829" s="11" t="n"/>
-      <c r="S829" s="11" t="n"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="11" t="n"/>
@@ -18528,7 +17646,6 @@
       <c r="P830" s="11" t="n"/>
       <c r="Q830" s="11" t="n"/>
       <c r="R830" s="11" t="n"/>
-      <c r="S830" s="11" t="n"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="11" t="n"/>
@@ -18549,7 +17666,6 @@
       <c r="P831" s="11" t="n"/>
       <c r="Q831" s="11" t="n"/>
       <c r="R831" s="11" t="n"/>
-      <c r="S831" s="11" t="n"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="11" t="n"/>
@@ -18570,7 +17686,6 @@
       <c r="P832" s="11" t="n"/>
       <c r="Q832" s="11" t="n"/>
       <c r="R832" s="11" t="n"/>
-      <c r="S832" s="11" t="n"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="11" t="n"/>
@@ -18591,7 +17706,6 @@
       <c r="P833" s="11" t="n"/>
       <c r="Q833" s="11" t="n"/>
       <c r="R833" s="11" t="n"/>
-      <c r="S833" s="11" t="n"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="11" t="n"/>
@@ -18612,7 +17726,6 @@
       <c r="P834" s="11" t="n"/>
       <c r="Q834" s="11" t="n"/>
       <c r="R834" s="11" t="n"/>
-      <c r="S834" s="11" t="n"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="11" t="n"/>
@@ -18633,7 +17746,6 @@
       <c r="P835" s="11" t="n"/>
       <c r="Q835" s="11" t="n"/>
       <c r="R835" s="11" t="n"/>
-      <c r="S835" s="11" t="n"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="11" t="n"/>
@@ -18654,7 +17766,6 @@
       <c r="P836" s="11" t="n"/>
       <c r="Q836" s="11" t="n"/>
       <c r="R836" s="11" t="n"/>
-      <c r="S836" s="11" t="n"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="11" t="n"/>
@@ -18675,7 +17786,6 @@
       <c r="P837" s="11" t="n"/>
       <c r="Q837" s="11" t="n"/>
       <c r="R837" s="11" t="n"/>
-      <c r="S837" s="11" t="n"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="11" t="n"/>
@@ -18696,7 +17806,6 @@
       <c r="P838" s="11" t="n"/>
       <c r="Q838" s="11" t="n"/>
       <c r="R838" s="11" t="n"/>
-      <c r="S838" s="11" t="n"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="11" t="n"/>
@@ -18717,7 +17826,6 @@
       <c r="P839" s="11" t="n"/>
       <c r="Q839" s="11" t="n"/>
       <c r="R839" s="11" t="n"/>
-      <c r="S839" s="11" t="n"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="11" t="n"/>
@@ -18738,7 +17846,6 @@
       <c r="P840" s="11" t="n"/>
       <c r="Q840" s="11" t="n"/>
       <c r="R840" s="11" t="n"/>
-      <c r="S840" s="11" t="n"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="11" t="n"/>
@@ -18759,7 +17866,6 @@
       <c r="P841" s="11" t="n"/>
       <c r="Q841" s="11" t="n"/>
       <c r="R841" s="11" t="n"/>
-      <c r="S841" s="11" t="n"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="11" t="n"/>
@@ -18780,7 +17886,6 @@
       <c r="P842" s="11" t="n"/>
       <c r="Q842" s="11" t="n"/>
       <c r="R842" s="11" t="n"/>
-      <c r="S842" s="11" t="n"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="11" t="n"/>
@@ -18801,7 +17906,6 @@
       <c r="P843" s="11" t="n"/>
       <c r="Q843" s="11" t="n"/>
       <c r="R843" s="11" t="n"/>
-      <c r="S843" s="11" t="n"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="11" t="n"/>
@@ -18822,7 +17926,6 @@
       <c r="P844" s="11" t="n"/>
       <c r="Q844" s="11" t="n"/>
       <c r="R844" s="11" t="n"/>
-      <c r="S844" s="11" t="n"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="11" t="n"/>
@@ -18843,7 +17946,6 @@
       <c r="P845" s="11" t="n"/>
       <c r="Q845" s="11" t="n"/>
       <c r="R845" s="11" t="n"/>
-      <c r="S845" s="11" t="n"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="11" t="n"/>
@@ -18864,7 +17966,6 @@
       <c r="P846" s="11" t="n"/>
       <c r="Q846" s="11" t="n"/>
       <c r="R846" s="11" t="n"/>
-      <c r="S846" s="11" t="n"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="11" t="n"/>
@@ -18885,7 +17986,6 @@
       <c r="P847" s="11" t="n"/>
       <c r="Q847" s="11" t="n"/>
       <c r="R847" s="11" t="n"/>
-      <c r="S847" s="11" t="n"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="11" t="n"/>
@@ -18906,7 +18006,6 @@
       <c r="P848" s="11" t="n"/>
       <c r="Q848" s="11" t="n"/>
       <c r="R848" s="11" t="n"/>
-      <c r="S848" s="11" t="n"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="11" t="n"/>
@@ -18927,7 +18026,6 @@
       <c r="P849" s="11" t="n"/>
       <c r="Q849" s="11" t="n"/>
       <c r="R849" s="11" t="n"/>
-      <c r="S849" s="11" t="n"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="11" t="n"/>
@@ -18948,7 +18046,6 @@
       <c r="P850" s="11" t="n"/>
       <c r="Q850" s="11" t="n"/>
       <c r="R850" s="11" t="n"/>
-      <c r="S850" s="11" t="n"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="11" t="n"/>
@@ -18969,7 +18066,6 @@
       <c r="P851" s="11" t="n"/>
       <c r="Q851" s="11" t="n"/>
       <c r="R851" s="11" t="n"/>
-      <c r="S851" s="11" t="n"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="11" t="n"/>
@@ -18990,7 +18086,6 @@
       <c r="P852" s="11" t="n"/>
       <c r="Q852" s="11" t="n"/>
       <c r="R852" s="11" t="n"/>
-      <c r="S852" s="11" t="n"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="11" t="n"/>
@@ -19011,7 +18106,6 @@
       <c r="P853" s="11" t="n"/>
       <c r="Q853" s="11" t="n"/>
       <c r="R853" s="11" t="n"/>
-      <c r="S853" s="11" t="n"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="11" t="n"/>
@@ -19032,7 +18126,6 @@
       <c r="P854" s="11" t="n"/>
       <c r="Q854" s="11" t="n"/>
       <c r="R854" s="11" t="n"/>
-      <c r="S854" s="11" t="n"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="11" t="n"/>
@@ -19053,7 +18146,6 @@
       <c r="P855" s="11" t="n"/>
       <c r="Q855" s="11" t="n"/>
       <c r="R855" s="11" t="n"/>
-      <c r="S855" s="11" t="n"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="11" t="n"/>
@@ -19074,7 +18166,6 @@
       <c r="P856" s="11" t="n"/>
       <c r="Q856" s="11" t="n"/>
       <c r="R856" s="11" t="n"/>
-      <c r="S856" s="11" t="n"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="11" t="n"/>
@@ -19095,7 +18186,6 @@
       <c r="P857" s="11" t="n"/>
       <c r="Q857" s="11" t="n"/>
       <c r="R857" s="11" t="n"/>
-      <c r="S857" s="11" t="n"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="11" t="n"/>
@@ -19116,7 +18206,6 @@
       <c r="P858" s="11" t="n"/>
       <c r="Q858" s="11" t="n"/>
       <c r="R858" s="11" t="n"/>
-      <c r="S858" s="11" t="n"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="11" t="n"/>
@@ -19137,7 +18226,6 @@
       <c r="P859" s="11" t="n"/>
       <c r="Q859" s="11" t="n"/>
       <c r="R859" s="11" t="n"/>
-      <c r="S859" s="11" t="n"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="11" t="n"/>
@@ -19158,7 +18246,6 @@
       <c r="P860" s="11" t="n"/>
       <c r="Q860" s="11" t="n"/>
       <c r="R860" s="11" t="n"/>
-      <c r="S860" s="11" t="n"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="11" t="n"/>
@@ -19179,7 +18266,6 @@
       <c r="P861" s="11" t="n"/>
       <c r="Q861" s="11" t="n"/>
       <c r="R861" s="11" t="n"/>
-      <c r="S861" s="11" t="n"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="11" t="n"/>
@@ -19200,7 +18286,6 @@
       <c r="P862" s="11" t="n"/>
       <c r="Q862" s="11" t="n"/>
       <c r="R862" s="11" t="n"/>
-      <c r="S862" s="11" t="n"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="11" t="n"/>
@@ -19221,7 +18306,6 @@
       <c r="P863" s="11" t="n"/>
       <c r="Q863" s="11" t="n"/>
       <c r="R863" s="11" t="n"/>
-      <c r="S863" s="11" t="n"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="11" t="n"/>
@@ -19242,7 +18326,6 @@
       <c r="P864" s="11" t="n"/>
       <c r="Q864" s="11" t="n"/>
       <c r="R864" s="11" t="n"/>
-      <c r="S864" s="11" t="n"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
       <c r="A865" s="11" t="n"/>
@@ -19263,7 +18346,6 @@
       <c r="P865" s="11" t="n"/>
       <c r="Q865" s="11" t="n"/>
       <c r="R865" s="11" t="n"/>
-      <c r="S865" s="11" t="n"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="11" t="n"/>
@@ -19284,7 +18366,6 @@
       <c r="P866" s="11" t="n"/>
       <c r="Q866" s="11" t="n"/>
       <c r="R866" s="11" t="n"/>
-      <c r="S866" s="11" t="n"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="11" t="n"/>
@@ -19305,7 +18386,6 @@
       <c r="P867" s="11" t="n"/>
       <c r="Q867" s="11" t="n"/>
       <c r="R867" s="11" t="n"/>
-      <c r="S867" s="11" t="n"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="11" t="n"/>
@@ -19326,7 +18406,6 @@
       <c r="P868" s="11" t="n"/>
       <c r="Q868" s="11" t="n"/>
       <c r="R868" s="11" t="n"/>
-      <c r="S868" s="11" t="n"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="11" t="n"/>
@@ -19347,7 +18426,6 @@
       <c r="P869" s="11" t="n"/>
       <c r="Q869" s="11" t="n"/>
       <c r="R869" s="11" t="n"/>
-      <c r="S869" s="11" t="n"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="11" t="n"/>
@@ -19368,7 +18446,6 @@
       <c r="P870" s="11" t="n"/>
       <c r="Q870" s="11" t="n"/>
       <c r="R870" s="11" t="n"/>
-      <c r="S870" s="11" t="n"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="11" t="n"/>
@@ -19389,7 +18466,6 @@
       <c r="P871" s="11" t="n"/>
       <c r="Q871" s="11" t="n"/>
       <c r="R871" s="11" t="n"/>
-      <c r="S871" s="11" t="n"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="11" t="n"/>
@@ -19410,7 +18486,6 @@
       <c r="P872" s="11" t="n"/>
       <c r="Q872" s="11" t="n"/>
       <c r="R872" s="11" t="n"/>
-      <c r="S872" s="11" t="n"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="11" t="n"/>
@@ -19431,7 +18506,6 @@
       <c r="P873" s="11" t="n"/>
       <c r="Q873" s="11" t="n"/>
       <c r="R873" s="11" t="n"/>
-      <c r="S873" s="11" t="n"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="11" t="n"/>
@@ -19452,7 +18526,6 @@
       <c r="P874" s="11" t="n"/>
       <c r="Q874" s="11" t="n"/>
       <c r="R874" s="11" t="n"/>
-      <c r="S874" s="11" t="n"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="11" t="n"/>
@@ -19473,7 +18546,6 @@
       <c r="P875" s="11" t="n"/>
       <c r="Q875" s="11" t="n"/>
       <c r="R875" s="11" t="n"/>
-      <c r="S875" s="11" t="n"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="11" t="n"/>
@@ -19494,7 +18566,6 @@
       <c r="P876" s="11" t="n"/>
       <c r="Q876" s="11" t="n"/>
       <c r="R876" s="11" t="n"/>
-      <c r="S876" s="11" t="n"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="11" t="n"/>
@@ -19515,7 +18586,6 @@
       <c r="P877" s="11" t="n"/>
       <c r="Q877" s="11" t="n"/>
       <c r="R877" s="11" t="n"/>
-      <c r="S877" s="11" t="n"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="11" t="n"/>
@@ -19536,7 +18606,6 @@
       <c r="P878" s="11" t="n"/>
       <c r="Q878" s="11" t="n"/>
       <c r="R878" s="11" t="n"/>
-      <c r="S878" s="11" t="n"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="11" t="n"/>
@@ -19557,7 +18626,6 @@
       <c r="P879" s="11" t="n"/>
       <c r="Q879" s="11" t="n"/>
       <c r="R879" s="11" t="n"/>
-      <c r="S879" s="11" t="n"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="11" t="n"/>
@@ -19578,7 +18646,6 @@
       <c r="P880" s="11" t="n"/>
       <c r="Q880" s="11" t="n"/>
       <c r="R880" s="11" t="n"/>
-      <c r="S880" s="11" t="n"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="11" t="n"/>
@@ -19599,7 +18666,6 @@
       <c r="P881" s="11" t="n"/>
       <c r="Q881" s="11" t="n"/>
       <c r="R881" s="11" t="n"/>
-      <c r="S881" s="11" t="n"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="11" t="n"/>
@@ -19620,7 +18686,6 @@
       <c r="P882" s="11" t="n"/>
       <c r="Q882" s="11" t="n"/>
       <c r="R882" s="11" t="n"/>
-      <c r="S882" s="11" t="n"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="11" t="n"/>
@@ -19641,7 +18706,6 @@
       <c r="P883" s="11" t="n"/>
       <c r="Q883" s="11" t="n"/>
       <c r="R883" s="11" t="n"/>
-      <c r="S883" s="11" t="n"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="11" t="n"/>
@@ -19662,7 +18726,6 @@
       <c r="P884" s="11" t="n"/>
       <c r="Q884" s="11" t="n"/>
       <c r="R884" s="11" t="n"/>
-      <c r="S884" s="11" t="n"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="11" t="n"/>
@@ -19683,7 +18746,6 @@
       <c r="P885" s="11" t="n"/>
       <c r="Q885" s="11" t="n"/>
       <c r="R885" s="11" t="n"/>
-      <c r="S885" s="11" t="n"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="11" t="n"/>
@@ -19704,7 +18766,6 @@
       <c r="P886" s="11" t="n"/>
       <c r="Q886" s="11" t="n"/>
       <c r="R886" s="11" t="n"/>
-      <c r="S886" s="11" t="n"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="11" t="n"/>
@@ -19725,7 +18786,6 @@
       <c r="P887" s="11" t="n"/>
       <c r="Q887" s="11" t="n"/>
       <c r="R887" s="11" t="n"/>
-      <c r="S887" s="11" t="n"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="11" t="n"/>
@@ -19746,7 +18806,6 @@
       <c r="P888" s="11" t="n"/>
       <c r="Q888" s="11" t="n"/>
       <c r="R888" s="11" t="n"/>
-      <c r="S888" s="11" t="n"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="11" t="n"/>
@@ -19767,7 +18826,6 @@
       <c r="P889" s="11" t="n"/>
       <c r="Q889" s="11" t="n"/>
       <c r="R889" s="11" t="n"/>
-      <c r="S889" s="11" t="n"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="11" t="n"/>
@@ -19788,7 +18846,6 @@
       <c r="P890" s="11" t="n"/>
       <c r="Q890" s="11" t="n"/>
       <c r="R890" s="11" t="n"/>
-      <c r="S890" s="11" t="n"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="11" t="n"/>
@@ -19809,7 +18866,6 @@
       <c r="P891" s="11" t="n"/>
       <c r="Q891" s="11" t="n"/>
       <c r="R891" s="11" t="n"/>
-      <c r="S891" s="11" t="n"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="11" t="n"/>
@@ -19830,7 +18886,6 @@
       <c r="P892" s="11" t="n"/>
       <c r="Q892" s="11" t="n"/>
       <c r="R892" s="11" t="n"/>
-      <c r="S892" s="11" t="n"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="11" t="n"/>
@@ -19851,7 +18906,6 @@
       <c r="P893" s="11" t="n"/>
       <c r="Q893" s="11" t="n"/>
       <c r="R893" s="11" t="n"/>
-      <c r="S893" s="11" t="n"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="11" t="n"/>
@@ -19872,7 +18926,6 @@
       <c r="P894" s="11" t="n"/>
       <c r="Q894" s="11" t="n"/>
       <c r="R894" s="11" t="n"/>
-      <c r="S894" s="11" t="n"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="11" t="n"/>
@@ -19893,7 +18946,6 @@
       <c r="P895" s="11" t="n"/>
       <c r="Q895" s="11" t="n"/>
       <c r="R895" s="11" t="n"/>
-      <c r="S895" s="11" t="n"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="11" t="n"/>
@@ -19914,7 +18966,6 @@
       <c r="P896" s="11" t="n"/>
       <c r="Q896" s="11" t="n"/>
       <c r="R896" s="11" t="n"/>
-      <c r="S896" s="11" t="n"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="11" t="n"/>
@@ -19935,7 +18986,6 @@
       <c r="P897" s="11" t="n"/>
       <c r="Q897" s="11" t="n"/>
       <c r="R897" s="11" t="n"/>
-      <c r="S897" s="11" t="n"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="11" t="n"/>
@@ -19956,7 +19006,6 @@
       <c r="P898" s="11" t="n"/>
       <c r="Q898" s="11" t="n"/>
       <c r="R898" s="11" t="n"/>
-      <c r="S898" s="11" t="n"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="11" t="n"/>
@@ -19977,7 +19026,6 @@
       <c r="P899" s="11" t="n"/>
       <c r="Q899" s="11" t="n"/>
       <c r="R899" s="11" t="n"/>
-      <c r="S899" s="11" t="n"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="11" t="n"/>
@@ -19998,7 +19046,6 @@
       <c r="P900" s="11" t="n"/>
       <c r="Q900" s="11" t="n"/>
       <c r="R900" s="11" t="n"/>
-      <c r="S900" s="11" t="n"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="11" t="n"/>
@@ -20019,7 +19066,6 @@
       <c r="P901" s="11" t="n"/>
       <c r="Q901" s="11" t="n"/>
       <c r="R901" s="11" t="n"/>
-      <c r="S901" s="11" t="n"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="11" t="n"/>
@@ -20040,7 +19086,6 @@
       <c r="P902" s="11" t="n"/>
       <c r="Q902" s="11" t="n"/>
       <c r="R902" s="11" t="n"/>
-      <c r="S902" s="11" t="n"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="11" t="n"/>
@@ -20061,7 +19106,6 @@
       <c r="P903" s="11" t="n"/>
       <c r="Q903" s="11" t="n"/>
       <c r="R903" s="11" t="n"/>
-      <c r="S903" s="11" t="n"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="11" t="n"/>
@@ -20082,7 +19126,6 @@
       <c r="P904" s="11" t="n"/>
       <c r="Q904" s="11" t="n"/>
       <c r="R904" s="11" t="n"/>
-      <c r="S904" s="11" t="n"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="11" t="n"/>
@@ -20103,7 +19146,6 @@
       <c r="P905" s="11" t="n"/>
       <c r="Q905" s="11" t="n"/>
       <c r="R905" s="11" t="n"/>
-      <c r="S905" s="11" t="n"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="11" t="n"/>
@@ -20124,7 +19166,6 @@
       <c r="P906" s="11" t="n"/>
       <c r="Q906" s="11" t="n"/>
       <c r="R906" s="11" t="n"/>
-      <c r="S906" s="11" t="n"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="11" t="n"/>
@@ -20145,7 +19186,6 @@
       <c r="P907" s="11" t="n"/>
       <c r="Q907" s="11" t="n"/>
       <c r="R907" s="11" t="n"/>
-      <c r="S907" s="11" t="n"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="11" t="n"/>
@@ -20166,7 +19206,6 @@
       <c r="P908" s="11" t="n"/>
       <c r="Q908" s="11" t="n"/>
       <c r="R908" s="11" t="n"/>
-      <c r="S908" s="11" t="n"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="11" t="n"/>
@@ -20187,7 +19226,6 @@
       <c r="P909" s="11" t="n"/>
       <c r="Q909" s="11" t="n"/>
       <c r="R909" s="11" t="n"/>
-      <c r="S909" s="11" t="n"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="11" t="n"/>
@@ -20208,7 +19246,6 @@
       <c r="P910" s="11" t="n"/>
       <c r="Q910" s="11" t="n"/>
       <c r="R910" s="11" t="n"/>
-      <c r="S910" s="11" t="n"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="11" t="n"/>
@@ -20229,7 +19266,6 @@
       <c r="P911" s="11" t="n"/>
       <c r="Q911" s="11" t="n"/>
       <c r="R911" s="11" t="n"/>
-      <c r="S911" s="11" t="n"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="11" t="n"/>
@@ -20250,7 +19286,6 @@
       <c r="P912" s="11" t="n"/>
       <c r="Q912" s="11" t="n"/>
       <c r="R912" s="11" t="n"/>
-      <c r="S912" s="11" t="n"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="11" t="n"/>
@@ -20271,7 +19306,6 @@
       <c r="P913" s="11" t="n"/>
       <c r="Q913" s="11" t="n"/>
       <c r="R913" s="11" t="n"/>
-      <c r="S913" s="11" t="n"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="11" t="n"/>
@@ -20292,7 +19326,6 @@
       <c r="P914" s="11" t="n"/>
       <c r="Q914" s="11" t="n"/>
       <c r="R914" s="11" t="n"/>
-      <c r="S914" s="11" t="n"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="11" t="n"/>
@@ -20313,7 +19346,6 @@
       <c r="P915" s="11" t="n"/>
       <c r="Q915" s="11" t="n"/>
       <c r="R915" s="11" t="n"/>
-      <c r="S915" s="11" t="n"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="11" t="n"/>
@@ -20334,7 +19366,6 @@
       <c r="P916" s="11" t="n"/>
       <c r="Q916" s="11" t="n"/>
       <c r="R916" s="11" t="n"/>
-      <c r="S916" s="11" t="n"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="11" t="n"/>
@@ -20355,7 +19386,6 @@
       <c r="P917" s="11" t="n"/>
       <c r="Q917" s="11" t="n"/>
       <c r="R917" s="11" t="n"/>
-      <c r="S917" s="11" t="n"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="11" t="n"/>
@@ -20376,7 +19406,6 @@
       <c r="P918" s="11" t="n"/>
       <c r="Q918" s="11" t="n"/>
       <c r="R918" s="11" t="n"/>
-      <c r="S918" s="11" t="n"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
       <c r="A919" s="11" t="n"/>
@@ -20397,7 +19426,6 @@
       <c r="P919" s="11" t="n"/>
       <c r="Q919" s="11" t="n"/>
       <c r="R919" s="11" t="n"/>
-      <c r="S919" s="11" t="n"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="11" t="n"/>
@@ -20418,7 +19446,6 @@
       <c r="P920" s="11" t="n"/>
       <c r="Q920" s="11" t="n"/>
       <c r="R920" s="11" t="n"/>
-      <c r="S920" s="11" t="n"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="11" t="n"/>
@@ -20439,7 +19466,6 @@
       <c r="P921" s="11" t="n"/>
       <c r="Q921" s="11" t="n"/>
       <c r="R921" s="11" t="n"/>
-      <c r="S921" s="11" t="n"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="11" t="n"/>
@@ -20460,7 +19486,6 @@
       <c r="P922" s="11" t="n"/>
       <c r="Q922" s="11" t="n"/>
       <c r="R922" s="11" t="n"/>
-      <c r="S922" s="11" t="n"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="11" t="n"/>
@@ -20481,7 +19506,6 @@
       <c r="P923" s="11" t="n"/>
       <c r="Q923" s="11" t="n"/>
       <c r="R923" s="11" t="n"/>
-      <c r="S923" s="11" t="n"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="11" t="n"/>
@@ -20502,7 +19526,6 @@
       <c r="P924" s="11" t="n"/>
       <c r="Q924" s="11" t="n"/>
       <c r="R924" s="11" t="n"/>
-      <c r="S924" s="11" t="n"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="11" t="n"/>
@@ -20523,7 +19546,6 @@
       <c r="P925" s="11" t="n"/>
       <c r="Q925" s="11" t="n"/>
       <c r="R925" s="11" t="n"/>
-      <c r="S925" s="11" t="n"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="11" t="n"/>
@@ -20544,7 +19566,6 @@
       <c r="P926" s="11" t="n"/>
       <c r="Q926" s="11" t="n"/>
       <c r="R926" s="11" t="n"/>
-      <c r="S926" s="11" t="n"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="11" t="n"/>
@@ -20565,7 +19586,6 @@
       <c r="P927" s="11" t="n"/>
       <c r="Q927" s="11" t="n"/>
       <c r="R927" s="11" t="n"/>
-      <c r="S927" s="11" t="n"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
       <c r="A928" s="11" t="n"/>
@@ -20586,7 +19606,6 @@
       <c r="P928" s="11" t="n"/>
       <c r="Q928" s="11" t="n"/>
       <c r="R928" s="11" t="n"/>
-      <c r="S928" s="11" t="n"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="11" t="n"/>
@@ -20607,7 +19626,6 @@
       <c r="P929" s="11" t="n"/>
       <c r="Q929" s="11" t="n"/>
       <c r="R929" s="11" t="n"/>
-      <c r="S929" s="11" t="n"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="11" t="n"/>
@@ -20628,7 +19646,6 @@
       <c r="P930" s="11" t="n"/>
       <c r="Q930" s="11" t="n"/>
       <c r="R930" s="11" t="n"/>
-      <c r="S930" s="11" t="n"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="11" t="n"/>
@@ -20649,7 +19666,6 @@
       <c r="P931" s="11" t="n"/>
       <c r="Q931" s="11" t="n"/>
       <c r="R931" s="11" t="n"/>
-      <c r="S931" s="11" t="n"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="11" t="n"/>
@@ -20670,7 +19686,6 @@
       <c r="P932" s="11" t="n"/>
       <c r="Q932" s="11" t="n"/>
       <c r="R932" s="11" t="n"/>
-      <c r="S932" s="11" t="n"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="11" t="n"/>
@@ -20691,7 +19706,6 @@
       <c r="P933" s="11" t="n"/>
       <c r="Q933" s="11" t="n"/>
       <c r="R933" s="11" t="n"/>
-      <c r="S933" s="11" t="n"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="11" t="n"/>
@@ -20712,7 +19726,6 @@
       <c r="P934" s="11" t="n"/>
       <c r="Q934" s="11" t="n"/>
       <c r="R934" s="11" t="n"/>
-      <c r="S934" s="11" t="n"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="11" t="n"/>
@@ -20733,7 +19746,6 @@
       <c r="P935" s="11" t="n"/>
       <c r="Q935" s="11" t="n"/>
       <c r="R935" s="11" t="n"/>
-      <c r="S935" s="11" t="n"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="11" t="n"/>
@@ -20754,7 +19766,6 @@
       <c r="P936" s="11" t="n"/>
       <c r="Q936" s="11" t="n"/>
       <c r="R936" s="11" t="n"/>
-      <c r="S936" s="11" t="n"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
       <c r="A937" s="11" t="n"/>
@@ -20775,7 +19786,6 @@
       <c r="P937" s="11" t="n"/>
       <c r="Q937" s="11" t="n"/>
       <c r="R937" s="11" t="n"/>
-      <c r="S937" s="11" t="n"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="11" t="n"/>
@@ -20796,7 +19806,6 @@
       <c r="P938" s="11" t="n"/>
       <c r="Q938" s="11" t="n"/>
       <c r="R938" s="11" t="n"/>
-      <c r="S938" s="11" t="n"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="11" t="n"/>
@@ -20817,7 +19826,6 @@
       <c r="P939" s="11" t="n"/>
       <c r="Q939" s="11" t="n"/>
       <c r="R939" s="11" t="n"/>
-      <c r="S939" s="11" t="n"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="11" t="n"/>
@@ -20838,7 +19846,6 @@
       <c r="P940" s="11" t="n"/>
       <c r="Q940" s="11" t="n"/>
       <c r="R940" s="11" t="n"/>
-      <c r="S940" s="11" t="n"/>
     </row>
     <row r="941" ht="15.75" customHeight="1"/>
   </sheetData>
